--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1274" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CB8EE37-B1FF-4FAD-9517-4B8AF1B195D7}"/>
+  <xr:revisionPtr revIDLastSave="1287" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E076089F-D80F-42F5-9F72-0EE933C6F1F2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14098" uniqueCount="2542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14128" uniqueCount="2547">
   <si>
     <t>ID</t>
   </si>
@@ -7908,6 +7908,22 @@
   </si>
   <si>
     <t>FRQ RIBEIRAO PRETO R01</t>
+  </si>
+  <si>
+    <t>Tive uma experiência muito ruim. Sempre paguei as mensalidades da Brastemp por débito automático, portanto sempe em dia. Na passagem da Brastemp para a Culligan, houve uma mensalidade que ficou em aberto, não sei porquê. Pedi várias vezes para que me mandassem um boleto para que eu pudesse saldar essa pendência, e nunca recebi. Há duas semanas pedi uma revisão urgente porque a água do filtro estava saindo com pó preto. Me informaram que não poderiam agendar o serviço por causa da pendência de pagamento. Diante da minha indignação, finalmente me mandaram o boleto, paguei e recebi o serviço, com duas semanas de atraso. Achei a atitude muito desagradável para com uma usuária, como eu, que sempre foi pontual.</t>
+  </si>
+  <si>
+    <t>marquei manutencao e a pessoa nao apareceu. e nao ligou pra avisar
+ai marquei outro dia e. deu certo , foi bom o atendimento</t>
+  </si>
+  <si>
+    <t>tive muitos problemas para conseguir fazer essa solicitação, e só consegui após entrar no reclame aqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aparelho veio com defeito e até o momento não consegui contato com o suporte </t>
+  </si>
+  <si>
+    <t>Pela segunda vez foi combinado a vinda do Técnico para verificação do Purificador e não foi realizada a visita.</t>
   </si>
 </sst>
 </file>
@@ -8363,7 +8379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1556"/>
+  <dimension ref="A1:M1561"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -67768,6 +67784,136 @@
         <v>2419</v>
       </c>
     </row>
+    <row r="1557" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1557" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1557" s="4">
+        <v>141674</v>
+      </c>
+      <c r="D1557" s="2">
+        <v>46279</v>
+      </c>
+      <c r="E1557" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1557" s="4" t="s">
+        <v>2542</v>
+      </c>
+      <c r="G1557" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H1557" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="M1557" s="4" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="1558" spans="2:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="B1558" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1558" s="4">
+        <v>135185</v>
+      </c>
+      <c r="D1558" s="2">
+        <v>46279</v>
+      </c>
+      <c r="E1558" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1558" s="5" t="s">
+        <v>2543</v>
+      </c>
+      <c r="G1558" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1558" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="M1558" s="4" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="1559" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1559" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1559" s="4">
+        <v>139941</v>
+      </c>
+      <c r="D1559" s="2">
+        <v>46279</v>
+      </c>
+      <c r="E1559" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1559" s="4" t="s">
+        <v>2544</v>
+      </c>
+      <c r="G1559" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1559" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1559" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1560" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1560" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1560" s="4">
+        <v>143045</v>
+      </c>
+      <c r="D1560" s="2">
+        <v>46279</v>
+      </c>
+      <c r="E1560" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1560" s="4" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G1560" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1560" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1560" s="4" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="1561" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1561" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1561" s="4">
+        <v>133539</v>
+      </c>
+      <c r="D1561" s="2">
+        <v>46280</v>
+      </c>
+      <c r="E1561" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1561" s="4" t="s">
+        <v>2546</v>
+      </c>
+      <c r="G1561" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1561" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="M1561" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1287" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E076089F-D80F-42F5-9F72-0EE933C6F1F2}"/>
+  <xr:revisionPtr revIDLastSave="1298" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{484A27C1-DB15-4DA9-A93B-40D3EFA25BCD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14128" uniqueCount="2547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14146" uniqueCount="2552">
   <si>
     <t>ID</t>
   </si>
@@ -7924,6 +7924,22 @@
   </si>
   <si>
     <t>Pela segunda vez foi combinado a vinda do Técnico para verificação do Purificador e não foi realizada a visita.</t>
+  </si>
+  <si>
+    <t>O representante reclamou do serviço, tbm não deixou ficha de ordem de serviço serviço , Segunda via pra mim.</t>
+  </si>
+  <si>
+    <t>Equipamento com defeito e estou aguardando o técnico para solucionar o problema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não apareceu ninguêm nem deram uma satisfação
+</t>
+  </si>
+  <si>
+    <t>AT SJRPRETO SP R02</t>
+  </si>
+  <si>
+    <t>FRQ GALEAO SUL RJ R03</t>
   </si>
 </sst>
 </file>
@@ -8379,7 +8395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1561"/>
+  <dimension ref="A1:M1564"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -67914,6 +67930,84 @@
         <v>2494</v>
       </c>
     </row>
+    <row r="1562" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1562" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1562" s="4">
+        <v>115696</v>
+      </c>
+      <c r="D1562" s="2">
+        <v>46280</v>
+      </c>
+      <c r="E1562" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1562" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="G1562" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1562" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1562" s="4" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="1563" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1563" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1563" s="4">
+        <v>143317</v>
+      </c>
+      <c r="D1563" s="2">
+        <v>46280</v>
+      </c>
+      <c r="E1563" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1563" s="4" t="s">
+        <v>2548</v>
+      </c>
+      <c r="G1563" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1563" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1563" s="4" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="1564" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="B1564" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1564" s="4">
+        <v>117140</v>
+      </c>
+      <c r="D1564" s="2">
+        <v>46280</v>
+      </c>
+      <c r="E1564" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1564" s="5" t="s">
+        <v>2549</v>
+      </c>
+      <c r="G1564" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1564" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="M1564" s="4" t="s">
+        <v>2551</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1298" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{484A27C1-DB15-4DA9-A93B-40D3EFA25BCD}"/>
+  <xr:revisionPtr revIDLastSave="1309" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90D3BC6C-9816-4BF1-9CBE-F34981014D58}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14146" uniqueCount="2552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14189" uniqueCount="2556">
   <si>
     <t>ID</t>
   </si>
@@ -7940,6 +7940,18 @@
   </si>
   <si>
     <t>FRQ GALEAO SUL RJ R03</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>purificador continua com gosto ruim</t>
+  </si>
+  <si>
+    <t>prestador não veio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prestador de serviço não compareceu </t>
   </si>
 </sst>
 </file>
@@ -8395,7 +8407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1564"/>
+  <dimension ref="A1:M1567"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -67822,6 +67834,12 @@
       <c r="H1557" s="4" t="s">
         <v>1443</v>
       </c>
+      <c r="I1557" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1557" s="4" t="s">
+        <v>1337</v>
+      </c>
       <c r="M1557" s="4" t="s">
         <v>2419</v>
       </c>
@@ -67848,6 +67866,12 @@
       <c r="H1558" s="4" t="s">
         <v>948</v>
       </c>
+      <c r="I1558" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1558" s="4" t="s">
+        <v>1337</v>
+      </c>
       <c r="M1558" s="4" t="s">
         <v>2418</v>
       </c>
@@ -67874,6 +67898,12 @@
       <c r="H1559" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="I1559" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1559" s="4" t="s">
+        <v>1338</v>
+      </c>
       <c r="M1559" s="4" t="s">
         <v>2494</v>
       </c>
@@ -67900,6 +67930,12 @@
       <c r="H1560" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="I1560" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1560" s="4" t="s">
+        <v>1337</v>
+      </c>
       <c r="M1560" s="4" t="s">
         <v>2453</v>
       </c>
@@ -67926,6 +67962,12 @@
       <c r="H1561" s="4" t="s">
         <v>948</v>
       </c>
+      <c r="I1561" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1561" s="4" t="s">
+        <v>1337</v>
+      </c>
       <c r="M1561" s="4" t="s">
         <v>2494</v>
       </c>
@@ -67952,6 +67994,12 @@
       <c r="H1562" s="4" t="s">
         <v>48</v>
       </c>
+      <c r="I1562" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1562" s="4" t="s">
+        <v>1337</v>
+      </c>
       <c r="M1562" s="4" t="s">
         <v>2550</v>
       </c>
@@ -67978,6 +68026,12 @@
       <c r="H1563" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="I1563" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1563" s="4" t="s">
+        <v>1337</v>
+      </c>
       <c r="M1563" s="4" t="s">
         <v>2531</v>
       </c>
@@ -68004,8 +68058,110 @@
       <c r="H1564" s="4" t="s">
         <v>948</v>
       </c>
+      <c r="I1564" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1564" s="4" t="s">
+        <v>1337</v>
+      </c>
       <c r="M1564" s="4" t="s">
         <v>2551</v>
+      </c>
+    </row>
+    <row r="1565" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1565" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1565" s="4">
+        <v>135559</v>
+      </c>
+      <c r="D1565" s="2" t="s">
+        <v>2552</v>
+      </c>
+      <c r="E1565" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1565" s="4" t="s">
+        <v>2553</v>
+      </c>
+      <c r="G1565" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1565" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1565" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1565" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1565" s="4" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="1566" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1566" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1566" s="4">
+        <v>144331</v>
+      </c>
+      <c r="D1566" s="2" t="s">
+        <v>2552</v>
+      </c>
+      <c r="E1566" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1566" s="4" t="s">
+        <v>2554</v>
+      </c>
+      <c r="G1566" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1566" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1566" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1566" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1566" s="4" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="1567" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1567" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1567" s="4">
+        <v>134281</v>
+      </c>
+      <c r="D1567" s="2" t="s">
+        <v>2552</v>
+      </c>
+      <c r="E1567" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1567" s="4" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1567" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1567" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1567" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1567" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1567" s="4" t="s">
+        <v>2418</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1309" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90D3BC6C-9816-4BF1-9CBE-F34981014D58}"/>
+  <xr:revisionPtr revIDLastSave="1335" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17C76FF5-63F3-4483-9CFF-836CBCB01244}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1533</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1567</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14189" uniqueCount="2556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14208" uniqueCount="2559">
   <si>
     <t>ID</t>
   </si>
@@ -7952,6 +7952,15 @@
   </si>
   <si>
     <t xml:space="preserve">prestador de serviço não compareceu </t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>ninguem veio fazer a manutencao programada pela 2º vez .. alegaram imprevisto / urgencia , em outro estabelecimento</t>
+  </si>
+  <si>
+    <t>nem sempre obedece um padrão, as vezes não chegam no horario combinado o que atrapalha a rotina da casa,fazem uma manutenção rapida sem explicar direito o que é feito e nos deixam um comprovante em branco,  no passado tinham mais cuidao faziam higienização interna e externa com mais cuidado.</t>
   </si>
 </sst>
 </file>
@@ -8407,7 +8416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1567"/>
+  <dimension ref="A1:M1569"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -62181,6 +62190,9 @@
       <c r="A1408" s="4">
         <v>412</v>
       </c>
+      <c r="B1408" s="4" t="s">
+        <v>1315</v>
+      </c>
       <c r="C1408" s="4">
         <v>92325</v>
       </c>
@@ -67653,6 +67665,9 @@
       </c>
     </row>
     <row r="1552" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1552" s="4">
+        <v>573</v>
+      </c>
       <c r="B1552" s="4" t="s">
         <v>1227</v>
       </c>
@@ -67684,7 +67699,10 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="1553" spans="2:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="1553" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1553" s="4">
+        <v>574</v>
+      </c>
       <c r="B1553" s="4" t="s">
         <v>1227</v>
       </c>
@@ -67716,7 +67734,10 @@
         <v>2416</v>
       </c>
     </row>
-    <row r="1554" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1554" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1554" s="4">
+        <v>575</v>
+      </c>
       <c r="B1554" s="4" t="s">
         <v>1315</v>
       </c>
@@ -67748,7 +67769,10 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="1555" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1555" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1555" s="4">
+        <v>576</v>
+      </c>
       <c r="B1555" s="4" t="s">
         <v>1315</v>
       </c>
@@ -67780,7 +67804,10 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="1556" spans="2:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="1556" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+      <c r="A1556" s="4">
+        <v>577</v>
+      </c>
       <c r="B1556" s="4" t="s">
         <v>1315</v>
       </c>
@@ -67812,7 +67839,10 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="1557" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1557" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1557" s="4">
+        <v>578</v>
+      </c>
       <c r="B1557" s="4" t="s">
         <v>1227</v>
       </c>
@@ -67844,7 +67874,10 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="1558" spans="2:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="1558" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1558" s="4">
+        <v>579</v>
+      </c>
       <c r="B1558" s="4" t="s">
         <v>1315</v>
       </c>
@@ -67876,7 +67909,10 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="1559" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1559" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1559" s="4">
+        <v>580</v>
+      </c>
       <c r="B1559" s="4" t="s">
         <v>1227</v>
       </c>
@@ -67908,7 +67944,10 @@
         <v>2494</v>
       </c>
     </row>
-    <row r="1560" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1560" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1560" s="4">
+        <v>581</v>
+      </c>
       <c r="B1560" s="4" t="s">
         <v>49</v>
       </c>
@@ -67940,7 +67979,10 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="1561" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1561" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1561" s="4">
+        <v>582</v>
+      </c>
       <c r="B1561" s="4" t="s">
         <v>1315</v>
       </c>
@@ -67972,7 +68014,10 @@
         <v>2494</v>
       </c>
     </row>
-    <row r="1562" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1562" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1562" s="4">
+        <v>583</v>
+      </c>
       <c r="B1562" s="4" t="s">
         <v>1315</v>
       </c>
@@ -68004,7 +68049,10 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="1563" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1563" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1563" s="4">
+        <v>584</v>
+      </c>
       <c r="B1563" s="4" t="s">
         <v>49</v>
       </c>
@@ -68036,7 +68084,10 @@
         <v>2531</v>
       </c>
     </row>
-    <row r="1564" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="1564" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1564" s="4">
+        <v>585</v>
+      </c>
       <c r="B1564" s="4" t="s">
         <v>1315</v>
       </c>
@@ -68068,7 +68119,10 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="1565" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1565" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1565" s="4">
+        <v>586</v>
+      </c>
       <c r="B1565" s="4" t="s">
         <v>1227</v>
       </c>
@@ -68100,7 +68154,10 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="1566" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1566" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1566" s="4">
+        <v>587</v>
+      </c>
       <c r="B1566" s="4" t="s">
         <v>1227</v>
       </c>
@@ -68132,7 +68189,10 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="1567" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1567" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1567" s="4">
+        <v>588</v>
+      </c>
       <c r="B1567" s="4" t="s">
         <v>1315</v>
       </c>
@@ -68162,6 +68222,76 @@
       </c>
       <c r="M1567" s="4" t="s">
         <v>2418</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1568" s="4">
+        <v>589</v>
+      </c>
+      <c r="B1568" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1568" s="4">
+        <v>126474</v>
+      </c>
+      <c r="D1568" s="2" t="s">
+        <v>2556</v>
+      </c>
+      <c r="E1568" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1568" s="4" t="s">
+        <v>2557</v>
+      </c>
+      <c r="G1568" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1568" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1568" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1568" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1568" s="4" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1569" s="4">
+        <v>590</v>
+      </c>
+      <c r="B1569" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1569" s="4">
+        <v>139100</v>
+      </c>
+      <c r="D1569" s="2" t="s">
+        <v>2556</v>
+      </c>
+      <c r="E1569" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1569" s="4" t="s">
+        <v>2558</v>
+      </c>
+      <c r="G1569" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1569" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1569" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1569" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1569" s="4" t="s">
+        <v>2534</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1335" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17C76FF5-63F3-4483-9CFF-836CBCB01244}"/>
+  <xr:revisionPtr revIDLastSave="1344" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1A6D2A3-4B63-458B-BF11-C63F69D3457A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14208" uniqueCount="2559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14217" uniqueCount="2561">
   <si>
     <t>ID</t>
   </si>
@@ -7961,6 +7961,12 @@
   </si>
   <si>
     <t>nem sempre obedece um padrão, as vezes não chegam no horario combinado o que atrapalha a rotina da casa,fazem uma manutenção rapida sem explicar direito o que é feito e nos deixam um comprovante em branco,  no passado tinham mais cuidao faziam higienização interna e externa com mais cuidado.</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque nao me notificaram via WhatsApp que estava com 2 pagamentos em atraso. Troquei o cartão por perda . Trocaram meu purificador e deixaram vazando até hoje e qdo fui pedir o retorno do técnico foi qdo descobri o atraso de pagamentos e que so podia solicitar seevicos após a quitacao. Me mandaram um boleto que nao abre com meu cpf . Logo não consigo pagar e nem beber água filtrada sem falar no vazamento na cozinha . </t>
   </si>
 </sst>
 </file>
@@ -8416,7 +8422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1569"/>
+  <dimension ref="A1:M1570"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -68294,6 +68300,41 @@
         <v>2534</v>
       </c>
     </row>
+    <row r="1570" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1570" s="4">
+        <v>591</v>
+      </c>
+      <c r="B1570" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1570" s="4">
+        <v>130568</v>
+      </c>
+      <c r="D1570" s="2" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E1570" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1570" s="4" t="s">
+        <v>2560</v>
+      </c>
+      <c r="G1570" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H1570" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I1570" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1570" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1570" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1344" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1A6D2A3-4B63-458B-BF11-C63F69D3457A}"/>
+  <xr:revisionPtr revIDLastSave="1476" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70A0C2CF-C829-4045-9B72-C4AD9323F3C8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1567</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1570</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14217" uniqueCount="2561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14281" uniqueCount="2570">
   <si>
     <t>ID</t>
   </si>
@@ -7967,6 +7967,34 @@
   </si>
   <si>
     <t xml:space="preserve">Porque nao me notificaram via WhatsApp que estava com 2 pagamentos em atraso. Troquei o cartão por perda . Trocaram meu purificador e deixaram vazando até hoje e qdo fui pedir o retorno do técnico foi qdo descobri o atraso de pagamentos e que so podia solicitar seevicos após a quitacao. Me mandaram um boleto que nao abre com meu cpf . Logo não consigo pagar e nem beber água filtrada sem falar no vazamento na cozinha . </t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Só tivemos 1 manutenção até agora. Ano passado </t>
+  </si>
+  <si>
+    <t>Falta de pessoalidade e situações que não acontecem...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eu estava no processo de mudança tudo muito corrido e técnico veio instalar o purificador no meu novo endereço porém ele instalou o purificador em um local impróprio que está atrapalhando toda a logística da casa , e na hora não observei pois eu estava no corre corre da mudança. </t>
+  </si>
+  <si>
+    <t>Depois que foi transferido para a Culligan o serviço ficou pessimo. Minha manutenção estava, primeiramente, angendada para o dia 03/09 e não apareceu ninguem. Foi reagendada para 15/09 e também o tecnico não compareceu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existe muita demora no atendimento presencial dos técnicos. </t>
+  </si>
+  <si>
+    <t>02 visitas técnicas sem nenhuma solução.</t>
+  </si>
+  <si>
+    <t>Pessimo!!!! Marcaram 3 vez e nao vieram</t>
+  </si>
+  <si>
+    <t>Sem compromissos nas visitas agendadas.
+Não cumprem as datas.</t>
   </si>
 </sst>
 </file>
@@ -8422,7 +8450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1570"/>
+  <dimension ref="A1:M1578"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -67164,10 +67192,10 @@
         <v>1654</v>
       </c>
       <c r="G1538" s="4" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H1538" s="4" t="s">
-        <v>40</v>
+        <v>1435</v>
       </c>
       <c r="I1538" s="4" t="s">
         <v>1308</v>
@@ -68333,6 +68361,262 @@
       </c>
       <c r="M1570" s="4" t="s">
         <v>2494</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1571" s="4">
+        <v>592</v>
+      </c>
+      <c r="B1571" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1571" s="4">
+        <v>133394</v>
+      </c>
+      <c r="D1571" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1571" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1571" s="4" t="s">
+        <v>2562</v>
+      </c>
+      <c r="G1571" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1571" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="J1571" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1571" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1572" s="4">
+        <v>593</v>
+      </c>
+      <c r="B1572" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1572" s="4">
+        <v>141810</v>
+      </c>
+      <c r="D1572" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1572" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1572" s="4" t="s">
+        <v>2563</v>
+      </c>
+      <c r="G1572" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1572" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1572" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1572" s="4" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1573" s="4">
+        <v>594</v>
+      </c>
+      <c r="B1573" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1573" s="4">
+        <v>146746</v>
+      </c>
+      <c r="D1573" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1573" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1573" s="4" t="s">
+        <v>2564</v>
+      </c>
+      <c r="G1573" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1573" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1573" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1573" s="4" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1574" s="4">
+        <v>595</v>
+      </c>
+      <c r="B1574" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1574" s="4">
+        <v>139315</v>
+      </c>
+      <c r="D1574" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1574" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1574" s="4" t="s">
+        <v>2565</v>
+      </c>
+      <c r="G1574" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1574" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="J1574" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1574" s="4" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1575" s="4">
+        <v>596</v>
+      </c>
+      <c r="B1575" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1575" s="4">
+        <v>140718</v>
+      </c>
+      <c r="D1575" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1575" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1575" s="4" t="s">
+        <v>2566</v>
+      </c>
+      <c r="G1575" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1575" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1575" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1575" s="4" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1576" s="4">
+        <v>597</v>
+      </c>
+      <c r="B1576" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1576" s="4">
+        <v>145518</v>
+      </c>
+      <c r="D1576" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1576" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1576" s="4" t="s">
+        <v>2567</v>
+      </c>
+      <c r="G1576" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1576" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1576" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M1576" s="4" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1577" s="4">
+        <v>598</v>
+      </c>
+      <c r="B1577" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1577" s="4">
+        <v>146533</v>
+      </c>
+      <c r="D1577" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1577" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1577" s="4" t="s">
+        <v>2568</v>
+      </c>
+      <c r="G1577" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1577" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="J1577" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1577" s="4" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1578" s="4">
+        <v>599</v>
+      </c>
+      <c r="B1578" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1578" s="4">
+        <v>135603</v>
+      </c>
+      <c r="D1578" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1578" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1578" s="5" t="s">
+        <v>2569</v>
+      </c>
+      <c r="G1578" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1578" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="J1578" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1578" s="4" t="s">
+        <v>2531</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1476" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70A0C2CF-C829-4045-9B72-C4AD9323F3C8}"/>
+  <xr:revisionPtr revIDLastSave="1491" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68BCEA38-1491-48A7-966E-0733E5EEA57F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14281" uniqueCount="2570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14307" uniqueCount="2573">
   <si>
     <t>ID</t>
   </si>
@@ -7995,6 +7995,15 @@
   <si>
     <t>Sem compromissos nas visitas agendadas.
 Não cumprem as datas.</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>DEMOROU 2 MESES PARA SER EFETUADA A TROCA DO FILTRO QUE JA PAROU DE FUNCIONAR 3X E QUANDO O TECNICO VEIO FAZER A TROCA O FILTRO  QUE DEVERIA SER NOVO QUEBRADO. MAS ELE SÓ VIU APÓS INSTALAR. COMO MEU FILTRO ANTIGO FICA SOBRE UM SUPORTE DE PAREDE ELE RECOLOCOU ENTÃO O FILTRO ANTIGO SEM O PREDER, DE QUALQUER JEITO E TODO TORTO CORRENDO O RISCO DE QUEDA. FICOU DE VOLTAR AQUI NO DIA SEGUINTE COM OUTRO FILTRO E NÃO VEIO. ESTOU BEM INSATISFEITA E NÃO ACEITO TEREM LARGADO MEU FILTRO ANTIGO DESSA MANEIRA, PODENDO CAUSAR UM ACIDENTE.</t>
+  </si>
+  <si>
+    <t>Pela dificuldade que tive na solução do problema. Se têm acesso ao histórico poderão verificar. O problema do meu aparelho foi solucionado, mas em seguida notei um superaquecimento na parte superior. Não consegui falar para tentar uma solução. Estou com receio de mantê-lo ligado e causar um dano maior. Nada a reclamar do atendimento técnico.</t>
   </si>
 </sst>
 </file>
@@ -8450,7 +8459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1578"/>
+  <dimension ref="A1:M1580"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -68388,6 +68397,9 @@
       <c r="H1571" s="4" t="s">
         <v>948</v>
       </c>
+      <c r="I1571" s="4" t="s">
+        <v>1308</v>
+      </c>
       <c r="J1571" s="4" t="s">
         <v>1338</v>
       </c>
@@ -68420,6 +68432,9 @@
       <c r="H1572" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="I1572" s="4" t="s">
+        <v>1308</v>
+      </c>
       <c r="J1572" s="4" t="s">
         <v>1338</v>
       </c>
@@ -68452,6 +68467,9 @@
       <c r="H1573" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="I1573" s="4" t="s">
+        <v>1308</v>
+      </c>
       <c r="J1573" s="4" t="s">
         <v>1337</v>
       </c>
@@ -68484,6 +68502,9 @@
       <c r="H1574" s="4" t="s">
         <v>948</v>
       </c>
+      <c r="I1574" s="4" t="s">
+        <v>1308</v>
+      </c>
       <c r="J1574" s="4" t="s">
         <v>1337</v>
       </c>
@@ -68516,6 +68537,9 @@
       <c r="H1575" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="I1575" s="4" t="s">
+        <v>1308</v>
+      </c>
       <c r="J1575" s="4" t="s">
         <v>1337</v>
       </c>
@@ -68548,6 +68572,9 @@
       <c r="H1576" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="I1576" s="4" t="s">
+        <v>1308</v>
+      </c>
       <c r="J1576" s="4" t="s">
         <v>1339</v>
       </c>
@@ -68580,6 +68607,9 @@
       <c r="H1577" s="4" t="s">
         <v>948</v>
       </c>
+      <c r="I1577" s="4" t="s">
+        <v>1308</v>
+      </c>
       <c r="J1577" s="4" t="s">
         <v>1337</v>
       </c>
@@ -68612,11 +68642,84 @@
       <c r="H1578" s="4" t="s">
         <v>948</v>
       </c>
+      <c r="I1578" s="4" t="s">
+        <v>1308</v>
+      </c>
       <c r="J1578" s="4" t="s">
         <v>1337</v>
       </c>
       <c r="M1578" s="4" t="s">
         <v>2531</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1579" s="4">
+        <v>600</v>
+      </c>
+      <c r="B1579" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1579" s="4">
+        <v>146697</v>
+      </c>
+      <c r="D1579" s="2" t="s">
+        <v>2570</v>
+      </c>
+      <c r="E1579" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1579" s="4" t="s">
+        <v>2571</v>
+      </c>
+      <c r="G1579" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1579" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1579" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1579" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1579" s="4" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1580" s="4">
+        <v>601</v>
+      </c>
+      <c r="B1580" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1580" s="4">
+        <v>147829</v>
+      </c>
+      <c r="D1580" s="2" t="s">
+        <v>2570</v>
+      </c>
+      <c r="E1580" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1580" s="4" t="s">
+        <v>2572</v>
+      </c>
+      <c r="G1580" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1580" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1580" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1580" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1580" s="4" t="s">
+        <v>2490</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1491" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68BCEA38-1491-48A7-966E-0733E5EEA57F}"/>
+  <xr:revisionPtr revIDLastSave="1501" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A1709E1-82E1-4715-9E0A-003860678BBE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1570</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14307" uniqueCount="2573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14334" uniqueCount="2578">
   <si>
     <t>ID</t>
   </si>
@@ -8004,6 +8004,23 @@
   </si>
   <si>
     <t>Pela dificuldade que tive na solução do problema. Se têm acesso ao histórico poderão verificar. O problema do meu aparelho foi solucionado, mas em seguida notei um superaquecimento na parte superior. Não consegui falar para tentar uma solução. Estou com receio de mantê-lo ligado e causar um dano maior. Nada a reclamar do atendimento técnico.</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>24/09/2026</t>
+  </si>
+  <si>
+    <t>O atendimento dos técnicos é sempre muito bom, porém o atendimento ao cliente deixa a desejar, sou cliente ha 20 ou mais anos e no mês de Agosto tive pedido de troca de elemento filtrante negado devido a uma fatura do mês de Abril acredito,nunca fui cobrado , so soube quando liguei para pedir a substituição do elemento filtrante,  um total descaso com um cliente antigo,  não vou dar um golpe de uma mensalidade na Brastemp ! E a resposta será que o sistema não permite! Ridiculo!!</t>
+  </si>
+  <si>
+    <t>O técnico mudou o purificador antes da data combinada gerando transtornos para minha família. Adicionalmente, não instalou o suporte de parede como solicitei. Em outras palavras, fez o que deu na telha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOI FEITO MANUTENÇÃO PERIODICA DOS BEBEDOUROS DE AGUA, DIA 18/09/26, APOS ESTA MANUTENÇÃO FICOU SAINDO POUCA  AGUA E NÃO GELANDO. FIZ UM NOVO CHAMADO QUE SERIA DIA 24/09 NO PERIODO DA TARDE, MAS NO DIA 23/09 PELA MANHA VEIO UM TECNICO CHAMADO BRUNO, PEDIMOS A SENHA, ELE NÃO SOUBE INFORMAR E AINDA FOI MUITO MAL EDUCADO COM A GENTE, DIZENDO QUE ENTÃO IRIA EMBORA, ENTÃO FALAMOS PARA ELE IR EMBORA, QUESTÃO DE SEGURANÇA. DEPOIS ENTREI EM CONTATO COM O ATENDIMENTO E TIVE QUE CANCELAR A VISITA DO DIA 24/09, POIS A ATENTENDE NAIRA NÃO TINHA CADASTRADO A SENHA, AGORA VOU TER QUE ENTRAR NOVAMENTE EM CONTATO, PARA AGENDAR UMA NOVO VISITA.
+RESUMINDO FUNCIONARIOS OU TERCEIRIZADOS DESPREPARADOS,
+</t>
   </si>
 </sst>
 </file>
@@ -8459,7 +8476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1580"/>
+  <dimension ref="A1:M1583"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -68722,6 +68739,102 @@
         <v>2490</v>
       </c>
     </row>
+    <row r="1581" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1581" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1581" s="4">
+        <v>146253</v>
+      </c>
+      <c r="D1581" s="2" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E1581" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1581" s="4" t="s">
+        <v>2575</v>
+      </c>
+      <c r="G1581" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H1581" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I1581" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1581" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1581" s="4" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1582" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1582" s="4">
+        <v>147565</v>
+      </c>
+      <c r="D1582" s="2" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E1582" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1582" s="4" t="s">
+        <v>2576</v>
+      </c>
+      <c r="G1582" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1582" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1582" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1582" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1582" s="4" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+      <c r="B1583" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1583" s="4">
+        <v>146447</v>
+      </c>
+      <c r="D1583" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E1583" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1583" s="5" t="s">
+        <v>2577</v>
+      </c>
+      <c r="G1583" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1583" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1583" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1583" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1583" s="4" t="s">
+        <v>2517</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1501" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A1709E1-82E1-4715-9E0A-003860678BBE}"/>
+  <xr:revisionPtr revIDLastSave="1518" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF8FCEF0-86EA-45D3-947B-B74BDF9E5ECC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1570</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14334" uniqueCount="2578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14370" uniqueCount="2584">
   <si>
     <t>ID</t>
   </si>
@@ -8021,6 +8021,24 @@
     <t xml:space="preserve">FOI FEITO MANUTENÇÃO PERIODICA DOS BEBEDOUROS DE AGUA, DIA 18/09/26, APOS ESTA MANUTENÇÃO FICOU SAINDO POUCA  AGUA E NÃO GELANDO. FIZ UM NOVO CHAMADO QUE SERIA DIA 24/09 NO PERIODO DA TARDE, MAS NO DIA 23/09 PELA MANHA VEIO UM TECNICO CHAMADO BRUNO, PEDIMOS A SENHA, ELE NÃO SOUBE INFORMAR E AINDA FOI MUITO MAL EDUCADO COM A GENTE, DIZENDO QUE ENTÃO IRIA EMBORA, ENTÃO FALAMOS PARA ELE IR EMBORA, QUESTÃO DE SEGURANÇA. DEPOIS ENTREI EM CONTATO COM O ATENDIMENTO E TIVE QUE CANCELAR A VISITA DO DIA 24/09, POIS A ATENTENDE NAIRA NÃO TINHA CADASTRADO A SENHA, AGORA VOU TER QUE ENTRAR NOVAMENTE EM CONTATO, PARA AGENDAR UMA NOVO VISITA.
 RESUMINDO FUNCIONARIOS OU TERCEIRIZADOS DESPREPARADOS,
 </t>
+  </si>
+  <si>
+    <t>O preço pago mensalmente é inviável, em um ano dar pra comprar um bom filtro, sem pagar mensalidade. Pensando seriamente em cancelar …</t>
+  </si>
+  <si>
+    <t>Extrema morosidade no atendimento referente a instalação de novos filtros.</t>
+  </si>
+  <si>
+    <t>Péssimo atendimento, so via telefone pra agendar visita tecnica, marcam um dia e depois mandam um e-mail com outra data nada a ver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pq me faz perder meio dia para aguardar a chegada do técnico.  Esse agendamento tem de ser em um intervalo menor, talvez de 2 em 2 horas para não fazer o cliente ficar a disposição da visita , e avaliar a troca do aparelho por um concorrente que não o faça perder tanto tempo </t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>Aquisição</t>
   </si>
 </sst>
 </file>
@@ -8476,7 +8494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1583"/>
+  <dimension ref="A1:M1587"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -68740,6 +68758,9 @@
       </c>
     </row>
     <row r="1581" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1581" s="4">
+        <v>602</v>
+      </c>
       <c r="B1581" s="4" t="s">
         <v>1227</v>
       </c>
@@ -68772,6 +68793,9 @@
       </c>
     </row>
     <row r="1582" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1582" s="4">
+        <v>603</v>
+      </c>
       <c r="B1582" s="4" t="s">
         <v>1227</v>
       </c>
@@ -68804,6 +68828,9 @@
       </c>
     </row>
     <row r="1583" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+      <c r="A1583" s="4">
+        <v>604</v>
+      </c>
       <c r="B1583" s="4" t="s">
         <v>1315</v>
       </c>
@@ -68833,6 +68860,146 @@
       </c>
       <c r="M1583" s="4" t="s">
         <v>2517</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1584" s="4">
+        <v>605</v>
+      </c>
+      <c r="B1584" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1584" s="4">
+        <v>147640</v>
+      </c>
+      <c r="D1584" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E1584" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1584" s="4" t="s">
+        <v>2578</v>
+      </c>
+      <c r="G1584" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1584" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1584" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1584" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1584" s="4" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1585" s="4">
+        <v>606</v>
+      </c>
+      <c r="B1585" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1585" s="4">
+        <v>134800</v>
+      </c>
+      <c r="D1585" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E1585" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1585" s="4" t="s">
+        <v>2579</v>
+      </c>
+      <c r="G1585" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1585" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="I1585" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1585" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M1585" s="4" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1586" s="4">
+        <v>607</v>
+      </c>
+      <c r="B1586" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1586" s="4">
+        <v>149594</v>
+      </c>
+      <c r="D1586" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E1586" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1586" s="4" t="s">
+        <v>2580</v>
+      </c>
+      <c r="G1586" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1586" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1586" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1586" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M1586" s="4" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1587" s="4">
+        <v>608</v>
+      </c>
+      <c r="B1587" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1587" s="4">
+        <v>139831</v>
+      </c>
+      <c r="D1587" s="2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="E1587" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1587" s="4" t="s">
+        <v>2581</v>
+      </c>
+      <c r="G1587" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1587" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1587" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1587" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1587" s="4" t="s">
+        <v>2452</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1518" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF8FCEF0-86EA-45D3-947B-B74BDF9E5ECC}"/>
+  <xr:revisionPtr revIDLastSave="1535" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D11FE8E7-6BEA-451C-9552-DACDBDE73AF2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14370" uniqueCount="2584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14415" uniqueCount="2591">
   <si>
     <t>ID</t>
   </si>
@@ -8039,6 +8039,29 @@
   </si>
   <si>
     <t>Aquisição</t>
+  </si>
+  <si>
+    <t>26/09/2026</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalação com aspecto de favela, área que nenhuma pessoa gostaria ou deveria viver mas que a realidade impõe infelizmente às pessoas menos favorecidas. 
+Pedido ao instalador para modificar, disse que não faria. Como não assinamos a OS, se foi assinada, não é nossa assinatura. 
+Péssimo, deplorável. Jamais recomendável. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demora de 20 dias para primeira data de agendamento, culligan faltou e nao deu satisfação. Tentei atendimento e fiquei sem nenhuma resposta. Vcs tem 3 meses u 4 WhatsApp automatizados q funcionam muito mal e sem opção de atendente. Finalmente vcs entraram em contato p nova data sem nem pedir desculpas. Péssima experiência, mas produto é bom e por isso mantive contrato. Mas ja estou preocupado quando precisar de algum serviço </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não recebi nem manutenção esse mês </t>
+  </si>
+  <si>
+    <t>Os instaladores necessitam ( com urgência) passar por reciclagem sobre atendimento ao cliente</t>
+  </si>
+  <si>
+    <t>Desorganização para atendimento remoto. Sem pós venda não tem como manter qualidade</t>
   </si>
 </sst>
 </file>
@@ -8494,7 +8517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1587"/>
+  <dimension ref="A1:M1592"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -8507,8 +8530,8 @@
     <col min="8" max="8" width="28" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5703125" style="4" customWidth="1"/>
     <col min="10" max="10" width="18.140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="30" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="30" style="4" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" style="4" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="36.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="4"/>
   </cols>
@@ -69002,6 +69025,181 @@
         <v>2452</v>
       </c>
     </row>
+    <row r="1588" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1588" s="4">
+        <v>609</v>
+      </c>
+      <c r="B1588" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1588" s="4">
+        <v>143048</v>
+      </c>
+      <c r="D1588" s="2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="E1588" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1588" s="5" t="s">
+        <v>2586</v>
+      </c>
+      <c r="G1588" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1588" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1588" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1588" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1588" s="4" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1589" s="4">
+        <v>610</v>
+      </c>
+      <c r="B1589" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1589" s="4">
+        <v>148758</v>
+      </c>
+      <c r="D1589" s="2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="E1589" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1589" s="4" t="s">
+        <v>2587</v>
+      </c>
+      <c r="G1589" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1589" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1589" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1589" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1589" s="4" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1590" s="4">
+        <v>611</v>
+      </c>
+      <c r="B1590" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1590" s="4">
+        <v>149512</v>
+      </c>
+      <c r="D1590" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="E1590" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1590" s="4" t="s">
+        <v>2588</v>
+      </c>
+      <c r="G1590" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1590" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1590" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1590" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1590" s="4" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1591" s="4">
+        <v>612</v>
+      </c>
+      <c r="B1591" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1591" s="4">
+        <v>143798</v>
+      </c>
+      <c r="D1591" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="E1591" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1591" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="G1591" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1591" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1591" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1591" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1591" s="4" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1592" s="4">
+        <v>613</v>
+      </c>
+      <c r="B1592" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1592" s="4">
+        <v>149689</v>
+      </c>
+      <c r="D1592" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="E1592" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1592" s="4" t="s">
+        <v>2590</v>
+      </c>
+      <c r="G1592" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1592" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1592" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1592" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1592" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1535" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D11FE8E7-6BEA-451C-9552-DACDBDE73AF2}"/>
+  <xr:revisionPtr revIDLastSave="1554" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{699D063B-C65E-480A-80A8-D85194123DB8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14415" uniqueCount="2591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14460" uniqueCount="2597">
   <si>
     <t>ID</t>
   </si>
@@ -8062,6 +8062,25 @@
   </si>
   <si>
     <t>Desorganização para atendimento remoto. Sem pós venda não tem como manter qualidade</t>
+  </si>
+  <si>
+    <t>29/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tenho um contrato com filtro de agua em debito automatico! pararam as cobranças eu liguei varias vezes mais sem resultado. agora vcs resolvem cobrar tudo de 1 só vez e pior fiquei meses sem manutenção da onde vem isso???
+</t>
+  </si>
+  <si>
+    <t>Demora no atendimento, e demora para responder os e-mails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiquei muito tempo com filtro parado por falta de técnicos na minha região . Agora , após a troca do filtro, gostaria de começar a pagar novamente mas não consigo nenhum contato com a Brastemp. Tudo robotizado. </t>
+  </si>
+  <si>
+    <t>Pela segunda vez o técnico não apareceu!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou aguadando a troca do aparelho , e nada ,já estou sem agua gelada a 20 ou mais </t>
   </si>
 </sst>
 </file>
@@ -8517,7 +8536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1592"/>
+  <dimension ref="A1:M1597"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -69200,6 +69219,181 @@
         <v>2494</v>
       </c>
     </row>
+    <row r="1593" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1593" s="4">
+        <v>614</v>
+      </c>
+      <c r="B1593" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1593" s="4">
+        <v>143265</v>
+      </c>
+      <c r="D1593" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="E1593" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1593" s="5" t="s">
+        <v>2592</v>
+      </c>
+      <c r="G1593" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H1593" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I1593" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1593" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1593" s="4" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1594" s="4">
+        <v>615</v>
+      </c>
+      <c r="B1594" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1594" s="4">
+        <v>146263</v>
+      </c>
+      <c r="D1594" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="E1594" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1594" s="4" t="s">
+        <v>2593</v>
+      </c>
+      <c r="G1594" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1594" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1594" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1594" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1594" s="4" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1595" s="4">
+        <v>616</v>
+      </c>
+      <c r="B1595" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1595" s="4">
+        <v>123906</v>
+      </c>
+      <c r="D1595" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="E1595" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1595" s="4" t="s">
+        <v>2594</v>
+      </c>
+      <c r="G1595" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1595" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1595" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1595" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1595" s="4" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1596" s="4">
+        <v>617</v>
+      </c>
+      <c r="B1596" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1596" s="4">
+        <v>152889</v>
+      </c>
+      <c r="D1596" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="E1596" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1596" s="4" t="s">
+        <v>2595</v>
+      </c>
+      <c r="G1596" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1596" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1596" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1596" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1596" s="4" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1597" s="4">
+        <v>618</v>
+      </c>
+      <c r="B1597" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1597" s="4">
+        <v>146674</v>
+      </c>
+      <c r="D1597" s="2" t="s">
+        <v>2591</v>
+      </c>
+      <c r="E1597" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1597" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="G1597" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1597" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1597" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1597" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1597" s="4" t="s">
+        <v>2416</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1554" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{699D063B-C65E-480A-80A8-D85194123DB8}"/>
+  <xr:revisionPtr revIDLastSave="1565" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{843F0FF0-8958-4349-836F-3761DA2EF825}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14460" uniqueCount="2597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14468" uniqueCount="2598">
   <si>
     <t>ID</t>
   </si>
@@ -8081,6 +8081,9 @@
   </si>
   <si>
     <t xml:space="preserve">Estou aguadando a troca do aparelho , e nada ,já estou sem agua gelada a 20 ou mais </t>
+  </si>
+  <si>
+    <t>Manutenção péssima...desde o agendamento ao atendimento...</t>
   </si>
 </sst>
 </file>
@@ -8536,7 +8539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1597"/>
+  <dimension ref="A1:M1598"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -69394,6 +69397,38 @@
         <v>2416</v>
       </c>
     </row>
+    <row r="1598" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1598" s="4">
+        <v>619</v>
+      </c>
+      <c r="B1598" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1598" s="4">
+        <v>153041</v>
+      </c>
+      <c r="D1598" s="2" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F1598" s="4" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G1598" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1598" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1598" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1598" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1598" s="4" t="s">
+        <v>2416</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1565" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{843F0FF0-8958-4349-836F-3761DA2EF825}"/>
+  <xr:revisionPtr revIDLastSave="1580" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{867868CF-50ED-4178-A3BB-C643B59A8292}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14468" uniqueCount="2598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14496" uniqueCount="2602">
   <si>
     <t>ID</t>
   </si>
@@ -8084,6 +8084,19 @@
   </si>
   <si>
     <t>Manutenção péssima...desde o agendamento ao atendimento...</t>
+  </si>
+  <si>
+    <t>30/09/2026</t>
+  </si>
+  <si>
+    <t>Dificuldade no agendamento, empresa mal preparada para atender no agendamento, perderam solicitação de reparo ou troca realizada em março de 2026, desde então meu equipamento apresentando problemas. Para agenmdar agora foi muito vomplicado e difícil,poucas datas e desprepara nos atendentes. Estou seriamente disposto a cancelar meinha assinatura.</t>
+  </si>
+  <si>
+    <t>Durante o processo de vendas uma das perguntas que fiz expressamente é se todas as ferragens necessárias para a fixação em parede estariam incluídas na instalação e a resposta fio que sim. 
+No dia marcado para a instalação, que seria entre 8h e 13h. O instalador apareceu aos 48 do segundo tempo (13h10 aproximadamente) e informou que a Brastemp NÃO fornece/tem suporte para fixar em parede o filtro adquirido.</t>
+  </si>
+  <si>
+    <t>O serviço de agendamento e suporte ao cliente é muito problemático.</t>
   </si>
 </sst>
 </file>
@@ -8539,7 +8552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1598"/>
+  <dimension ref="A1:M1601"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -69410,6 +69423,9 @@
       <c r="D1598" s="2" t="s">
         <v>2591</v>
       </c>
+      <c r="E1598" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F1598" s="4" t="s">
         <v>2597</v>
       </c>
@@ -69427,6 +69443,111 @@
       </c>
       <c r="M1598" s="4" t="s">
         <v>2416</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1599" s="4">
+        <v>620</v>
+      </c>
+      <c r="B1599" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1599" s="4">
+        <v>153310</v>
+      </c>
+      <c r="D1599" s="2" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E1599" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1599" s="4" t="s">
+        <v>2599</v>
+      </c>
+      <c r="G1599" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1599" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1599" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1599" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1599" s="4" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+      <c r="A1600" s="4">
+        <v>621</v>
+      </c>
+      <c r="B1600" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1600" s="4">
+        <v>149511</v>
+      </c>
+      <c r="D1600" s="2" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E1600" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1600" s="5" t="s">
+        <v>2600</v>
+      </c>
+      <c r="G1600" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1600" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1600" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1600" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1600" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1601" s="4">
+        <v>622</v>
+      </c>
+      <c r="B1601" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1601" s="4">
+        <v>140740</v>
+      </c>
+      <c r="D1601" s="2" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E1601" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1601" s="4" t="s">
+        <v>2601</v>
+      </c>
+      <c r="G1601" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1601" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1601" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1601" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1601" s="4" t="s">
+        <v>2494</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1580" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{867868CF-50ED-4178-A3BB-C643B59A8292}"/>
+  <xr:revisionPtr revIDLastSave="1597" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B180481A-C1CB-42A9-A656-43A982078139}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14496" uniqueCount="2602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14532" uniqueCount="2608">
   <si>
     <t>ID</t>
   </si>
@@ -8097,6 +8097,28 @@
   </si>
   <si>
     <t>O serviço de agendamento e suporte ao cliente é muito problemático.</t>
+  </si>
+  <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqui só dei 5 pelo bom produto. Mas bom produto com serviço porco, vale pouco. Marquei a manutenção preventiva dia 21. Fiquei 5h esperando, visto que vocês não dão um horário e sim um periodo. Me deram o cano sem nenhuma explicação. Remarquei para dia 1/10 periodo tarde. Me programei para isso. Porem vieram pela manhã. Que tipo de atendimento é esse? Como vcs pioraram tanto? E o atendimento online é feito por pessoas totalmente despreparadas. </t>
+  </si>
+  <si>
+    <t>Marcaram à tarde, mas vieram pela manhã. Por acaso, era o dia da nossa diarista. Caso contrário não teria dado certo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por incrível que pareça, agendei 4 (quatro) vezes no horário das 13:00 às 18:00 horas 
+Nenhuma vez cumpriram o horário agendado 
+Na quarta e última visita por uma coincidência terrível, o técnico de vcs chegou às 11:00 horas e eu estava em casa. A coordenação de vcs não estão em sintonia com os clientes.
+Meus parabéns equipe bem competente 
+Nota 3 pela marca Brastemp </t>
+  </si>
+  <si>
+    <t>Ficou faltando uma informação, avisei o atendente que de vez em quando na liberação de agua com gas não libera instantâneo, o painel fica acesso girando e tenho que esperar as vezes vários minutos para conseguir liberar agua com gas. Ele passou essa dúvida para central mais não teve retorno, será que não precisar trocar o aparelho?</t>
   </si>
 </sst>
 </file>
@@ -8552,7 +8574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1601"/>
+  <dimension ref="A1:M1605"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -69550,6 +69572,146 @@
         <v>2494</v>
       </c>
     </row>
+    <row r="1602" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1602" s="4">
+        <v>623</v>
+      </c>
+      <c r="B1602" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1602" s="4">
+        <v>153268</v>
+      </c>
+      <c r="D1602" s="2" t="s">
+        <v>2602</v>
+      </c>
+      <c r="E1602" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1602" s="4" t="s">
+        <v>2604</v>
+      </c>
+      <c r="G1602" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1602" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1602" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1602" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1602" s="4" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1603" s="4">
+        <v>624</v>
+      </c>
+      <c r="B1603" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1603" s="4">
+        <v>139312</v>
+      </c>
+      <c r="D1603" s="2" t="s">
+        <v>2602</v>
+      </c>
+      <c r="E1603" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1603" s="4" t="s">
+        <v>2605</v>
+      </c>
+      <c r="G1603" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1603" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1603" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1603" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1603" s="4" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+      <c r="A1604" s="4">
+        <v>625</v>
+      </c>
+      <c r="B1604" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1604" s="4">
+        <v>154874</v>
+      </c>
+      <c r="D1604" s="2" t="s">
+        <v>2603</v>
+      </c>
+      <c r="E1604" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1604" s="5" t="s">
+        <v>2606</v>
+      </c>
+      <c r="G1604" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1604" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1604" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1604" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1604" s="4" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1605" s="4">
+        <v>626</v>
+      </c>
+      <c r="B1605" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1605" s="4">
+        <v>154819</v>
+      </c>
+      <c r="D1605" s="2" t="s">
+        <v>2603</v>
+      </c>
+      <c r="E1605" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1605" s="4" t="s">
+        <v>2607</v>
+      </c>
+      <c r="G1605" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1605" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1605" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1605" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1605" s="4" t="s">
+        <v>2452</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1597" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B180481A-C1CB-42A9-A656-43A982078139}"/>
+  <xr:revisionPtr revIDLastSave="1627" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE007699-816D-475C-A825-FAD43DEE9A4E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14532" uniqueCount="2608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14602" uniqueCount="2625">
   <si>
     <t>ID</t>
   </si>
@@ -8119,6 +8119,61 @@
   </si>
   <si>
     <t>Ficou faltando uma informação, avisei o atendente que de vez em quando na liberação de agua com gas não libera instantâneo, o painel fica acesso girando e tenho que esperar as vezes vários minutos para conseguir liberar agua com gas. Ele passou essa dúvida para central mais não teve retorno, será que não precisar trocar o aparelho?</t>
+  </si>
+  <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
+    <t>04/10/2026</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque na INSEGURANÇA em que vivemos,vocês DEIXARAM de continuar com o esquema de segurança que a Brastemp fazia,isto é enviava aos clientes antes do técnico chegar ,código da visita,nome e RG do funcionário que ia fazer o atendimento para ele .ser identificado por nós ,para poder ser feita sua identificação .Isso e’ feito pela Claro,Vivo e outras prestadoras de Serviço .
+Isso é muito simples de vocês implantarem .E’ só fazerem uma pequena inclusão no programa eletrônico de atendimento ao cliente .
+Quanto ao técnico ,seu trabalho foi excelente.
+Ah ,deixem conosco uma 2. Via do recibo do atendimento também.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque vcs priorizam o atendimento eletrônico em detrimento do pessoal, além de u ser há anos cliente e ter dois aparelhos em locais diferentes, pedi para um terceiro, mas, pedi um preço melhor , que me foi negado sem nenhuma atenção. </t>
+  </si>
+  <si>
+    <t>Só fui atendida como desejava depois de muito stress e visita que não aconteceu,  sem explicações. Quando desisti de me aborrecer, marcaram visita e por incrível que pareça,  fui atendida satisfatoriamente.</t>
+  </si>
+  <si>
+    <t>Marcou e não compareceu, depois marcou num horário e veio no outro.</t>
+  </si>
+  <si>
+    <t>Não vieram pela manhã como programado, a técnica não repos a etiqueta com as informações da última troca e contatos telefônico, deixou a copa toda respingada de água</t>
+  </si>
+  <si>
+    <t>Porque além de não resolver o problema inicial, ainda gerou estresse na hora de marcar nova data com o técnico.</t>
+  </si>
+  <si>
+    <t>FRQ LONDRINA PR R03</t>
+  </si>
+  <si>
+    <t>visita agendada não foi cumprida</t>
+  </si>
+  <si>
+    <t>não enviam dados do técnico + sem 2ª via do recibo</t>
+  </si>
+  <si>
+    <t>pedi preço melhor, negado + atendimento eletrônico</t>
+  </si>
+  <si>
+    <t>visita que não aconteceu, sem explicações</t>
+  </si>
+  <si>
+    <t>marcou e não compareceu + veio em outro horário</t>
+  </si>
+  <si>
+    <t>não vieram pela manhã + sem etiqueta + respingou água</t>
+  </si>
+  <si>
+    <t>não resolveu o problema inicial + estresse para remarcar</t>
   </si>
 </sst>
 </file>
@@ -8574,7 +8629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1605"/>
+  <dimension ref="A1:M1611"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -67637,11 +67692,23 @@
       <c r="F1546" s="4" t="s">
         <v>1672</v>
       </c>
+      <c r="G1546" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1546" s="4" t="s">
+        <v>948</v>
+      </c>
       <c r="I1546" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1546" s="4" t="s">
         <v>1337</v>
+      </c>
+      <c r="K1546" s="4" t="s">
+        <v>2618</v>
+      </c>
+      <c r="L1546" s="4" t="s">
+        <v>1550</v>
       </c>
       <c r="M1546" s="4" t="s">
         <v>2449</v>
@@ -69710,6 +69777,234 @@
       </c>
       <c r="M1605" s="4" t="s">
         <v>2452</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+      <c r="B1606" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1606" s="4">
+        <v>138735</v>
+      </c>
+      <c r="D1606" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="E1606" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1606" s="5" t="s">
+        <v>2611</v>
+      </c>
+      <c r="G1606" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1606" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1606" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1606" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1606" s="4" t="s">
+        <v>2619</v>
+      </c>
+      <c r="L1606" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="M1606" s="4" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1607" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1607" s="4">
+        <v>150739</v>
+      </c>
+      <c r="D1607" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="E1607" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1607" s="4" t="s">
+        <v>2612</v>
+      </c>
+      <c r="G1607" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1607" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1607" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1607" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1607" s="4" t="s">
+        <v>2620</v>
+      </c>
+      <c r="L1607" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="M1607" s="4" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1608" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1608" s="4">
+        <v>148521</v>
+      </c>
+      <c r="D1608" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="E1608" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1608" s="4" t="s">
+        <v>2613</v>
+      </c>
+      <c r="G1608" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1608" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1608" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1608" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1608" s="4" t="s">
+        <v>2621</v>
+      </c>
+      <c r="L1608" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="M1608" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1609" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1609" s="4">
+        <v>155418</v>
+      </c>
+      <c r="D1609" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="E1609" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1609" s="4" t="s">
+        <v>2614</v>
+      </c>
+      <c r="G1609" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1609" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1609" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1609" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1609" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="L1609" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="M1609" s="4" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1610" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1610" s="4">
+        <v>152748</v>
+      </c>
+      <c r="D1610" s="2" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E1610" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1610" s="4" t="s">
+        <v>2615</v>
+      </c>
+      <c r="G1610" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1610" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1610" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1610" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1610" s="4" t="s">
+        <v>2623</v>
+      </c>
+      <c r="L1610" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="M1610" s="4" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1611" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1611" s="4">
+        <v>156293</v>
+      </c>
+      <c r="D1611" s="2" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E1611" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1611" s="4" t="s">
+        <v>2616</v>
+      </c>
+      <c r="G1611" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1611" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1611" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1611" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1611" s="4" t="s">
+        <v>2624</v>
+      </c>
+      <c r="L1611" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="M1611" s="4" t="s">
+        <v>2492</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2703" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49944A41-2514-4451-9F0C-AB35243E17F5}"/>
+  <xr:revisionPtr revIDLastSave="2716" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26A3224E-F964-4036-90E8-448D27AEF531}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16260" uniqueCount="3381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16290" uniqueCount="3387">
   <si>
     <t>ID</t>
   </si>
@@ -8111,10 +8111,6 @@
     <t>AT BAURU SP R03</t>
   </si>
   <si>
-    <t xml:space="preserve">Inicialmente, essa visita estava marcada para a semana passada. Não compareceram. Liguei na Brastemp para cancelar, insistiram e remarcaram a visita para ontem (31/09) na período da manhã. Chegaram em minha residência próximo das 16h. Eu já não estava mais em casa, por sorte meu filho mais velho estava e o recebeu. O que não era o mais indicado, pois ele não estava por dentro do ocorrido. E não era o horário agendado. 
-O técnico informou que o mau cheiro e mau gosto da água é porque a água estava parada. Não. A água ficou parada devido o mau cheiro e mau gosto. E na troca do filtro, após seis meses de uso, o filtro não foi trocado, pois o técnico na época disse não ser necessário. Enfim, estou insatisfeita e provavelmente solicitarei o cancelamento quando meu contrato vencer agora em outubro. </t>
-  </si>
-  <si>
     <t>dificil falar com vocês, quando consigo não resolvem nada</t>
   </si>
   <si>
@@ -10369,76 +10365,107 @@
     <t>agendamento e suporte problemáticos</t>
   </si>
   <si>
-    <t>não compareceram + chegaram às 16h</t>
-  </si>
-  <si>
-    <t>me deram o cano sem explicação</t>
-  </si>
-  <si>
-    <t>marcaram à tarde, vieram de manhã</t>
-  </si>
-  <si>
-    <t>água com gás não libera + sem retorno</t>
-  </si>
-  <si>
-    <t>pedi preço melhor e foi negado</t>
-  </si>
-  <si>
-    <t>marcou e não compareceu + horário</t>
-  </si>
-  <si>
-    <t>não vieram de manhã + sem etiqueta</t>
-  </si>
-  <si>
-    <t>não resolveu o problema inicial</t>
-  </si>
-  <si>
-    <t>está com gotejamento</t>
-  </si>
-  <si>
-    <t>difícil falar com vocês</t>
-  </si>
-  <si>
-    <t>muito demorado agendar + robô</t>
-  </si>
-  <si>
-    <t>não trocou o filtro + fluxo reduzido</t>
-  </si>
-  <si>
-    <t>incapacidade profissional</t>
-  </si>
-  <si>
-    <t>ninguém veio nas datas acordadas</t>
-  </si>
-  <si>
-    <t>duas visitas não aconteceram</t>
-  </si>
-  <si>
-    <t>sem comunicado de agendamento</t>
-  </si>
-  <si>
-    <t>atendimento de vocês é péssimo (R6)</t>
-  </si>
-  <si>
-    <t>mais uma vez não gela + gás</t>
-  </si>
-  <si>
     <t>horário após o informado</t>
   </si>
   <si>
-    <t>agendado 09/10, veio 06/10 sem aviso</t>
-  </si>
-  <si>
-    <t>vazando sem ferramenta p/ ajuste</t>
-  </si>
-  <si>
     <t>conta não chega + quer cancelar (fora da taxonomia: Financeiro)</t>
   </si>
   <si>
     <t>manutenção prevista desde junho não agendada</t>
   </si>
   <si>
-    <t>Neste momento o purificador de água está com um cotejamento</t>
+    <t xml:space="preserve">Por incrível que pareça, agendei 4 (quatro) vezes no horário das 13:00 às 18:00 horas 
+Nenhuma vez cumpriram o horário agendado 
+Na quarta e última visita por uma coincidência terrível, o técnico de vcs chegou às 11:00 horas e eu estava em casa. A coordenação de vcs não estão em sintonia com os clientes.
+Meus parabéns equipe bem competente 
+Nota 3 pela marca Brastemp </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque na INSEGURANÇA em que vivemos,vocês DEIXARAM de continuar com o esquema de segurança que a Brastemp fazia,isto é enviava aos clientes antes do técnico chegar ,código da visita,nome e RG do funcionário que ia fazer o atendimento para ele .ser identificado por nós ,para poder ser feita sua identificação .Isso e’ feito pela Claro,Vivo e outras prestadoras de Serviço .
+Isso é muito simples de vocês implantarem .E’ só fazerem uma pequena inclusão no programa eletrônico de atendimento ao cliente .
+Quanto ao técnico ,seu trabalho foi excelente.
+Ah ,deixem conosco uma 2. Via do recibo do atendimento também.
+</t>
+  </si>
+  <si>
+    <t>Só fui atendida como desejava depois de muito stress e visita que não aconteceu,  sem explicações. Quando desisti de me aborrecer, marcaram visita e por incrível que pareça,  fui atendida satisfatoriamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neste momento o purificador de água está com um cotejamento, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O purificador está jogando água fora do copo. Quando é acionado...
+Sobre a manutenção correu tudo bem..
+</t>
+  </si>
+  <si>
+    <t>remarcou tarde, vieram de manhã + atendimento online despreparado</t>
+  </si>
+  <si>
+    <t>marcaram à tarde, vieram pela manhã</t>
+  </si>
+  <si>
+    <t>nenhuma vez cumpriram o horário agendado</t>
+  </si>
+  <si>
+    <t>água com gás não libera instantâneo + central sem retorno</t>
+  </si>
+  <si>
+    <t>sem identificação prévia do técnico + 2ª via do recibo</t>
+  </si>
+  <si>
+    <t>pedi preço melhor, negado + atendimento eletrônico</t>
+  </si>
+  <si>
+    <t>visita que não aconteceu, sem explicações</t>
+  </si>
+  <si>
+    <t>marcou e não compareceu + veio em outro horário</t>
+  </si>
+  <si>
+    <t>não vieram pela manhã + etiqueta não reposta, copa respingada</t>
+  </si>
+  <si>
+    <t>não resolver o problema inicial + estresse para remarcar</t>
+  </si>
+  <si>
+    <t>purificador com um cotejamento (gotejamento?)</t>
+  </si>
+  <si>
+    <t>difícil falar com vocês + não resolvem nada</t>
+  </si>
+  <si>
+    <t>só conversamos com máquinas, sem soluções</t>
+  </si>
+  <si>
+    <t>jogando água fora do copo</t>
+  </si>
+  <si>
+    <t>não trocou o filtro apesar do fluxo reduzido</t>
+  </si>
+  <si>
+    <t>falta de organização e incapacidade profissional</t>
+  </si>
+  <si>
+    <t>marcaram repetidas vezes e ninguém veio</t>
+  </si>
+  <si>
+    <t>duas visitas não aconteceram + cobrança com ameaça</t>
+  </si>
+  <si>
+    <t>não recebi comunicado de agendamento + manutenção dos 3 juntos</t>
+  </si>
+  <si>
+    <t>manutenção boa, mas atendimento péssimo (R6)</t>
+  </si>
+  <si>
+    <t>aparelho novo com mesmo problema + não gela; 2 meses de espera</t>
+  </si>
+  <si>
+    <t>agendado 09/10, veio 06/10 sem aviso + sem palavra de segurança</t>
+  </si>
+  <si>
+    <t>não ajustou fluxo, estava vazando + sem ferramenta</t>
   </si>
 </sst>
 </file>
@@ -10894,7 +10921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1622"/>
+  <dimension ref="A1:M1625"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -41736,7 +41763,7 @@
         <v>1336</v>
       </c>
       <c r="K752" s="4" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="L752" s="4" t="s">
         <v>1546</v>
@@ -41777,7 +41804,7 @@
         <v>1336</v>
       </c>
       <c r="K753" s="4" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="L753" s="4" t="s">
         <v>1546</v>
@@ -41818,7 +41845,7 @@
         <v>1336</v>
       </c>
       <c r="K754" s="4" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="L754" s="4" t="s">
         <v>1546</v>
@@ -41859,7 +41886,7 @@
         <v>1336</v>
       </c>
       <c r="K755" s="4" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="L755" s="4" t="s">
         <v>1546</v>
@@ -41900,7 +41927,7 @@
         <v>1336</v>
       </c>
       <c r="K756" s="4" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="L756" s="4" t="s">
         <v>1546</v>
@@ -41982,7 +42009,7 @@
         <v>1338</v>
       </c>
       <c r="K758" s="4" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="L758" s="4" t="s">
         <v>1546</v>
@@ -42023,7 +42050,7 @@
         <v>1336</v>
       </c>
       <c r="K759" s="4" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="L759" s="4" t="s">
         <v>1546</v>
@@ -42064,7 +42091,7 @@
         <v>1336</v>
       </c>
       <c r="K760" s="4" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="L760" s="4" t="s">
         <v>1547</v>
@@ -42105,7 +42132,7 @@
         <v>1336</v>
       </c>
       <c r="K761" s="4" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="L761" s="4" t="s">
         <v>1547</v>
@@ -42146,7 +42173,7 @@
         <v>1336</v>
       </c>
       <c r="K762" s="4" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="L762" s="4" t="s">
         <v>1546</v>
@@ -42187,7 +42214,7 @@
         <v>1336</v>
       </c>
       <c r="K763" s="4" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="L763" s="4" t="s">
         <v>1547</v>
@@ -42228,7 +42255,7 @@
         <v>1336</v>
       </c>
       <c r="K764" s="4" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="L764" s="4" t="s">
         <v>1546</v>
@@ -42269,7 +42296,7 @@
         <v>1336</v>
       </c>
       <c r="K765" s="4" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="L765" s="4" t="s">
         <v>1547</v>
@@ -42310,7 +42337,7 @@
         <v>1336</v>
       </c>
       <c r="K766" s="4" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="L766" s="4" t="s">
         <v>1547</v>
@@ -42351,7 +42378,7 @@
         <v>1338</v>
       </c>
       <c r="K767" s="4" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="L767" s="4" t="s">
         <v>1546</v>
@@ -42392,7 +42419,7 @@
         <v>1336</v>
       </c>
       <c r="K768" s="4" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="L768" s="4" t="s">
         <v>1547</v>
@@ -42433,7 +42460,7 @@
         <v>1336</v>
       </c>
       <c r="K769" s="4" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="L769" s="4" t="s">
         <v>1546</v>
@@ -42474,7 +42501,7 @@
         <v>1336</v>
       </c>
       <c r="K770" s="4" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="L770" s="4" t="s">
         <v>1547</v>
@@ -42515,7 +42542,7 @@
         <v>1336</v>
       </c>
       <c r="K771" s="4" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="L771" s="4" t="s">
         <v>1546</v>
@@ -42556,7 +42583,7 @@
         <v>1336</v>
       </c>
       <c r="K772" s="4" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="L772" s="4" t="s">
         <v>1546</v>
@@ -42597,7 +42624,7 @@
         <v>1338</v>
       </c>
       <c r="K773" s="4" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="L773" s="4" t="s">
         <v>1546</v>
@@ -42638,7 +42665,7 @@
         <v>1338</v>
       </c>
       <c r="K774" s="4" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="L774" s="4" t="s">
         <v>1547</v>
@@ -42679,7 +42706,7 @@
         <v>1336</v>
       </c>
       <c r="K775" s="4" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="L775" s="4" t="s">
         <v>1547</v>
@@ -42720,7 +42747,7 @@
         <v>1338</v>
       </c>
       <c r="K776" s="4" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="L776" s="4" t="s">
         <v>1546</v>
@@ -42761,7 +42788,7 @@
         <v>1336</v>
       </c>
       <c r="K777" s="4" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="L777" s="4" t="s">
         <v>1547</v>
@@ -42802,7 +42829,7 @@
         <v>1338</v>
       </c>
       <c r="K778" s="4" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="L778" s="4" t="s">
         <v>1546</v>
@@ -42843,7 +42870,7 @@
         <v>1338</v>
       </c>
       <c r="K779" s="4" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="L779" s="4" t="s">
         <v>1546</v>
@@ -42884,7 +42911,7 @@
         <v>1336</v>
       </c>
       <c r="K780" s="4" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="L780" s="4" t="s">
         <v>1547</v>
@@ -42925,7 +42952,7 @@
         <v>1338</v>
       </c>
       <c r="K781" s="4" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="L781" s="4" t="s">
         <v>1547</v>
@@ -42966,7 +42993,7 @@
         <v>1338</v>
       </c>
       <c r="K782" s="4" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="L782" s="4" t="s">
         <v>1546</v>
@@ -43007,7 +43034,7 @@
         <v>1336</v>
       </c>
       <c r="K783" s="4" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="L783" s="4" t="s">
         <v>1546</v>
@@ -43048,7 +43075,7 @@
         <v>1336</v>
       </c>
       <c r="K784" s="4" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="L784" s="4" t="s">
         <v>1546</v>
@@ -43089,7 +43116,7 @@
         <v>1336</v>
       </c>
       <c r="K785" s="4" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="L785" s="4" t="s">
         <v>1546</v>
@@ -43130,7 +43157,7 @@
         <v>1336</v>
       </c>
       <c r="K786" s="4" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="L786" s="4" t="s">
         <v>1546</v>
@@ -43171,7 +43198,7 @@
         <v>1336</v>
       </c>
       <c r="K787" s="4" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="L787" s="4" t="s">
         <v>1546</v>
@@ -43212,7 +43239,7 @@
         <v>1336</v>
       </c>
       <c r="K788" s="4" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="L788" s="4" t="s">
         <v>1546</v>
@@ -43253,7 +43280,7 @@
         <v>1336</v>
       </c>
       <c r="K789" s="4" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="L789" s="4" t="s">
         <v>1546</v>
@@ -43294,7 +43321,7 @@
         <v>1336</v>
       </c>
       <c r="K790" s="4" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="L790" s="4" t="s">
         <v>1546</v>
@@ -43335,7 +43362,7 @@
         <v>1336</v>
       </c>
       <c r="K791" s="4" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="L791" s="4" t="s">
         <v>1547</v>
@@ -43376,7 +43403,7 @@
         <v>1336</v>
       </c>
       <c r="K792" s="4" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="L792" s="4" t="s">
         <v>1546</v>
@@ -43417,7 +43444,7 @@
         <v>1338</v>
       </c>
       <c r="K793" s="4" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="L793" s="4" t="s">
         <v>1546</v>
@@ -43458,7 +43485,7 @@
         <v>1336</v>
       </c>
       <c r="K794" s="4" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="L794" s="4" t="s">
         <v>1546</v>
@@ -43499,7 +43526,7 @@
         <v>1336</v>
       </c>
       <c r="K795" s="4" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="L795" s="4" t="s">
         <v>1546</v>
@@ -43540,7 +43567,7 @@
         <v>1338</v>
       </c>
       <c r="K796" s="4" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="L796" s="4" t="s">
         <v>1547</v>
@@ -43581,7 +43608,7 @@
         <v>1336</v>
       </c>
       <c r="K797" s="4" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="L797" s="4" t="s">
         <v>1546</v>
@@ -43622,7 +43649,7 @@
         <v>1336</v>
       </c>
       <c r="K798" s="4" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="L798" s="4" t="s">
         <v>1546</v>
@@ -43663,7 +43690,7 @@
         <v>1336</v>
       </c>
       <c r="K799" s="4" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
       <c r="L799" s="4" t="s">
         <v>1547</v>
@@ -43704,7 +43731,7 @@
         <v>1336</v>
       </c>
       <c r="K800" s="4" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="L800" s="4" t="s">
         <v>1546</v>
@@ -43745,7 +43772,7 @@
         <v>1336</v>
       </c>
       <c r="K801" s="4" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="L801" s="4" t="s">
         <v>1546</v>
@@ -43786,7 +43813,7 @@
         <v>1336</v>
       </c>
       <c r="K802" s="4" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="L802" s="4" t="s">
         <v>1546</v>
@@ -43827,7 +43854,7 @@
         <v>1338</v>
       </c>
       <c r="K803" s="4" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="L803" s="4" t="s">
         <v>1546</v>
@@ -43868,7 +43895,7 @@
         <v>1336</v>
       </c>
       <c r="K804" s="4" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="L804" s="4" t="s">
         <v>1546</v>
@@ -43909,7 +43936,7 @@
         <v>1336</v>
       </c>
       <c r="K805" s="4" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="L805" s="4" t="s">
         <v>1546</v>
@@ -43950,7 +43977,7 @@
         <v>1336</v>
       </c>
       <c r="K806" s="4" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="L806" s="4" t="s">
         <v>1546</v>
@@ -43991,7 +44018,7 @@
         <v>1336</v>
       </c>
       <c r="K807" s="4" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="L807" s="4" t="s">
         <v>1547</v>
@@ -44032,7 +44059,7 @@
         <v>1336</v>
       </c>
       <c r="K808" s="4" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="L808" s="4" t="s">
         <v>1546</v>
@@ -44073,7 +44100,7 @@
         <v>1336</v>
       </c>
       <c r="K809" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="L809" s="4" t="s">
         <v>1546</v>
@@ -44114,7 +44141,7 @@
         <v>1336</v>
       </c>
       <c r="K810" s="4" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="L810" s="4" t="s">
         <v>1546</v>
@@ -44155,7 +44182,7 @@
         <v>1338</v>
       </c>
       <c r="K811" s="4" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="L811" s="4" t="s">
         <v>1546</v>
@@ -44196,7 +44223,7 @@
         <v>1336</v>
       </c>
       <c r="K812" s="4" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="L812" s="4" t="s">
         <v>1546</v>
@@ -44237,7 +44264,7 @@
         <v>1336</v>
       </c>
       <c r="K813" s="4" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="L813" s="4" t="s">
         <v>1546</v>
@@ -44278,7 +44305,7 @@
         <v>1338</v>
       </c>
       <c r="K814" s="4" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="L814" s="4" t="s">
         <v>1546</v>
@@ -44360,7 +44387,7 @@
         <v>1338</v>
       </c>
       <c r="K816" s="4" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="L816" s="4" t="s">
         <v>1546</v>
@@ -44401,7 +44428,7 @@
         <v>1336</v>
       </c>
       <c r="K817" s="4" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="L817" s="4" t="s">
         <v>1547</v>
@@ -44442,7 +44469,7 @@
         <v>1336</v>
       </c>
       <c r="K818" s="4" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="L818" s="4" t="s">
         <v>1546</v>
@@ -44483,7 +44510,7 @@
         <v>1336</v>
       </c>
       <c r="K819" s="4" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="L819" s="4" t="s">
         <v>1546</v>
@@ -44524,7 +44551,7 @@
         <v>1338</v>
       </c>
       <c r="K820" s="4" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="L820" s="4" t="s">
         <v>1546</v>
@@ -44565,7 +44592,7 @@
         <v>1336</v>
       </c>
       <c r="K821" s="4" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="L821" s="4" t="s">
         <v>1546</v>
@@ -44606,7 +44633,7 @@
         <v>1336</v>
       </c>
       <c r="K822" s="4" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="L822" s="4" t="s">
         <v>1546</v>
@@ -44647,7 +44674,7 @@
         <v>1336</v>
       </c>
       <c r="K823" s="4" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="L823" s="4" t="s">
         <v>1546</v>
@@ -44688,7 +44715,7 @@
         <v>1338</v>
       </c>
       <c r="K824" s="4" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="L824" s="4" t="s">
         <v>1547</v>
@@ -44729,7 +44756,7 @@
         <v>1338</v>
       </c>
       <c r="K825" s="4" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="L825" s="4" t="s">
         <v>1546</v>
@@ -44770,7 +44797,7 @@
         <v>1336</v>
       </c>
       <c r="K826" s="4" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="L826" s="4" t="s">
         <v>1546</v>
@@ -44811,7 +44838,7 @@
         <v>1336</v>
       </c>
       <c r="K827" s="4" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="L827" s="4" t="s">
         <v>1546</v>
@@ -44852,7 +44879,7 @@
         <v>1336</v>
       </c>
       <c r="K828" s="4" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="L828" s="4" t="s">
         <v>1546</v>
@@ -44893,7 +44920,7 @@
         <v>1338</v>
       </c>
       <c r="K829" s="4" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="L829" s="4" t="s">
         <v>1547</v>
@@ -44934,7 +44961,7 @@
         <v>1336</v>
       </c>
       <c r="K830" s="4" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="L830" s="4" t="s">
         <v>1546</v>
@@ -44975,7 +45002,7 @@
         <v>1336</v>
       </c>
       <c r="K831" s="4" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="L831" s="4" t="s">
         <v>1546</v>
@@ -45016,7 +45043,7 @@
         <v>1336</v>
       </c>
       <c r="K832" s="4" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="L832" s="4" t="s">
         <v>1546</v>
@@ -45057,7 +45084,7 @@
         <v>1336</v>
       </c>
       <c r="K833" s="4" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="L833" s="4" t="s">
         <v>1546</v>
@@ -45098,7 +45125,7 @@
         <v>1336</v>
       </c>
       <c r="K834" s="4" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="L834" s="4" t="s">
         <v>1546</v>
@@ -45139,7 +45166,7 @@
         <v>1336</v>
       </c>
       <c r="K835" s="4" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="L835" s="4" t="s">
         <v>1546</v>
@@ -45180,7 +45207,7 @@
         <v>1336</v>
       </c>
       <c r="K836" s="4" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="L836" s="4" t="s">
         <v>1546</v>
@@ -45221,7 +45248,7 @@
         <v>1336</v>
       </c>
       <c r="K837" s="4" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="L837" s="4" t="s">
         <v>1546</v>
@@ -45262,7 +45289,7 @@
         <v>1338</v>
       </c>
       <c r="K838" s="4" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="L838" s="4" t="s">
         <v>1547</v>
@@ -45303,7 +45330,7 @@
         <v>1336</v>
       </c>
       <c r="K839" s="4" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="L839" s="4" t="s">
         <v>1546</v>
@@ -45344,7 +45371,7 @@
         <v>1336</v>
       </c>
       <c r="K840" s="4" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="L840" s="4" t="s">
         <v>1546</v>
@@ -45385,7 +45412,7 @@
         <v>1336</v>
       </c>
       <c r="K841" s="4" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="L841" s="4" t="s">
         <v>1546</v>
@@ -45426,7 +45453,7 @@
         <v>1336</v>
       </c>
       <c r="K842" s="4" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="L842" s="4" t="s">
         <v>1546</v>
@@ -45467,7 +45494,7 @@
         <v>1336</v>
       </c>
       <c r="K843" s="4" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="L843" s="4" t="s">
         <v>1546</v>
@@ -45508,7 +45535,7 @@
         <v>1336</v>
       </c>
       <c r="K844" s="4" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="L844" s="4" t="s">
         <v>1547</v>
@@ -45549,7 +45576,7 @@
         <v>1336</v>
       </c>
       <c r="K845" s="4" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="L845" s="4" t="s">
         <v>1546</v>
@@ -45590,7 +45617,7 @@
         <v>1336</v>
       </c>
       <c r="K846" s="4" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="L846" s="4" t="s">
         <v>1547</v>
@@ -45631,7 +45658,7 @@
         <v>1338</v>
       </c>
       <c r="K847" s="4" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="L847" s="4" t="s">
         <v>1547</v>
@@ -45672,7 +45699,7 @@
         <v>1336</v>
       </c>
       <c r="K848" s="4" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="L848" s="4" t="s">
         <v>1547</v>
@@ -45713,7 +45740,7 @@
         <v>1336</v>
       </c>
       <c r="K849" s="4" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
       <c r="L849" s="4" t="s">
         <v>1546</v>
@@ -45754,7 +45781,7 @@
         <v>1336</v>
       </c>
       <c r="K850" s="4" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
       <c r="L850" s="4" t="s">
         <v>1546</v>
@@ -45795,7 +45822,7 @@
         <v>1336</v>
       </c>
       <c r="K851" s="4" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="L851" s="4" t="s">
         <v>1546</v>
@@ -45836,7 +45863,7 @@
         <v>1336</v>
       </c>
       <c r="K852" s="4" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="L852" s="4" t="s">
         <v>1547</v>
@@ -45877,7 +45904,7 @@
         <v>1336</v>
       </c>
       <c r="K853" s="4" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="L853" s="4" t="s">
         <v>1547</v>
@@ -45918,7 +45945,7 @@
         <v>1336</v>
       </c>
       <c r="K854" s="4" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="L854" s="4" t="s">
         <v>1546</v>
@@ -45959,7 +45986,7 @@
         <v>1336</v>
       </c>
       <c r="K855" s="4" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="L855" s="4" t="s">
         <v>1546</v>
@@ -46000,7 +46027,7 @@
         <v>1336</v>
       </c>
       <c r="K856" s="4" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="L856" s="4" t="s">
         <v>1546</v>
@@ -46041,7 +46068,7 @@
         <v>1336</v>
       </c>
       <c r="K857" s="4" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="L857" s="4" t="s">
         <v>1546</v>
@@ -46082,7 +46109,7 @@
         <v>1336</v>
       </c>
       <c r="K858" s="4" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="L858" s="4" t="s">
         <v>1547</v>
@@ -46123,7 +46150,7 @@
         <v>1336</v>
       </c>
       <c r="K859" s="4" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="L859" s="4" t="s">
         <v>1546</v>
@@ -46164,7 +46191,7 @@
         <v>1336</v>
       </c>
       <c r="K860" s="4" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="L860" s="4" t="s">
         <v>1546</v>
@@ -46205,7 +46232,7 @@
         <v>1336</v>
       </c>
       <c r="K861" s="4" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="L861" s="4" t="s">
         <v>1546</v>
@@ -46246,7 +46273,7 @@
         <v>1336</v>
       </c>
       <c r="K862" s="4" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="L862" s="4" t="s">
         <v>1546</v>
@@ -46287,7 +46314,7 @@
         <v>1338</v>
       </c>
       <c r="K863" s="4" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="L863" s="4" t="s">
         <v>1546</v>
@@ -46328,7 +46355,7 @@
         <v>1336</v>
       </c>
       <c r="K864" s="4" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="L864" s="4" t="s">
         <v>1546</v>
@@ -46369,7 +46396,7 @@
         <v>1336</v>
       </c>
       <c r="K865" s="4" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="L865" s="4" t="s">
         <v>1547</v>
@@ -46410,7 +46437,7 @@
         <v>1336</v>
       </c>
       <c r="K866" s="4" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="L866" s="4" t="s">
         <v>1546</v>
@@ -46451,7 +46478,7 @@
         <v>1336</v>
       </c>
       <c r="K867" s="4" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="L867" s="4" t="s">
         <v>1546</v>
@@ -46492,7 +46519,7 @@
         <v>1336</v>
       </c>
       <c r="K868" s="4" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="L868" s="4" t="s">
         <v>1546</v>
@@ -46533,7 +46560,7 @@
         <v>1336</v>
       </c>
       <c r="K869" s="4" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="L869" s="4" t="s">
         <v>1546</v>
@@ -46574,7 +46601,7 @@
         <v>1336</v>
       </c>
       <c r="K870" s="4" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="L870" s="4" t="s">
         <v>1547</v>
@@ -46615,7 +46642,7 @@
         <v>1336</v>
       </c>
       <c r="K871" s="4" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="L871" s="4" t="s">
         <v>1546</v>
@@ -46656,7 +46683,7 @@
         <v>1336</v>
       </c>
       <c r="K872" s="4" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="L872" s="4" t="s">
         <v>1546</v>
@@ -46697,7 +46724,7 @@
         <v>1336</v>
       </c>
       <c r="K873" s="4" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="L873" s="4" t="s">
         <v>1546</v>
@@ -46738,7 +46765,7 @@
         <v>1336</v>
       </c>
       <c r="K874" s="4" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="L874" s="4" t="s">
         <v>1546</v>
@@ -46820,7 +46847,7 @@
         <v>1336</v>
       </c>
       <c r="K876" s="4" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="L876" s="4" t="s">
         <v>1546</v>
@@ -46861,7 +46888,7 @@
         <v>1336</v>
       </c>
       <c r="K877" s="4" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="L877" s="4" t="s">
         <v>1546</v>
@@ -46902,7 +46929,7 @@
         <v>1336</v>
       </c>
       <c r="K878" s="4" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="L878" s="4" t="s">
         <v>1547</v>
@@ -46943,7 +46970,7 @@
         <v>1336</v>
       </c>
       <c r="K879" s="4" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="L879" s="4" t="s">
         <v>1546</v>
@@ -46984,7 +47011,7 @@
         <v>1336</v>
       </c>
       <c r="K880" s="4" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="L880" s="4" t="s">
         <v>1546</v>
@@ -47025,7 +47052,7 @@
         <v>1336</v>
       </c>
       <c r="K881" s="4" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="L881" s="4" t="s">
         <v>1546</v>
@@ -47066,7 +47093,7 @@
         <v>1336</v>
       </c>
       <c r="K882" s="4" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="L882" s="4" t="s">
         <v>1546</v>
@@ -47107,7 +47134,7 @@
         <v>1336</v>
       </c>
       <c r="K883" s="4" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="L883" s="4" t="s">
         <v>1546</v>
@@ -47148,7 +47175,7 @@
         <v>1336</v>
       </c>
       <c r="K884" s="4" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="L884" s="4" t="s">
         <v>1546</v>
@@ -47189,7 +47216,7 @@
         <v>1336</v>
       </c>
       <c r="K885" s="4" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
       <c r="L885" s="4" t="s">
         <v>1546</v>
@@ -47230,7 +47257,7 @@
         <v>1336</v>
       </c>
       <c r="K886" s="4" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="L886" s="4" t="s">
         <v>1546</v>
@@ -47271,7 +47298,7 @@
         <v>1338</v>
       </c>
       <c r="K887" s="4" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="L887" s="4" t="s">
         <v>1546</v>
@@ -47312,7 +47339,7 @@
         <v>1336</v>
       </c>
       <c r="K888" s="4" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="L888" s="4" t="s">
         <v>1546</v>
@@ -47353,7 +47380,7 @@
         <v>1336</v>
       </c>
       <c r="K889" s="4" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="L889" s="4" t="s">
         <v>1546</v>
@@ -47394,7 +47421,7 @@
         <v>1336</v>
       </c>
       <c r="K890" s="4" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="L890" s="4" t="s">
         <v>1547</v>
@@ -47435,7 +47462,7 @@
         <v>1336</v>
       </c>
       <c r="K891" s="4" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="L891" s="4" t="s">
         <v>1546</v>
@@ -47476,7 +47503,7 @@
         <v>1336</v>
       </c>
       <c r="K892" s="4" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="L892" s="4" t="s">
         <v>1546</v>
@@ -47517,7 +47544,7 @@
         <v>1338</v>
       </c>
       <c r="K893" s="4" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="L893" s="4" t="s">
         <v>1546</v>
@@ -47558,7 +47585,7 @@
         <v>1336</v>
       </c>
       <c r="K894" s="4" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="L894" s="4" t="s">
         <v>1547</v>
@@ -47599,7 +47626,7 @@
         <v>1338</v>
       </c>
       <c r="K895" s="4" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="L895" s="4" t="s">
         <v>1547</v>
@@ -47640,7 +47667,7 @@
         <v>1336</v>
       </c>
       <c r="K896" s="4" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="L896" s="4" t="s">
         <v>1547</v>
@@ -47681,7 +47708,7 @@
         <v>1336</v>
       </c>
       <c r="K897" s="4" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="L897" s="4" t="s">
         <v>1546</v>
@@ -47722,7 +47749,7 @@
         <v>1336</v>
       </c>
       <c r="K898" s="4" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="L898" s="4" t="s">
         <v>1546</v>
@@ -47763,7 +47790,7 @@
         <v>1336</v>
       </c>
       <c r="K899" s="4" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="L899" s="4" t="s">
         <v>1546</v>
@@ -47804,7 +47831,7 @@
         <v>1336</v>
       </c>
       <c r="K900" s="4" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="L900" s="4" t="s">
         <v>1547</v>
@@ -47845,7 +47872,7 @@
         <v>1338</v>
       </c>
       <c r="K901" s="4" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="L901" s="4" t="s">
         <v>1546</v>
@@ -47886,7 +47913,7 @@
         <v>1336</v>
       </c>
       <c r="K902" s="4" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="L902" s="4" t="s">
         <v>1546</v>
@@ -47927,7 +47954,7 @@
         <v>1336</v>
       </c>
       <c r="K903" s="4" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="L903" s="4" t="s">
         <v>1546</v>
@@ -47968,7 +47995,7 @@
         <v>1338</v>
       </c>
       <c r="K904" s="4" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="L904" s="4" t="s">
         <v>1546</v>
@@ -48009,7 +48036,7 @@
         <v>1336</v>
       </c>
       <c r="K905" s="4" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="L905" s="4" t="s">
         <v>1547</v>
@@ -48050,7 +48077,7 @@
         <v>1336</v>
       </c>
       <c r="K906" s="4" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="L906" s="4" t="s">
         <v>1546</v>
@@ -48082,16 +48109,16 @@
         <v>51</v>
       </c>
       <c r="H907" s="4" t="s">
+        <v>2769</v>
+      </c>
+      <c r="I907" s="4" t="s">
+        <v>1307</v>
+      </c>
+      <c r="J907" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="K907" s="4" t="s">
         <v>2770</v>
-      </c>
-      <c r="I907" s="4" t="s">
-        <v>1307</v>
-      </c>
-      <c r="J907" s="4" t="s">
-        <v>1336</v>
-      </c>
-      <c r="K907" s="4" t="s">
-        <v>2771</v>
       </c>
       <c r="L907" s="4" t="s">
         <v>1546</v>
@@ -48132,7 +48159,7 @@
         <v>1336</v>
       </c>
       <c r="K908" s="4" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="L908" s="4" t="s">
         <v>1547</v>
@@ -48173,7 +48200,7 @@
         <v>1338</v>
       </c>
       <c r="K909" s="4" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="L909" s="4" t="s">
         <v>1547</v>
@@ -48214,7 +48241,7 @@
         <v>1336</v>
       </c>
       <c r="K910" s="4" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="L910" s="4" t="s">
         <v>1546</v>
@@ -48296,7 +48323,7 @@
         <v>1336</v>
       </c>
       <c r="K912" s="4" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="L912" s="4" t="s">
         <v>1546</v>
@@ -48337,7 +48364,7 @@
         <v>1336</v>
       </c>
       <c r="K913" s="4" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="L913" s="4" t="s">
         <v>1546</v>
@@ -48378,7 +48405,7 @@
         <v>1336</v>
       </c>
       <c r="K914" s="4" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="L914" s="4" t="s">
         <v>1546</v>
@@ -48419,7 +48446,7 @@
         <v>1336</v>
       </c>
       <c r="K915" s="4" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L915" s="4" t="s">
         <v>1546</v>
@@ -48460,7 +48487,7 @@
         <v>1336</v>
       </c>
       <c r="K916" s="4" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="L916" s="4" t="s">
         <v>1547</v>
@@ -48501,7 +48528,7 @@
         <v>1336</v>
       </c>
       <c r="K917" s="4" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="L917" s="4" t="s">
         <v>1546</v>
@@ -48542,7 +48569,7 @@
         <v>1336</v>
       </c>
       <c r="K918" s="4" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="L918" s="4" t="s">
         <v>1546</v>
@@ -48583,7 +48610,7 @@
         <v>1336</v>
       </c>
       <c r="K919" s="4" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="L919" s="4" t="s">
         <v>1546</v>
@@ -48624,7 +48651,7 @@
         <v>1336</v>
       </c>
       <c r="K920" s="4" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="L920" s="4" t="s">
         <v>1547</v>
@@ -48665,7 +48692,7 @@
         <v>1336</v>
       </c>
       <c r="K921" s="4" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="L921" s="4" t="s">
         <v>1546</v>
@@ -48706,7 +48733,7 @@
         <v>1336</v>
       </c>
       <c r="K922" s="4" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="L922" s="4" t="s">
         <v>1546</v>
@@ -48747,7 +48774,7 @@
         <v>1336</v>
       </c>
       <c r="K923" s="4" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="L923" s="4" t="s">
         <v>1546</v>
@@ -48788,7 +48815,7 @@
         <v>1336</v>
       </c>
       <c r="K924" s="4" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="L924" s="4" t="s">
         <v>1547</v>
@@ -48829,7 +48856,7 @@
         <v>1336</v>
       </c>
       <c r="K925" s="4" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="L925" s="4" t="s">
         <v>1546</v>
@@ -48870,7 +48897,7 @@
         <v>1338</v>
       </c>
       <c r="K926" s="4" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="L926" s="4" t="s">
         <v>1546</v>
@@ -48911,7 +48938,7 @@
         <v>1338</v>
       </c>
       <c r="K927" s="4" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="L927" s="4" t="s">
         <v>1546</v>
@@ -48952,7 +48979,7 @@
         <v>1338</v>
       </c>
       <c r="K928" s="4" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="L928" s="4" t="s">
         <v>1546</v>
@@ -48993,7 +49020,7 @@
         <v>1336</v>
       </c>
       <c r="K929" s="4" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="L929" s="4" t="s">
         <v>1546</v>
@@ -49034,7 +49061,7 @@
         <v>1336</v>
       </c>
       <c r="K930" s="4" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="L930" s="4" t="s">
         <v>1546</v>
@@ -49075,7 +49102,7 @@
         <v>1338</v>
       </c>
       <c r="K931" s="4" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="L931" s="4" t="s">
         <v>1546</v>
@@ -49116,7 +49143,7 @@
         <v>1336</v>
       </c>
       <c r="K932" s="4" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
       <c r="L932" s="4" t="s">
         <v>1546</v>
@@ -49157,7 +49184,7 @@
         <v>1336</v>
       </c>
       <c r="K933" s="4" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="L933" s="4" t="s">
         <v>1547</v>
@@ -49198,7 +49225,7 @@
         <v>1336</v>
       </c>
       <c r="K934" s="4" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="L934" s="4" t="s">
         <v>1546</v>
@@ -49239,7 +49266,7 @@
         <v>1336</v>
       </c>
       <c r="K935" s="4" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="L935" s="4" t="s">
         <v>1546</v>
@@ -49280,7 +49307,7 @@
         <v>1338</v>
       </c>
       <c r="K936" s="4" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="L936" s="4" t="s">
         <v>1546</v>
@@ -49321,7 +49348,7 @@
         <v>1336</v>
       </c>
       <c r="K937" s="4" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="L937" s="4" t="s">
         <v>1547</v>
@@ -49362,7 +49389,7 @@
         <v>1338</v>
       </c>
       <c r="K938" s="4" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="L938" s="4" t="s">
         <v>1546</v>
@@ -49403,7 +49430,7 @@
         <v>1336</v>
       </c>
       <c r="K939" s="4" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="L939" s="4" t="s">
         <v>1547</v>
@@ -49444,7 +49471,7 @@
         <v>1336</v>
       </c>
       <c r="K940" s="4" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="L940" s="4" t="s">
         <v>1546</v>
@@ -49485,7 +49512,7 @@
         <v>1336</v>
       </c>
       <c r="K941" s="4" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="L941" s="4" t="s">
         <v>1546</v>
@@ -49526,7 +49553,7 @@
         <v>1336</v>
       </c>
       <c r="K942" s="4" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="L942" s="4" t="s">
         <v>1547</v>
@@ -49608,7 +49635,7 @@
         <v>1336</v>
       </c>
       <c r="K944" s="4" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="L944" s="4" t="s">
         <v>1546</v>
@@ -49649,7 +49676,7 @@
         <v>1336</v>
       </c>
       <c r="K945" s="4" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="L945" s="4" t="s">
         <v>1547</v>
@@ -49731,7 +49758,7 @@
         <v>1336</v>
       </c>
       <c r="K947" s="4" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="L947" s="4" t="s">
         <v>1546</v>
@@ -49772,7 +49799,7 @@
         <v>1336</v>
       </c>
       <c r="K948" s="4" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="L948" s="4" t="s">
         <v>1546</v>
@@ -49813,7 +49840,7 @@
         <v>1336</v>
       </c>
       <c r="K949" s="4" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="L949" s="4" t="s">
         <v>1547</v>
@@ -49854,7 +49881,7 @@
         <v>1336</v>
       </c>
       <c r="K950" s="4" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="L950" s="4" t="s">
         <v>1547</v>
@@ -49895,7 +49922,7 @@
         <v>1336</v>
       </c>
       <c r="K951" s="4" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="L951" s="4" t="s">
         <v>1546</v>
@@ -49936,7 +49963,7 @@
         <v>1336</v>
       </c>
       <c r="K952" s="4" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="L952" s="4" t="s">
         <v>1546</v>
@@ -49977,7 +50004,7 @@
         <v>1336</v>
       </c>
       <c r="K953" s="4" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="L953" s="4" t="s">
         <v>1546</v>
@@ -50018,7 +50045,7 @@
         <v>1336</v>
       </c>
       <c r="K954" s="4" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="L954" s="4" t="s">
         <v>1546</v>
@@ -50059,7 +50086,7 @@
         <v>1336</v>
       </c>
       <c r="K955" s="4" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="L955" s="4" t="s">
         <v>1546</v>
@@ -50100,7 +50127,7 @@
         <v>1336</v>
       </c>
       <c r="K956" s="4" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
       <c r="L956" s="4" t="s">
         <v>1547</v>
@@ -50141,7 +50168,7 @@
         <v>1336</v>
       </c>
       <c r="K957" s="4" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="L957" s="4" t="s">
         <v>1546</v>
@@ -50182,7 +50209,7 @@
         <v>1336</v>
       </c>
       <c r="K958" s="4" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="L958" s="4" t="s">
         <v>1546</v>
@@ -50223,7 +50250,7 @@
         <v>1336</v>
       </c>
       <c r="K959" s="4" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="L959" s="4" t="s">
         <v>1546</v>
@@ -50264,7 +50291,7 @@
         <v>1336</v>
       </c>
       <c r="K960" s="4" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="L960" s="4" t="s">
         <v>1546</v>
@@ -50305,7 +50332,7 @@
         <v>1336</v>
       </c>
       <c r="K961" s="4" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="L961" s="4" t="s">
         <v>1546</v>
@@ -50346,7 +50373,7 @@
         <v>1336</v>
       </c>
       <c r="K962" s="4" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="L962" s="4" t="s">
         <v>1546</v>
@@ -50387,7 +50414,7 @@
         <v>1336</v>
       </c>
       <c r="K963" s="4" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="L963" s="4" t="s">
         <v>1546</v>
@@ -50428,7 +50455,7 @@
         <v>1336</v>
       </c>
       <c r="K964" s="4" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="L964" s="4" t="s">
         <v>1546</v>
@@ -50469,7 +50496,7 @@
         <v>1336</v>
       </c>
       <c r="K965" s="4" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="L965" s="4" t="s">
         <v>1547</v>
@@ -50510,7 +50537,7 @@
         <v>1336</v>
       </c>
       <c r="K966" s="4" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="L966" s="4" t="s">
         <v>1546</v>
@@ -50551,7 +50578,7 @@
         <v>1336</v>
       </c>
       <c r="K967" s="4" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="L967" s="4" t="s">
         <v>1546</v>
@@ -50592,7 +50619,7 @@
         <v>1336</v>
       </c>
       <c r="K968" s="4" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="L968" s="4" t="s">
         <v>1546</v>
@@ -50674,7 +50701,7 @@
         <v>1338</v>
       </c>
       <c r="K970" s="4" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="L970" s="4" t="s">
         <v>1546</v>
@@ -50715,7 +50742,7 @@
         <v>1338</v>
       </c>
       <c r="K971" s="4" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="L971" s="4" t="s">
         <v>1547</v>
@@ -50756,7 +50783,7 @@
         <v>1336</v>
       </c>
       <c r="K972" s="4" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="L972" s="4" t="s">
         <v>1546</v>
@@ -50797,7 +50824,7 @@
         <v>1336</v>
       </c>
       <c r="K973" s="4" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="L973" s="4" t="s">
         <v>1546</v>
@@ -50838,7 +50865,7 @@
         <v>1336</v>
       </c>
       <c r="K974" s="4" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="L974" s="4" t="s">
         <v>1546</v>
@@ -50879,7 +50906,7 @@
         <v>1336</v>
       </c>
       <c r="K975" s="4" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="L975" s="4" t="s">
         <v>1547</v>
@@ -50920,7 +50947,7 @@
         <v>1336</v>
       </c>
       <c r="K976" s="4" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="L976" s="4" t="s">
         <v>1547</v>
@@ -51002,7 +51029,7 @@
         <v>1336</v>
       </c>
       <c r="K978" s="4" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="L978" s="4" t="s">
         <v>1547</v>
@@ -51043,7 +51070,7 @@
         <v>1336</v>
       </c>
       <c r="K979" s="4" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="L979" s="4" t="s">
         <v>1546</v>
@@ -51084,7 +51111,7 @@
         <v>1336</v>
       </c>
       <c r="K980" s="4" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="L980" s="4" t="s">
         <v>1546</v>
@@ -51125,7 +51152,7 @@
         <v>1336</v>
       </c>
       <c r="K981" s="4" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="L981" s="4" t="s">
         <v>1546</v>
@@ -51166,7 +51193,7 @@
         <v>1336</v>
       </c>
       <c r="K982" s="4" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="L982" s="4" t="s">
         <v>1546</v>
@@ -51207,7 +51234,7 @@
         <v>1336</v>
       </c>
       <c r="K983" s="4" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="L983" s="4" t="s">
         <v>1546</v>
@@ -51239,7 +51266,7 @@
         <v>51</v>
       </c>
       <c r="H984" s="4" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="I984" s="4" t="s">
         <v>1307</v>
@@ -51248,7 +51275,7 @@
         <v>1336</v>
       </c>
       <c r="K984" s="4" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="L984" s="4" t="s">
         <v>1546</v>
@@ -51289,7 +51316,7 @@
         <v>1336</v>
       </c>
       <c r="K985" s="4" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="L985" s="4" t="s">
         <v>1546</v>
@@ -51330,7 +51357,7 @@
         <v>1336</v>
       </c>
       <c r="K986" s="4" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="L986" s="4" t="s">
         <v>1546</v>
@@ -51371,7 +51398,7 @@
         <v>1336</v>
       </c>
       <c r="K987" s="4" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="L987" s="4" t="s">
         <v>1546</v>
@@ -51453,7 +51480,7 @@
         <v>1336</v>
       </c>
       <c r="K989" s="4" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="L989" s="4" t="s">
         <v>1546</v>
@@ -51494,7 +51521,7 @@
         <v>1336</v>
       </c>
       <c r="K990" s="4" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="L990" s="4" t="s">
         <v>1546</v>
@@ -51535,7 +51562,7 @@
         <v>1336</v>
       </c>
       <c r="K991" s="4" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="L991" s="4" t="s">
         <v>1547</v>
@@ -51576,7 +51603,7 @@
         <v>1338</v>
       </c>
       <c r="K992" s="4" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="L992" s="4" t="s">
         <v>1547</v>
@@ -51617,7 +51644,7 @@
         <v>1336</v>
       </c>
       <c r="K993" s="4" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="L993" s="4" t="s">
         <v>1546</v>
@@ -51658,7 +51685,7 @@
         <v>1336</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="L994" s="4" t="s">
         <v>1546</v>
@@ -51699,7 +51726,7 @@
         <v>1338</v>
       </c>
       <c r="K995" s="4" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="L995" s="4" t="s">
         <v>1546</v>
@@ -51740,7 +51767,7 @@
         <v>1338</v>
       </c>
       <c r="K996" s="4" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="L996" s="4" t="s">
         <v>1546</v>
@@ -51781,7 +51808,7 @@
         <v>1336</v>
       </c>
       <c r="K997" s="4" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="L997" s="4" t="s">
         <v>1546</v>
@@ -51822,7 +51849,7 @@
         <v>1336</v>
       </c>
       <c r="K998" s="4" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="L998" s="4" t="s">
         <v>1546</v>
@@ -51863,7 +51890,7 @@
         <v>1336</v>
       </c>
       <c r="K999" s="4" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="L999" s="4" t="s">
         <v>1546</v>
@@ -51904,7 +51931,7 @@
         <v>1336</v>
       </c>
       <c r="K1000" s="4" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="L1000" s="4" t="s">
         <v>1546</v>
@@ -51945,7 +51972,7 @@
         <v>1338</v>
       </c>
       <c r="K1001" s="4" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="L1001" s="4" t="s">
         <v>1547</v>
@@ -51986,7 +52013,7 @@
         <v>1336</v>
       </c>
       <c r="K1002" s="4" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="L1002" s="4" t="s">
         <v>1546</v>
@@ -52027,7 +52054,7 @@
         <v>1338</v>
       </c>
       <c r="K1003" s="4" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="L1003" s="4" t="s">
         <v>1546</v>
@@ -52068,7 +52095,7 @@
         <v>1336</v>
       </c>
       <c r="K1004" s="4" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="L1004" s="4" t="s">
         <v>1546</v>
@@ -52109,7 +52136,7 @@
         <v>1336</v>
       </c>
       <c r="K1005" s="4" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="L1005" s="4" t="s">
         <v>1546</v>
@@ -52150,7 +52177,7 @@
         <v>1338</v>
       </c>
       <c r="K1006" s="4" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="L1006" s="4" t="s">
         <v>1546</v>
@@ -52191,7 +52218,7 @@
         <v>1336</v>
       </c>
       <c r="K1007" s="4" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="L1007" s="4" t="s">
         <v>1546</v>
@@ -52232,7 +52259,7 @@
         <v>1336</v>
       </c>
       <c r="K1008" s="4" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="L1008" s="4" t="s">
         <v>1546</v>
@@ -52273,7 +52300,7 @@
         <v>1336</v>
       </c>
       <c r="K1009" s="4" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="L1009" s="4" t="s">
         <v>1546</v>
@@ -52314,7 +52341,7 @@
         <v>1336</v>
       </c>
       <c r="K1010" s="4" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="L1010" s="4" t="s">
         <v>1546</v>
@@ -52355,7 +52382,7 @@
         <v>1336</v>
       </c>
       <c r="K1011" s="4" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="L1011" s="4" t="s">
         <v>1546</v>
@@ -52396,7 +52423,7 @@
         <v>1336</v>
       </c>
       <c r="K1012" s="4" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="L1012" s="4" t="s">
         <v>1546</v>
@@ -52437,7 +52464,7 @@
         <v>1336</v>
       </c>
       <c r="K1013" s="4" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="L1013" s="4" t="s">
         <v>1547</v>
@@ -52478,7 +52505,7 @@
         <v>1336</v>
       </c>
       <c r="K1014" s="4" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="L1014" s="4" t="s">
         <v>1546</v>
@@ -52519,7 +52546,7 @@
         <v>1336</v>
       </c>
       <c r="K1015" s="4" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="L1015" s="4" t="s">
         <v>1546</v>
@@ -52560,7 +52587,7 @@
         <v>1336</v>
       </c>
       <c r="K1016" s="4" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="L1016" s="4" t="s">
         <v>1546</v>
@@ -52601,7 +52628,7 @@
         <v>1336</v>
       </c>
       <c r="K1017" s="4" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="L1017" s="4" t="s">
         <v>1547</v>
@@ -52642,7 +52669,7 @@
         <v>1336</v>
       </c>
       <c r="K1018" s="4" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="L1018" s="4" t="s">
         <v>1547</v>
@@ -52683,7 +52710,7 @@
         <v>1338</v>
       </c>
       <c r="K1019" s="4" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="L1019" s="4" t="s">
         <v>1547</v>
@@ -52724,7 +52751,7 @@
         <v>1336</v>
       </c>
       <c r="K1020" s="4" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="L1020" s="4" t="s">
         <v>1546</v>
@@ -52765,7 +52792,7 @@
         <v>1336</v>
       </c>
       <c r="K1021" s="4" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="L1021" s="4" t="s">
         <v>1546</v>
@@ -52806,7 +52833,7 @@
         <v>1336</v>
       </c>
       <c r="K1022" s="4" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="L1022" s="4" t="s">
         <v>1546</v>
@@ -52847,7 +52874,7 @@
         <v>1336</v>
       </c>
       <c r="K1023" s="4" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="L1023" s="4" t="s">
         <v>1546</v>
@@ -52888,7 +52915,7 @@
         <v>1336</v>
       </c>
       <c r="K1024" s="4" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="L1024" s="4" t="s">
         <v>1546</v>
@@ -52929,7 +52956,7 @@
         <v>1336</v>
       </c>
       <c r="K1025" s="4" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="L1025" s="4" t="s">
         <v>1546</v>
@@ -52970,7 +52997,7 @@
         <v>1336</v>
       </c>
       <c r="K1026" s="4" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="L1026" s="4" t="s">
         <v>1547</v>
@@ -53052,7 +53079,7 @@
         <v>1336</v>
       </c>
       <c r="K1028" s="4" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="L1028" s="4" t="s">
         <v>1546</v>
@@ -53093,7 +53120,7 @@
         <v>1336</v>
       </c>
       <c r="K1029" s="4" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="L1029" s="4" t="s">
         <v>1546</v>
@@ -53134,7 +53161,7 @@
         <v>1336</v>
       </c>
       <c r="K1030" s="4" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="L1030" s="4" t="s">
         <v>1546</v>
@@ -53175,7 +53202,7 @@
         <v>1336</v>
       </c>
       <c r="K1031" s="4" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="L1031" s="4" t="s">
         <v>1546</v>
@@ -53216,7 +53243,7 @@
         <v>1336</v>
       </c>
       <c r="K1032" s="4" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="L1032" s="4" t="s">
         <v>1547</v>
@@ -53257,7 +53284,7 @@
         <v>1336</v>
       </c>
       <c r="K1033" s="4" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="L1033" s="4" t="s">
         <v>1546</v>
@@ -53298,7 +53325,7 @@
         <v>1336</v>
       </c>
       <c r="K1034" s="4" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="L1034" s="4" t="s">
         <v>1546</v>
@@ -53339,7 +53366,7 @@
         <v>1338</v>
       </c>
       <c r="K1035" s="4" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="L1035" s="4" t="s">
         <v>1546</v>
@@ -53380,7 +53407,7 @@
         <v>1336</v>
       </c>
       <c r="K1036" s="4" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="L1036" s="4" t="s">
         <v>1546</v>
@@ -53421,7 +53448,7 @@
         <v>1336</v>
       </c>
       <c r="K1037" s="4" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="L1037" s="4" t="s">
         <v>1546</v>
@@ -53462,7 +53489,7 @@
         <v>1338</v>
       </c>
       <c r="K1038" s="4" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="L1038" s="4" t="s">
         <v>1546</v>
@@ -53503,7 +53530,7 @@
         <v>1336</v>
       </c>
       <c r="K1039" s="4" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="L1039" s="4" t="s">
         <v>1546</v>
@@ -53544,7 +53571,7 @@
         <v>1336</v>
       </c>
       <c r="K1040" s="4" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="L1040" s="4" t="s">
         <v>1547</v>
@@ -53585,7 +53612,7 @@
         <v>1336</v>
       </c>
       <c r="K1041" s="4" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="L1041" s="4" t="s">
         <v>1546</v>
@@ -53626,7 +53653,7 @@
         <v>1336</v>
       </c>
       <c r="K1042" s="4" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="L1042" s="4" t="s">
         <v>1546</v>
@@ -53658,7 +53685,7 @@
         <v>51</v>
       </c>
       <c r="H1043" s="4" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="I1043" s="4" t="s">
         <v>1307</v>
@@ -53667,7 +53694,7 @@
         <v>1336</v>
       </c>
       <c r="K1043" s="4" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="L1043" s="4" t="s">
         <v>1547</v>
@@ -53708,7 +53735,7 @@
         <v>1336</v>
       </c>
       <c r="K1044" s="4" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="L1044" s="4" t="s">
         <v>1546</v>
@@ -53749,7 +53776,7 @@
         <v>1336</v>
       </c>
       <c r="K1045" s="4" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="L1045" s="4" t="s">
         <v>1546</v>
@@ -53790,7 +53817,7 @@
         <v>1336</v>
       </c>
       <c r="K1046" s="4" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="L1046" s="4" t="s">
         <v>1547</v>
@@ -53831,7 +53858,7 @@
         <v>1336</v>
       </c>
       <c r="K1047" s="4" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="L1047" s="4" t="s">
         <v>1546</v>
@@ -53872,7 +53899,7 @@
         <v>1336</v>
       </c>
       <c r="K1048" s="4" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="L1048" s="4" t="s">
         <v>1546</v>
@@ -53913,7 +53940,7 @@
         <v>1336</v>
       </c>
       <c r="K1049" s="4" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="L1049" s="4" t="s">
         <v>1546</v>
@@ -53954,7 +53981,7 @@
         <v>1336</v>
       </c>
       <c r="K1050" s="4" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="L1050" s="4" t="s">
         <v>1546</v>
@@ -53995,7 +54022,7 @@
         <v>1336</v>
       </c>
       <c r="K1051" s="4" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="L1051" s="4" t="s">
         <v>1546</v>
@@ -54036,7 +54063,7 @@
         <v>1338</v>
       </c>
       <c r="K1052" s="4" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="L1052" s="4" t="s">
         <v>1546</v>
@@ -54077,7 +54104,7 @@
         <v>1336</v>
       </c>
       <c r="K1053" s="4" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="L1053" s="4" t="s">
         <v>1547</v>
@@ -54118,7 +54145,7 @@
         <v>1336</v>
       </c>
       <c r="K1054" s="4" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="L1054" s="4" t="s">
         <v>1546</v>
@@ -54159,7 +54186,7 @@
         <v>1336</v>
       </c>
       <c r="K1055" s="4" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="L1055" s="4" t="s">
         <v>1547</v>
@@ -54241,7 +54268,7 @@
         <v>1336</v>
       </c>
       <c r="K1057" s="4" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="L1057" s="4" t="s">
         <v>1546</v>
@@ -54282,7 +54309,7 @@
         <v>1336</v>
       </c>
       <c r="K1058" s="4" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="L1058" s="4" t="s">
         <v>1546</v>
@@ -54364,7 +54391,7 @@
         <v>1336</v>
       </c>
       <c r="K1060" s="4" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="L1060" s="4" t="s">
         <v>1546</v>
@@ -54405,7 +54432,7 @@
         <v>1336</v>
       </c>
       <c r="K1061" s="4" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="L1061" s="4" t="s">
         <v>1547</v>
@@ -54446,7 +54473,7 @@
         <v>1336</v>
       </c>
       <c r="K1062" s="4" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="L1062" s="4" t="s">
         <v>1546</v>
@@ -54487,7 +54514,7 @@
         <v>1336</v>
       </c>
       <c r="K1063" s="4" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="L1063" s="4" t="s">
         <v>1546</v>
@@ -54528,7 +54555,7 @@
         <v>1336</v>
       </c>
       <c r="K1064" s="4" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="L1064" s="4" t="s">
         <v>1546</v>
@@ -54569,7 +54596,7 @@
         <v>1336</v>
       </c>
       <c r="K1065" s="4" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="L1065" s="4" t="s">
         <v>1546</v>
@@ -54610,7 +54637,7 @@
         <v>1336</v>
       </c>
       <c r="K1066" s="4" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="L1066" s="4" t="s">
         <v>1546</v>
@@ -54651,7 +54678,7 @@
         <v>1336</v>
       </c>
       <c r="K1067" s="4" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="L1067" s="4" t="s">
         <v>1546</v>
@@ -54692,7 +54719,7 @@
         <v>1336</v>
       </c>
       <c r="K1068" s="4" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="L1068" s="4" t="s">
         <v>1546</v>
@@ -54733,7 +54760,7 @@
         <v>1336</v>
       </c>
       <c r="K1069" s="4" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="L1069" s="4" t="s">
         <v>1546</v>
@@ -54774,7 +54801,7 @@
         <v>1336</v>
       </c>
       <c r="K1070" s="4" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="L1070" s="4" t="s">
         <v>1546</v>
@@ -54815,7 +54842,7 @@
         <v>1336</v>
       </c>
       <c r="K1071" s="4" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="L1071" s="4" t="s">
         <v>1547</v>
@@ -54856,7 +54883,7 @@
         <v>1336</v>
       </c>
       <c r="K1072" s="4" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="L1072" s="4" t="s">
         <v>1546</v>
@@ -54897,7 +54924,7 @@
         <v>1336</v>
       </c>
       <c r="K1073" s="4" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="L1073" s="4" t="s">
         <v>1547</v>
@@ -54938,7 +54965,7 @@
         <v>1336</v>
       </c>
       <c r="K1074" s="4" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="L1074" s="4" t="s">
         <v>1547</v>
@@ -54979,7 +55006,7 @@
         <v>1336</v>
       </c>
       <c r="K1075" s="4" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="L1075" s="4" t="s">
         <v>1546</v>
@@ -55020,7 +55047,7 @@
         <v>1336</v>
       </c>
       <c r="K1076" s="4" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="L1076" s="4" t="s">
         <v>1547</v>
@@ -55061,7 +55088,7 @@
         <v>1338</v>
       </c>
       <c r="K1077" s="4" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="L1077" s="4" t="s">
         <v>1546</v>
@@ -55102,7 +55129,7 @@
         <v>1336</v>
       </c>
       <c r="K1078" s="4" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="L1078" s="4" t="s">
         <v>1546</v>
@@ -55143,7 +55170,7 @@
         <v>1336</v>
       </c>
       <c r="K1079" s="4" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="L1079" s="4" t="s">
         <v>1546</v>
@@ -55184,7 +55211,7 @@
         <v>1336</v>
       </c>
       <c r="K1080" s="4" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="L1080" s="4" t="s">
         <v>1546</v>
@@ -55225,7 +55252,7 @@
         <v>1336</v>
       </c>
       <c r="K1081" s="4" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="L1081" s="4" t="s">
         <v>1546</v>
@@ -55266,7 +55293,7 @@
         <v>1336</v>
       </c>
       <c r="K1082" s="4" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="L1082" s="4" t="s">
         <v>1546</v>
@@ -55307,7 +55334,7 @@
         <v>1336</v>
       </c>
       <c r="K1083" s="4" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="L1083" s="4" t="s">
         <v>1547</v>
@@ -55348,7 +55375,7 @@
         <v>1336</v>
       </c>
       <c r="K1084" s="4" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="L1084" s="4" t="s">
         <v>1547</v>
@@ -55389,7 +55416,7 @@
         <v>1336</v>
       </c>
       <c r="K1085" s="4" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="L1085" s="4" t="s">
         <v>1546</v>
@@ -55430,7 +55457,7 @@
         <v>1336</v>
       </c>
       <c r="K1086" s="4" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="L1086" s="4" t="s">
         <v>1546</v>
@@ -55512,7 +55539,7 @@
         <v>1336</v>
       </c>
       <c r="K1088" s="4" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="L1088" s="4" t="s">
         <v>1546</v>
@@ -55553,7 +55580,7 @@
         <v>1336</v>
       </c>
       <c r="K1089" s="4" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="L1089" s="4" t="s">
         <v>1547</v>
@@ -55594,7 +55621,7 @@
         <v>1336</v>
       </c>
       <c r="K1090" s="4" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="L1090" s="4" t="s">
         <v>1547</v>
@@ -55635,7 +55662,7 @@
         <v>1336</v>
       </c>
       <c r="K1091" s="4" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="L1091" s="4" t="s">
         <v>1546</v>
@@ -55676,7 +55703,7 @@
         <v>1338</v>
       </c>
       <c r="K1092" s="4" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="L1092" s="4" t="s">
         <v>1546</v>
@@ -55717,7 +55744,7 @@
         <v>1336</v>
       </c>
       <c r="K1093" s="4" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="L1093" s="4" t="s">
         <v>1546</v>
@@ -55758,7 +55785,7 @@
         <v>1336</v>
       </c>
       <c r="K1094" s="4" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="L1094" s="4" t="s">
         <v>1546</v>
@@ -55799,7 +55826,7 @@
         <v>1336</v>
       </c>
       <c r="K1095" s="4" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="L1095" s="4" t="s">
         <v>1547</v>
@@ -55840,7 +55867,7 @@
         <v>1336</v>
       </c>
       <c r="K1096" s="4" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="L1096" s="4" t="s">
         <v>1547</v>
@@ -55881,7 +55908,7 @@
         <v>1336</v>
       </c>
       <c r="K1097" s="4" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="L1097" s="4" t="s">
         <v>1546</v>
@@ -55922,7 +55949,7 @@
         <v>1336</v>
       </c>
       <c r="K1098" s="4" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="L1098" s="4" t="s">
         <v>1546</v>
@@ -55963,7 +55990,7 @@
         <v>1336</v>
       </c>
       <c r="K1099" s="4" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="L1099" s="4" t="s">
         <v>1546</v>
@@ -56004,7 +56031,7 @@
         <v>1336</v>
       </c>
       <c r="K1100" s="4" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="L1100" s="4" t="s">
         <v>1546</v>
@@ -56045,7 +56072,7 @@
         <v>1336</v>
       </c>
       <c r="K1101" s="4" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="L1101" s="4" t="s">
         <v>1546</v>
@@ -56127,7 +56154,7 @@
         <v>1336</v>
       </c>
       <c r="K1103" s="4" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="L1103" s="4" t="s">
         <v>1547</v>
@@ -56168,7 +56195,7 @@
         <v>1338</v>
       </c>
       <c r="K1104" s="4" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="L1104" s="4" t="s">
         <v>1546</v>
@@ -56209,7 +56236,7 @@
         <v>1336</v>
       </c>
       <c r="K1105" s="4" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="L1105" s="4" t="s">
         <v>1547</v>
@@ -56250,7 +56277,7 @@
         <v>1336</v>
       </c>
       <c r="K1106" s="4" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="L1106" s="4" t="s">
         <v>1546</v>
@@ -56291,7 +56318,7 @@
         <v>1336</v>
       </c>
       <c r="K1107" s="4" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="L1107" s="4" t="s">
         <v>1546</v>
@@ -56332,7 +56359,7 @@
         <v>1336</v>
       </c>
       <c r="K1108" s="4" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="L1108" s="4" t="s">
         <v>1547</v>
@@ -56373,7 +56400,7 @@
         <v>1336</v>
       </c>
       <c r="K1109" s="4" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="L1109" s="4" t="s">
         <v>1546</v>
@@ -56414,7 +56441,7 @@
         <v>1336</v>
       </c>
       <c r="K1110" s="4" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="L1110" s="4" t="s">
         <v>1546</v>
@@ -56455,7 +56482,7 @@
         <v>1336</v>
       </c>
       <c r="K1111" s="4" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="L1111" s="4" t="s">
         <v>1546</v>
@@ -56496,7 +56523,7 @@
         <v>1336</v>
       </c>
       <c r="K1112" s="4" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="L1112" s="4" t="s">
         <v>1546</v>
@@ -56537,7 +56564,7 @@
         <v>1336</v>
       </c>
       <c r="K1113" s="4" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="L1113" s="4" t="s">
         <v>1547</v>
@@ -56578,7 +56605,7 @@
         <v>1336</v>
       </c>
       <c r="K1114" s="4" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="L1114" s="4" t="s">
         <v>1546</v>
@@ -56619,7 +56646,7 @@
         <v>1338</v>
       </c>
       <c r="K1115" s="4" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="L1115" s="4" t="s">
         <v>1546</v>
@@ -56660,7 +56687,7 @@
         <v>1338</v>
       </c>
       <c r="K1116" s="4" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="L1116" s="4" t="s">
         <v>1546</v>
@@ -56701,7 +56728,7 @@
         <v>1336</v>
       </c>
       <c r="K1117" s="4" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="L1117" s="4" t="s">
         <v>1546</v>
@@ -56742,7 +56769,7 @@
         <v>1336</v>
       </c>
       <c r="K1118" s="4" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="L1118" s="4" t="s">
         <v>1546</v>
@@ -56783,7 +56810,7 @@
         <v>1336</v>
       </c>
       <c r="K1119" s="4" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="L1119" s="4" t="s">
         <v>1546</v>
@@ -56865,7 +56892,7 @@
         <v>1336</v>
       </c>
       <c r="K1121" s="4" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="L1121" s="4" t="s">
         <v>1546</v>
@@ -56906,7 +56933,7 @@
         <v>1336</v>
       </c>
       <c r="K1122" s="4" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="L1122" s="4" t="s">
         <v>1546</v>
@@ -56947,7 +56974,7 @@
         <v>1336</v>
       </c>
       <c r="K1123" s="4" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="L1123" s="4" t="s">
         <v>1546</v>
@@ -56988,7 +57015,7 @@
         <v>1338</v>
       </c>
       <c r="K1124" s="4" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="L1124" s="4" t="s">
         <v>1546</v>
@@ -57029,7 +57056,7 @@
         <v>1336</v>
       </c>
       <c r="K1125" s="4" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="L1125" s="4" t="s">
         <v>1546</v>
@@ -57070,7 +57097,7 @@
         <v>1336</v>
       </c>
       <c r="K1126" s="4" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="L1126" s="4" t="s">
         <v>1546</v>
@@ -57111,7 +57138,7 @@
         <v>1336</v>
       </c>
       <c r="K1127" s="4" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="L1127" s="4" t="s">
         <v>1546</v>
@@ -57152,7 +57179,7 @@
         <v>1336</v>
       </c>
       <c r="K1128" s="4" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="L1128" s="4" t="s">
         <v>1546</v>
@@ -57193,7 +57220,7 @@
         <v>1336</v>
       </c>
       <c r="K1129" s="4" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="L1129" s="4" t="s">
         <v>1546</v>
@@ -57275,7 +57302,7 @@
         <v>1336</v>
       </c>
       <c r="K1131" s="4" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="L1131" s="4" t="s">
         <v>1546</v>
@@ -57316,7 +57343,7 @@
         <v>1336</v>
       </c>
       <c r="K1132" s="4" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="L1132" s="4" t="s">
         <v>1546</v>
@@ -57357,7 +57384,7 @@
         <v>1336</v>
       </c>
       <c r="K1133" s="4" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="L1133" s="4" t="s">
         <v>1546</v>
@@ -57398,7 +57425,7 @@
         <v>1336</v>
       </c>
       <c r="K1134" s="4" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="L1134" s="4" t="s">
         <v>1547</v>
@@ -57439,7 +57466,7 @@
         <v>1338</v>
       </c>
       <c r="K1135" s="4" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="L1135" s="4" t="s">
         <v>1546</v>
@@ -57480,7 +57507,7 @@
         <v>1336</v>
       </c>
       <c r="K1136" s="4" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="L1136" s="4" t="s">
         <v>1546</v>
@@ -57521,7 +57548,7 @@
         <v>1336</v>
       </c>
       <c r="K1137" s="4" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="L1137" s="4" t="s">
         <v>1546</v>
@@ -57562,7 +57589,7 @@
         <v>1336</v>
       </c>
       <c r="K1138" s="4" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="L1138" s="4" t="s">
         <v>1546</v>
@@ -57603,7 +57630,7 @@
         <v>1338</v>
       </c>
       <c r="K1139" s="4" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="L1139" s="4" t="s">
         <v>1546</v>
@@ -57644,7 +57671,7 @@
         <v>1338</v>
       </c>
       <c r="K1140" s="4" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="L1140" s="4" t="s">
         <v>1546</v>
@@ -57685,7 +57712,7 @@
         <v>1336</v>
       </c>
       <c r="K1141" s="4" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="L1141" s="4" t="s">
         <v>1546</v>
@@ -57726,7 +57753,7 @@
         <v>1338</v>
       </c>
       <c r="K1142" s="4" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="L1142" s="4" t="s">
         <v>1546</v>
@@ -57767,7 +57794,7 @@
         <v>1338</v>
       </c>
       <c r="K1143" s="4" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="L1143" s="4" t="s">
         <v>1546</v>
@@ -57808,7 +57835,7 @@
         <v>1338</v>
       </c>
       <c r="K1144" s="4" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="L1144" s="4" t="s">
         <v>1546</v>
@@ -57849,7 +57876,7 @@
         <v>1336</v>
       </c>
       <c r="K1145" s="4" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="L1145" s="4" t="s">
         <v>1546</v>
@@ -57931,7 +57958,7 @@
         <v>1336</v>
       </c>
       <c r="K1147" s="4" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="L1147" s="4" t="s">
         <v>1546</v>
@@ -57972,7 +57999,7 @@
         <v>1336</v>
       </c>
       <c r="K1148" s="4" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="L1148" s="4" t="s">
         <v>1546</v>
@@ -58013,7 +58040,7 @@
         <v>1336</v>
       </c>
       <c r="K1149" s="4" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="L1149" s="4" t="s">
         <v>1547</v>
@@ -58054,7 +58081,7 @@
         <v>1336</v>
       </c>
       <c r="K1150" s="4" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="L1150" s="4" t="s">
         <v>1546</v>
@@ -58095,7 +58122,7 @@
         <v>1336</v>
       </c>
       <c r="K1151" s="4" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="L1151" s="4" t="s">
         <v>1546</v>
@@ -58136,7 +58163,7 @@
         <v>1336</v>
       </c>
       <c r="K1152" s="4" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="L1152" s="4" t="s">
         <v>1546</v>
@@ -58177,7 +58204,7 @@
         <v>1336</v>
       </c>
       <c r="K1153" s="4" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="L1153" s="4" t="s">
         <v>1546</v>
@@ -58218,7 +58245,7 @@
         <v>1338</v>
       </c>
       <c r="K1154" s="4" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="L1154" s="4" t="s">
         <v>1546</v>
@@ -58259,7 +58286,7 @@
         <v>1336</v>
       </c>
       <c r="K1155" s="4" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="L1155" s="4" t="s">
         <v>1546</v>
@@ -58300,7 +58327,7 @@
         <v>1336</v>
       </c>
       <c r="K1156" s="4" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="L1156" s="4" t="s">
         <v>1546</v>
@@ -58341,7 +58368,7 @@
         <v>1336</v>
       </c>
       <c r="K1157" s="4" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="L1157" s="4" t="s">
         <v>1546</v>
@@ -58382,7 +58409,7 @@
         <v>1336</v>
       </c>
       <c r="K1158" s="4" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="L1158" s="4" t="s">
         <v>1546</v>
@@ -58423,7 +58450,7 @@
         <v>1336</v>
       </c>
       <c r="K1159" s="4" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="L1159" s="4" t="s">
         <v>1546</v>
@@ -58464,7 +58491,7 @@
         <v>1336</v>
       </c>
       <c r="K1160" s="4" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="L1160" s="4" t="s">
         <v>1547</v>
@@ -58505,7 +58532,7 @@
         <v>1336</v>
       </c>
       <c r="K1161" s="4" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="L1161" s="4" t="s">
         <v>1546</v>
@@ -58546,7 +58573,7 @@
         <v>1336</v>
       </c>
       <c r="K1162" s="4" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="L1162" s="4" t="s">
         <v>1546</v>
@@ -58587,7 +58614,7 @@
         <v>1336</v>
       </c>
       <c r="K1163" s="4" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="L1163" s="4" t="s">
         <v>1547</v>
@@ -58628,7 +58655,7 @@
         <v>1336</v>
       </c>
       <c r="K1164" s="4" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="L1164" s="4" t="s">
         <v>1546</v>
@@ -58669,7 +58696,7 @@
         <v>1336</v>
       </c>
       <c r="K1165" s="4" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="L1165" s="4" t="s">
         <v>1546</v>
@@ -58710,7 +58737,7 @@
         <v>1336</v>
       </c>
       <c r="K1166" s="4" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="L1166" s="4" t="s">
         <v>1546</v>
@@ -58751,7 +58778,7 @@
         <v>1336</v>
       </c>
       <c r="K1167" s="4" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="L1167" s="4" t="s">
         <v>1546</v>
@@ -58792,7 +58819,7 @@
         <v>1336</v>
       </c>
       <c r="K1168" s="4" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="L1168" s="4" t="s">
         <v>1547</v>
@@ -58833,7 +58860,7 @@
         <v>1336</v>
       </c>
       <c r="K1169" s="4" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="L1169" s="4" t="s">
         <v>1546</v>
@@ -58874,7 +58901,7 @@
         <v>1336</v>
       </c>
       <c r="K1170" s="4" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="L1170" s="4" t="s">
         <v>1546</v>
@@ -58915,7 +58942,7 @@
         <v>1336</v>
       </c>
       <c r="K1171" s="4" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="L1171" s="4" t="s">
         <v>1546</v>
@@ -58956,7 +58983,7 @@
         <v>1336</v>
       </c>
       <c r="K1172" s="4" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="L1172" s="4" t="s">
         <v>1546</v>
@@ -58997,7 +59024,7 @@
         <v>1336</v>
       </c>
       <c r="K1173" s="4" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="L1173" s="4" t="s">
         <v>1546</v>
@@ -59038,7 +59065,7 @@
         <v>1336</v>
       </c>
       <c r="K1174" s="4" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="L1174" s="4" t="s">
         <v>1546</v>
@@ -59079,7 +59106,7 @@
         <v>1336</v>
       </c>
       <c r="K1175" s="4" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="L1175" s="4" t="s">
         <v>1546</v>
@@ -59120,7 +59147,7 @@
         <v>1336</v>
       </c>
       <c r="K1176" s="4" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="L1176" s="4" t="s">
         <v>1546</v>
@@ -59161,7 +59188,7 @@
         <v>1338</v>
       </c>
       <c r="K1177" s="4" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="L1177" s="4" t="s">
         <v>1546</v>
@@ -59202,7 +59229,7 @@
         <v>1336</v>
       </c>
       <c r="K1178" s="4" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="L1178" s="4" t="s">
         <v>1546</v>
@@ -59243,7 +59270,7 @@
         <v>1336</v>
       </c>
       <c r="K1179" s="4" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="L1179" s="4" t="s">
         <v>1546</v>
@@ -59284,7 +59311,7 @@
         <v>1336</v>
       </c>
       <c r="K1180" s="4" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="L1180" s="4" t="s">
         <v>1547</v>
@@ -59325,7 +59352,7 @@
         <v>1336</v>
       </c>
       <c r="K1181" s="4" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="L1181" s="4" t="s">
         <v>1547</v>
@@ -59366,7 +59393,7 @@
         <v>1336</v>
       </c>
       <c r="K1182" s="4" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="L1182" s="4" t="s">
         <v>1546</v>
@@ -59407,7 +59434,7 @@
         <v>1336</v>
       </c>
       <c r="K1183" s="4" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="L1183" s="4" t="s">
         <v>1547</v>
@@ -59489,7 +59516,7 @@
         <v>1336</v>
       </c>
       <c r="K1185" s="4" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="L1185" s="4" t="s">
         <v>1546</v>
@@ -59530,7 +59557,7 @@
         <v>1336</v>
       </c>
       <c r="K1186" s="4" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="L1186" s="4" t="s">
         <v>1546</v>
@@ -59571,7 +59598,7 @@
         <v>1336</v>
       </c>
       <c r="K1187" s="4" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="L1187" s="4" t="s">
         <v>1546</v>
@@ -59612,7 +59639,7 @@
         <v>1336</v>
       </c>
       <c r="K1188" s="4" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="L1188" s="4" t="s">
         <v>1546</v>
@@ -59653,7 +59680,7 @@
         <v>1338</v>
       </c>
       <c r="K1189" s="4" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="L1189" s="4" t="s">
         <v>1546</v>
@@ -59694,7 +59721,7 @@
         <v>1336</v>
       </c>
       <c r="K1190" s="4" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="L1190" s="4" t="s">
         <v>1546</v>
@@ -59735,7 +59762,7 @@
         <v>1336</v>
       </c>
       <c r="K1191" s="4" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="L1191" s="4" t="s">
         <v>1546</v>
@@ -59776,7 +59803,7 @@
         <v>1338</v>
       </c>
       <c r="K1192" s="4" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="L1192" s="4" t="s">
         <v>1546</v>
@@ -59817,7 +59844,7 @@
         <v>1336</v>
       </c>
       <c r="K1193" s="4" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="L1193" s="4" t="s">
         <v>1546</v>
@@ -59858,7 +59885,7 @@
         <v>1336</v>
       </c>
       <c r="K1194" s="4" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="L1194" s="4" t="s">
         <v>1546</v>
@@ -59899,7 +59926,7 @@
         <v>1336</v>
       </c>
       <c r="K1195" s="4" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="L1195" s="4" t="s">
         <v>1546</v>
@@ -59940,7 +59967,7 @@
         <v>1336</v>
       </c>
       <c r="K1196" s="4" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="L1196" s="4" t="s">
         <v>1546</v>
@@ -59981,7 +60008,7 @@
         <v>1336</v>
       </c>
       <c r="K1197" s="4" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="L1197" s="4" t="s">
         <v>1546</v>
@@ -60022,7 +60049,7 @@
         <v>1337</v>
       </c>
       <c r="K1198" s="4" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="L1198" s="4" t="s">
         <v>1546</v>
@@ -60063,7 +60090,7 @@
         <v>1338</v>
       </c>
       <c r="K1199" s="4" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="L1199" s="4" t="s">
         <v>1546</v>
@@ -60104,7 +60131,7 @@
         <v>1337</v>
       </c>
       <c r="K1200" s="4" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="L1200" s="4" t="s">
         <v>1546</v>
@@ -60145,7 +60172,7 @@
         <v>1337</v>
       </c>
       <c r="K1201" s="4" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="L1201" s="4" t="s">
         <v>1546</v>
@@ -60186,7 +60213,7 @@
         <v>1337</v>
       </c>
       <c r="K1202" s="4" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="L1202" s="4" t="s">
         <v>1547</v>
@@ -60227,7 +60254,7 @@
         <v>1336</v>
       </c>
       <c r="K1203" s="4" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="L1203" s="4" t="s">
         <v>1547</v>
@@ -60268,7 +60295,7 @@
         <v>1336</v>
       </c>
       <c r="K1204" s="4" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="L1204" s="4" t="s">
         <v>1546</v>
@@ -60309,7 +60336,7 @@
         <v>1336</v>
       </c>
       <c r="K1205" s="4" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="L1205" s="4" t="s">
         <v>1546</v>
@@ -60350,7 +60377,7 @@
         <v>1336</v>
       </c>
       <c r="K1206" s="4" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="L1206" s="4" t="s">
         <v>1546</v>
@@ -60391,7 +60418,7 @@
         <v>1338</v>
       </c>
       <c r="K1207" s="4" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="L1207" s="4" t="s">
         <v>1546</v>
@@ -60432,7 +60459,7 @@
         <v>1336</v>
       </c>
       <c r="K1208" s="4" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="L1208" s="4" t="s">
         <v>1546</v>
@@ -60473,7 +60500,7 @@
         <v>1336</v>
       </c>
       <c r="K1209" s="4" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="L1209" s="4" t="s">
         <v>1546</v>
@@ -60514,7 +60541,7 @@
         <v>1338</v>
       </c>
       <c r="K1210" s="4" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="L1210" s="4" t="s">
         <v>1546</v>
@@ -60555,7 +60582,7 @@
         <v>1336</v>
       </c>
       <c r="K1211" s="4" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="L1211" s="4" t="s">
         <v>1546</v>
@@ -60596,7 +60623,7 @@
         <v>1336</v>
       </c>
       <c r="K1212" s="4" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="L1212" s="4" t="s">
         <v>1546</v>
@@ -60637,7 +60664,7 @@
         <v>1337</v>
       </c>
       <c r="K1213" s="4" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="L1213" s="4" t="s">
         <v>1547</v>
@@ -60678,7 +60705,7 @@
         <v>1338</v>
       </c>
       <c r="K1214" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="L1214" s="4" t="s">
         <v>1546</v>
@@ -60719,7 +60746,7 @@
         <v>1337</v>
       </c>
       <c r="K1215" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="L1215" s="4" t="s">
         <v>1546</v>
@@ -60760,7 +60787,7 @@
         <v>1337</v>
       </c>
       <c r="K1216" s="4" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="L1216" s="4" t="s">
         <v>1547</v>
@@ -60801,7 +60828,7 @@
         <v>1336</v>
       </c>
       <c r="K1217" s="4" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="L1217" s="4" t="s">
         <v>1546</v>
@@ -60842,7 +60869,7 @@
         <v>1336</v>
       </c>
       <c r="K1218" s="4" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="L1218" s="4" t="s">
         <v>1546</v>
@@ -60883,7 +60910,7 @@
         <v>1336</v>
       </c>
       <c r="K1219" s="4" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="L1219" s="4" t="s">
         <v>1546</v>
@@ -60965,7 +60992,7 @@
         <v>1336</v>
       </c>
       <c r="K1221" s="4" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="L1221" s="4" t="s">
         <v>1546</v>
@@ -61006,7 +61033,7 @@
         <v>1336</v>
       </c>
       <c r="K1222" s="4" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="L1222" s="4" t="s">
         <v>1546</v>
@@ -61047,7 +61074,7 @@
         <v>1336</v>
       </c>
       <c r="K1223" s="4" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="L1223" s="4" t="s">
         <v>1546</v>
@@ -61129,7 +61156,7 @@
         <v>1336</v>
       </c>
       <c r="K1225" s="4" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="L1225" s="4" t="s">
         <v>1546</v>
@@ -61170,7 +61197,7 @@
         <v>1336</v>
       </c>
       <c r="K1226" s="4" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="L1226" s="4" t="s">
         <v>1546</v>
@@ -61211,7 +61238,7 @@
         <v>1336</v>
       </c>
       <c r="K1227" s="4" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="L1227" s="4" t="s">
         <v>1546</v>
@@ -61252,7 +61279,7 @@
         <v>1336</v>
       </c>
       <c r="K1228" s="4" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="L1228" s="4" t="s">
         <v>1546</v>
@@ -61293,7 +61320,7 @@
         <v>1336</v>
       </c>
       <c r="K1229" s="4" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="L1229" s="4" t="s">
         <v>1546</v>
@@ -61334,7 +61361,7 @@
         <v>1338</v>
       </c>
       <c r="K1230" s="4" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="L1230" s="4" t="s">
         <v>1546</v>
@@ -61375,7 +61402,7 @@
         <v>1337</v>
       </c>
       <c r="K1231" s="4" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="L1231" s="4" t="s">
         <v>1546</v>
@@ -61416,7 +61443,7 @@
         <v>1338</v>
       </c>
       <c r="K1232" s="4" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="L1232" s="4" t="s">
         <v>1547</v>
@@ -61457,7 +61484,7 @@
         <v>1337</v>
       </c>
       <c r="K1233" s="4" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="L1233" s="4" t="s">
         <v>1546</v>
@@ -61498,7 +61525,7 @@
         <v>1336</v>
       </c>
       <c r="K1234" s="4" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="L1234" s="4" t="s">
         <v>1546</v>
@@ -61539,7 +61566,7 @@
         <v>1336</v>
       </c>
       <c r="K1235" s="4" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="L1235" s="4" t="s">
         <v>1546</v>
@@ -61580,7 +61607,7 @@
         <v>1338</v>
       </c>
       <c r="K1236" s="4" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="L1236" s="4" t="s">
         <v>1546</v>
@@ -61621,7 +61648,7 @@
         <v>1336</v>
       </c>
       <c r="K1237" s="4" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="L1237" s="4" t="s">
         <v>1546</v>
@@ -61662,7 +61689,7 @@
         <v>1336</v>
       </c>
       <c r="K1238" s="4" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="L1238" s="4" t="s">
         <v>1546</v>
@@ -61703,7 +61730,7 @@
         <v>1338</v>
       </c>
       <c r="K1239" s="4" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="L1239" s="4" t="s">
         <v>1546</v>
@@ -61744,7 +61771,7 @@
         <v>1338</v>
       </c>
       <c r="K1240" s="4" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="L1240" s="4" t="s">
         <v>1546</v>
@@ -61785,7 +61812,7 @@
         <v>1336</v>
       </c>
       <c r="K1241" s="4" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="L1241" s="4" t="s">
         <v>1546</v>
@@ -61867,7 +61894,7 @@
         <v>1336</v>
       </c>
       <c r="K1243" s="4" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="L1243" s="4" t="s">
         <v>1546</v>
@@ -61908,7 +61935,7 @@
         <v>1338</v>
       </c>
       <c r="K1244" s="4" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="L1244" s="4" t="s">
         <v>1546</v>
@@ -61949,7 +61976,7 @@
         <v>1336</v>
       </c>
       <c r="K1245" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="L1245" s="4" t="s">
         <v>1546</v>
@@ -61990,7 +62017,7 @@
         <v>1336</v>
       </c>
       <c r="K1246" s="4" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="L1246" s="4" t="s">
         <v>1546</v>
@@ -62031,7 +62058,7 @@
         <v>1336</v>
       </c>
       <c r="K1247" s="4" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="L1247" s="4" t="s">
         <v>1546</v>
@@ -62072,7 +62099,7 @@
         <v>1336</v>
       </c>
       <c r="K1248" s="4" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="L1248" s="4" t="s">
         <v>1546</v>
@@ -62113,7 +62140,7 @@
         <v>1336</v>
       </c>
       <c r="K1249" s="4" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="L1249" s="4" t="s">
         <v>1546</v>
@@ -62154,7 +62181,7 @@
         <v>1338</v>
       </c>
       <c r="K1250" s="4" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="L1250" s="4" t="s">
         <v>1547</v>
@@ -62195,7 +62222,7 @@
         <v>1336</v>
       </c>
       <c r="K1251" s="4" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="L1251" s="4" t="s">
         <v>1546</v>
@@ -62236,7 +62263,7 @@
         <v>1336</v>
       </c>
       <c r="K1252" s="4" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="L1252" s="4" t="s">
         <v>1546</v>
@@ -62277,7 +62304,7 @@
         <v>1336</v>
       </c>
       <c r="K1253" s="4" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="L1253" s="4" t="s">
         <v>1547</v>
@@ -62318,7 +62345,7 @@
         <v>1337</v>
       </c>
       <c r="K1254" s="4" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="L1254" s="4" t="s">
         <v>1547</v>
@@ -62359,7 +62386,7 @@
         <v>1337</v>
       </c>
       <c r="K1255" s="4" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="L1255" s="4" t="s">
         <v>1547</v>
@@ -62400,7 +62427,7 @@
         <v>1337</v>
       </c>
       <c r="K1256" s="4" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="L1256" s="4" t="s">
         <v>1546</v>
@@ -62441,7 +62468,7 @@
         <v>1336</v>
       </c>
       <c r="K1257" s="4" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="L1257" s="4" t="s">
         <v>1546</v>
@@ -62482,7 +62509,7 @@
         <v>1336</v>
       </c>
       <c r="K1258" s="4" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="L1258" s="4" t="s">
         <v>1546</v>
@@ -62523,7 +62550,7 @@
         <v>1336</v>
       </c>
       <c r="K1259" s="4" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="L1259" s="4" t="s">
         <v>1546</v>
@@ -62564,7 +62591,7 @@
         <v>1336</v>
       </c>
       <c r="K1260" s="4" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="L1260" s="4" t="s">
         <v>1546</v>
@@ -62605,7 +62632,7 @@
         <v>1336</v>
       </c>
       <c r="K1261" s="4" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="L1261" s="4" t="s">
         <v>1546</v>
@@ -62646,7 +62673,7 @@
         <v>1336</v>
       </c>
       <c r="K1262" s="4" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="L1262" s="4" t="s">
         <v>1546</v>
@@ -62687,7 +62714,7 @@
         <v>1336</v>
       </c>
       <c r="K1263" s="4" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="L1263" s="4" t="s">
         <v>1546</v>
@@ -62728,7 +62755,7 @@
         <v>1336</v>
       </c>
       <c r="K1264" s="4" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="L1264" s="4" t="s">
         <v>1546</v>
@@ -62769,7 +62796,7 @@
         <v>1336</v>
       </c>
       <c r="K1265" s="4" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="L1265" s="4" t="s">
         <v>1546</v>
@@ -62810,7 +62837,7 @@
         <v>1336</v>
       </c>
       <c r="K1266" s="4" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="L1266" s="4" t="s">
         <v>1546</v>
@@ -62851,7 +62878,7 @@
         <v>1336</v>
       </c>
       <c r="K1267" s="4" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="L1267" s="4" t="s">
         <v>1547</v>
@@ -62892,7 +62919,7 @@
         <v>1336</v>
       </c>
       <c r="K1268" s="4" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="L1268" s="4" t="s">
         <v>1546</v>
@@ -62933,7 +62960,7 @@
         <v>1336</v>
       </c>
       <c r="K1269" s="4" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="L1269" s="4" t="s">
         <v>1546</v>
@@ -62974,7 +63001,7 @@
         <v>1337</v>
       </c>
       <c r="K1270" s="4" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="L1270" s="4" t="s">
         <v>1547</v>
@@ -63015,7 +63042,7 @@
         <v>1337</v>
       </c>
       <c r="K1271" s="4" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="L1271" s="4" t="s">
         <v>1547</v>
@@ -63056,7 +63083,7 @@
         <v>1337</v>
       </c>
       <c r="K1272" s="4" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="L1272" s="4" t="s">
         <v>1546</v>
@@ -63097,7 +63124,7 @@
         <v>1336</v>
       </c>
       <c r="K1273" s="4" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="L1273" s="4" t="s">
         <v>1546</v>
@@ -63138,7 +63165,7 @@
         <v>1336</v>
       </c>
       <c r="K1274" s="4" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="L1274" s="4" t="s">
         <v>1546</v>
@@ -63179,7 +63206,7 @@
         <v>1337</v>
       </c>
       <c r="K1275" s="4" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="L1275" s="4" t="s">
         <v>1547</v>
@@ -63220,7 +63247,7 @@
         <v>1337</v>
       </c>
       <c r="K1276" s="4" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="L1276" s="4" t="s">
         <v>1546</v>
@@ -63261,7 +63288,7 @@
         <v>1336</v>
       </c>
       <c r="K1277" s="4" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="L1277" s="4" t="s">
         <v>1546</v>
@@ -63302,7 +63329,7 @@
         <v>1336</v>
       </c>
       <c r="K1278" s="4" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="L1278" s="4" t="s">
         <v>1546</v>
@@ -63343,7 +63370,7 @@
         <v>1336</v>
       </c>
       <c r="K1279" s="4" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="L1279" s="4" t="s">
         <v>1547</v>
@@ -63384,7 +63411,7 @@
         <v>1336</v>
       </c>
       <c r="K1280" s="4" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="L1280" s="4" t="s">
         <v>1546</v>
@@ -63425,7 +63452,7 @@
         <v>1336</v>
       </c>
       <c r="K1281" s="4" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="L1281" s="4" t="s">
         <v>1547</v>
@@ -63466,7 +63493,7 @@
         <v>1337</v>
       </c>
       <c r="K1282" s="4" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="L1282" s="4" t="s">
         <v>1546</v>
@@ -63507,7 +63534,7 @@
         <v>1337</v>
       </c>
       <c r="K1283" s="4" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="L1283" s="4" t="s">
         <v>1546</v>
@@ -63548,7 +63575,7 @@
         <v>1338</v>
       </c>
       <c r="K1284" s="4" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="L1284" s="4" t="s">
         <v>1546</v>
@@ -63589,7 +63616,7 @@
         <v>1339</v>
       </c>
       <c r="K1285" s="4" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="L1285" s="4" t="s">
         <v>1546</v>
@@ -63630,7 +63657,7 @@
         <v>1337</v>
       </c>
       <c r="K1286" s="4" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="L1286" s="4" t="s">
         <v>1546</v>
@@ -63671,7 +63698,7 @@
         <v>1337</v>
       </c>
       <c r="K1287" s="4" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="L1287" s="4" t="s">
         <v>1546</v>
@@ -63712,7 +63739,7 @@
         <v>1338</v>
       </c>
       <c r="K1288" s="4" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="L1288" s="4" t="s">
         <v>1546</v>
@@ -63753,7 +63780,7 @@
         <v>1337</v>
       </c>
       <c r="K1289" s="4" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="L1289" s="4" t="s">
         <v>1546</v>
@@ -63794,7 +63821,7 @@
         <v>1337</v>
       </c>
       <c r="K1290" s="4" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="L1290" s="4" t="s">
         <v>1546</v>
@@ -63835,7 +63862,7 @@
         <v>1337</v>
       </c>
       <c r="K1291" s="4" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="L1291" s="4" t="s">
         <v>1546</v>
@@ -63876,7 +63903,7 @@
         <v>1337</v>
       </c>
       <c r="K1292" s="4" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="L1292" s="4" t="s">
         <v>1546</v>
@@ -63917,7 +63944,7 @@
         <v>1337</v>
       </c>
       <c r="K1293" s="4" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="L1293" s="4" t="s">
         <v>1546</v>
@@ -63958,7 +63985,7 @@
         <v>1337</v>
       </c>
       <c r="K1294" s="4" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="L1294" s="4" t="s">
         <v>1546</v>
@@ -63999,7 +64026,7 @@
         <v>1338</v>
       </c>
       <c r="K1295" s="4" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="L1295" s="4" t="s">
         <v>1546</v>
@@ -64040,7 +64067,7 @@
         <v>1337</v>
       </c>
       <c r="K1296" s="4" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="L1296" s="4" t="s">
         <v>1546</v>
@@ -64081,7 +64108,7 @@
         <v>1337</v>
       </c>
       <c r="K1297" s="4" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="L1297" s="4" t="s">
         <v>1546</v>
@@ -64122,7 +64149,7 @@
         <v>1337</v>
       </c>
       <c r="K1298" s="4" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="L1298" s="4" t="s">
         <v>1546</v>
@@ -64163,7 +64190,7 @@
         <v>1337</v>
       </c>
       <c r="K1299" s="4" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="L1299" s="4" t="s">
         <v>1546</v>
@@ -64204,7 +64231,7 @@
         <v>1337</v>
       </c>
       <c r="K1300" s="4" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="L1300" s="4" t="s">
         <v>1546</v>
@@ -64245,7 +64272,7 @@
         <v>1339</v>
       </c>
       <c r="K1301" s="4" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="L1301" s="4" t="s">
         <v>1547</v>
@@ -64286,7 +64313,7 @@
         <v>1339</v>
       </c>
       <c r="K1302" s="4" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="L1302" s="4" t="s">
         <v>1547</v>
@@ -64327,7 +64354,7 @@
         <v>1339</v>
       </c>
       <c r="K1303" s="4" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="L1303" s="4" t="s">
         <v>1547</v>
@@ -64368,7 +64395,7 @@
         <v>1359</v>
       </c>
       <c r="K1304" s="4" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="L1304" s="4" t="s">
         <v>1546</v>
@@ -64450,7 +64477,7 @@
         <v>1359</v>
       </c>
       <c r="K1306" s="4" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="L1306" s="4" t="s">
         <v>1547</v>
@@ -64491,7 +64518,7 @@
         <v>1359</v>
       </c>
       <c r="K1307" s="4" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="L1307" s="4" t="s">
         <v>1547</v>
@@ -64532,7 +64559,7 @@
         <v>1359</v>
       </c>
       <c r="K1308" s="4" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="L1308" s="4" t="s">
         <v>1547</v>
@@ -64655,7 +64682,7 @@
         <v>1339</v>
       </c>
       <c r="K1311" s="4" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="L1311" s="4" t="s">
         <v>1547</v>
@@ -64696,7 +64723,7 @@
         <v>1359</v>
       </c>
       <c r="K1312" s="4" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="L1312" s="4" t="s">
         <v>1547</v>
@@ -64737,7 +64764,7 @@
         <v>1359</v>
       </c>
       <c r="K1313" s="4" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="L1313" s="4" t="s">
         <v>1547</v>
@@ -64778,7 +64805,7 @@
         <v>1339</v>
       </c>
       <c r="K1314" s="4" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="L1314" s="4" t="s">
         <v>1547</v>
@@ -64819,7 +64846,7 @@
         <v>1339</v>
       </c>
       <c r="K1315" s="4" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="L1315" s="4" t="s">
         <v>1546</v>
@@ -64860,7 +64887,7 @@
         <v>1339</v>
       </c>
       <c r="K1316" s="4" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="L1316" s="4" t="s">
         <v>1547</v>
@@ -64901,7 +64928,7 @@
         <v>1339</v>
       </c>
       <c r="K1317" s="4" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="L1317" s="4" t="s">
         <v>1547</v>
@@ -64942,7 +64969,7 @@
         <v>1359</v>
       </c>
       <c r="K1318" s="4" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="L1318" s="4" t="s">
         <v>1547</v>
@@ -64983,7 +65010,7 @@
         <v>1337</v>
       </c>
       <c r="K1319" s="4" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="L1319" s="4" t="s">
         <v>1546</v>
@@ -65024,7 +65051,7 @@
         <v>1337</v>
       </c>
       <c r="K1320" s="4" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="L1320" s="4" t="s">
         <v>1546</v>
@@ -65065,7 +65092,7 @@
         <v>1337</v>
       </c>
       <c r="K1321" s="4" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="L1321" s="4" t="s">
         <v>1546</v>
@@ -65106,7 +65133,7 @@
         <v>1338</v>
       </c>
       <c r="K1322" s="4" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="L1322" s="4" t="s">
         <v>1546</v>
@@ -65147,7 +65174,7 @@
         <v>1337</v>
       </c>
       <c r="K1323" s="4" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="L1323" s="4" t="s">
         <v>1547</v>
@@ -65188,7 +65215,7 @@
         <v>1337</v>
       </c>
       <c r="K1324" s="4" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="L1324" s="4" t="s">
         <v>1546</v>
@@ -65270,7 +65297,7 @@
         <v>1359</v>
       </c>
       <c r="K1326" s="4" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="L1326" s="4" t="s">
         <v>1546</v>
@@ -65311,7 +65338,7 @@
         <v>1337</v>
       </c>
       <c r="K1327" s="4" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="L1327" s="4" t="s">
         <v>1547</v>
@@ -65352,7 +65379,7 @@
         <v>1337</v>
       </c>
       <c r="K1328" s="4" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="L1328" s="4" t="s">
         <v>1546</v>
@@ -65393,7 +65420,7 @@
         <v>1337</v>
       </c>
       <c r="K1329" s="4" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="L1329" s="4" t="s">
         <v>1546</v>
@@ -65475,7 +65502,7 @@
         <v>1337</v>
       </c>
       <c r="K1331" s="4" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="L1331" s="4" t="s">
         <v>1546</v>
@@ -65516,7 +65543,7 @@
         <v>1337</v>
       </c>
       <c r="K1332" s="4" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="L1332" s="4" t="s">
         <v>1547</v>
@@ -65557,7 +65584,7 @@
         <v>1337</v>
       </c>
       <c r="K1333" s="4" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="L1333" s="4" t="s">
         <v>1546</v>
@@ -65598,7 +65625,7 @@
         <v>1337</v>
       </c>
       <c r="K1334" s="4" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="L1334" s="4" t="s">
         <v>1546</v>
@@ -65639,7 +65666,7 @@
         <v>1337</v>
       </c>
       <c r="K1335" s="4" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="L1335" s="4" t="s">
         <v>1547</v>
@@ -65680,7 +65707,7 @@
         <v>1337</v>
       </c>
       <c r="K1336" s="4" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="L1336" s="4" t="s">
         <v>1547</v>
@@ -65762,7 +65789,7 @@
         <v>1337</v>
       </c>
       <c r="K1338" s="4" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="L1338" s="4" t="s">
         <v>1546</v>
@@ -65803,7 +65830,7 @@
         <v>1337</v>
       </c>
       <c r="K1339" s="4" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="L1339" s="4" t="s">
         <v>1546</v>
@@ -65844,7 +65871,7 @@
         <v>1337</v>
       </c>
       <c r="K1340" s="4" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="L1340" s="4" t="s">
         <v>1546</v>
@@ -65885,7 +65912,7 @@
         <v>1337</v>
       </c>
       <c r="K1341" s="4" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="L1341" s="4" t="s">
         <v>1547</v>
@@ -65926,7 +65953,7 @@
         <v>1337</v>
       </c>
       <c r="K1342" s="4" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="L1342" s="4" t="s">
         <v>1546</v>
@@ -65967,7 +65994,7 @@
         <v>1337</v>
       </c>
       <c r="K1343" s="4" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="L1343" s="4" t="s">
         <v>1546</v>
@@ -66008,7 +66035,7 @@
         <v>1337</v>
       </c>
       <c r="K1344" s="4" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="L1344" s="4" t="s">
         <v>1547</v>
@@ -66049,7 +66076,7 @@
         <v>1338</v>
       </c>
       <c r="K1345" s="4" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="L1345" s="4" t="s">
         <v>1546</v>
@@ -66090,7 +66117,7 @@
         <v>1338</v>
       </c>
       <c r="K1346" s="4" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="L1346" s="4" t="s">
         <v>1546</v>
@@ -66131,7 +66158,7 @@
         <v>1338</v>
       </c>
       <c r="K1347" s="4" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="L1347" s="4" t="s">
         <v>1547</v>
@@ -66172,7 +66199,7 @@
         <v>1337</v>
       </c>
       <c r="K1348" s="4" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="L1348" s="4" t="s">
         <v>1547</v>
@@ -66213,7 +66240,7 @@
         <v>1337</v>
       </c>
       <c r="K1349" s="4" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="L1349" s="4" t="s">
         <v>1546</v>
@@ -66254,7 +66281,7 @@
         <v>1337</v>
       </c>
       <c r="K1350" s="4" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="L1350" s="4" t="s">
         <v>1547</v>
@@ -66295,7 +66322,7 @@
         <v>1337</v>
       </c>
       <c r="K1351" s="4" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="L1351" s="4" t="s">
         <v>1546</v>
@@ -66336,7 +66363,7 @@
         <v>1337</v>
       </c>
       <c r="K1352" s="4" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="L1352" s="4" t="s">
         <v>1546</v>
@@ -66377,7 +66404,7 @@
         <v>1338</v>
       </c>
       <c r="K1353" s="4" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="L1353" s="4" t="s">
         <v>1546</v>
@@ -66418,7 +66445,7 @@
         <v>1337</v>
       </c>
       <c r="K1354" s="4" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="L1354" s="4" t="s">
         <v>1547</v>
@@ -66459,7 +66486,7 @@
         <v>1337</v>
       </c>
       <c r="K1355" s="4" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="L1355" s="4" t="s">
         <v>1547</v>
@@ -66541,7 +66568,7 @@
         <v>1337</v>
       </c>
       <c r="K1357" s="4" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="L1357" s="4" t="s">
         <v>1546</v>
@@ -66582,7 +66609,7 @@
         <v>1337</v>
       </c>
       <c r="K1358" s="4" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="L1358" s="4" t="s">
         <v>1547</v>
@@ -66623,7 +66650,7 @@
         <v>1337</v>
       </c>
       <c r="K1359" s="4" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="L1359" s="4" t="s">
         <v>1546</v>
@@ -66664,7 +66691,7 @@
         <v>1337</v>
       </c>
       <c r="K1360" s="4" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="L1360" s="4" t="s">
         <v>1546</v>
@@ -66705,7 +66732,7 @@
         <v>1337</v>
       </c>
       <c r="K1361" s="4" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="L1361" s="4" t="s">
         <v>1546</v>
@@ -66746,7 +66773,7 @@
         <v>1338</v>
       </c>
       <c r="K1362" s="4" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="L1362" s="4" t="s">
         <v>1546</v>
@@ -66787,7 +66814,7 @@
         <v>1337</v>
       </c>
       <c r="K1363" s="4" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="L1363" s="4" t="s">
         <v>1546</v>
@@ -66828,7 +66855,7 @@
         <v>1337</v>
       </c>
       <c r="K1364" s="4" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="L1364" s="4" t="s">
         <v>1546</v>
@@ -66869,7 +66896,7 @@
         <v>1337</v>
       </c>
       <c r="K1365" s="4" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="L1365" s="4" t="s">
         <v>1546</v>
@@ -66910,7 +66937,7 @@
         <v>1337</v>
       </c>
       <c r="K1366" s="4" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="L1366" s="4" t="s">
         <v>1546</v>
@@ -66951,7 +66978,7 @@
         <v>1337</v>
       </c>
       <c r="K1367" s="4" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="L1367" s="4" t="s">
         <v>1547</v>
@@ -66992,7 +67019,7 @@
         <v>1337</v>
       </c>
       <c r="K1368" s="4" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="L1368" s="4" t="s">
         <v>1547</v>
@@ -67033,7 +67060,7 @@
         <v>1337</v>
       </c>
       <c r="K1369" s="4" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="L1369" s="4" t="s">
         <v>1546</v>
@@ -67074,7 +67101,7 @@
         <v>1338</v>
       </c>
       <c r="K1370" s="4" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="L1370" s="4" t="s">
         <v>1547</v>
@@ -67115,7 +67142,7 @@
         <v>1337</v>
       </c>
       <c r="K1371" s="4" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="L1371" s="4" t="s">
         <v>1546</v>
@@ -67156,7 +67183,7 @@
         <v>1337</v>
       </c>
       <c r="K1372" s="4" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="L1372" s="4" t="s">
         <v>1547</v>
@@ -67197,7 +67224,7 @@
         <v>1337</v>
       </c>
       <c r="K1373" s="4" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="L1373" s="4" t="s">
         <v>1546</v>
@@ -67238,7 +67265,7 @@
         <v>1337</v>
       </c>
       <c r="K1374" s="4" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="L1374" s="4" t="s">
         <v>1546</v>
@@ -67279,7 +67306,7 @@
         <v>1338</v>
       </c>
       <c r="K1375" s="4" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="L1375" s="4" t="s">
         <v>1546</v>
@@ -67320,7 +67347,7 @@
         <v>1337</v>
       </c>
       <c r="K1376" s="4" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="L1376" s="4" t="s">
         <v>1547</v>
@@ -67361,7 +67388,7 @@
         <v>1338</v>
       </c>
       <c r="K1377" s="4" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="L1377" s="4" t="s">
         <v>1546</v>
@@ -67402,7 +67429,7 @@
         <v>1337</v>
       </c>
       <c r="K1378" s="4" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="L1378" s="4" t="s">
         <v>1546</v>
@@ -67443,7 +67470,7 @@
         <v>1337</v>
       </c>
       <c r="K1379" s="4" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="L1379" s="4" t="s">
         <v>1546</v>
@@ -67484,7 +67511,7 @@
         <v>1337</v>
       </c>
       <c r="K1380" s="4" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="L1380" s="4" t="s">
         <v>1546</v>
@@ -67525,7 +67552,7 @@
         <v>1337</v>
       </c>
       <c r="K1381" s="4" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="L1381" s="4" t="s">
         <v>1546</v>
@@ -67566,7 +67593,7 @@
         <v>1337</v>
       </c>
       <c r="K1382" s="4" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="L1382" s="4" t="s">
         <v>1546</v>
@@ -67607,7 +67634,7 @@
         <v>1337</v>
       </c>
       <c r="K1383" s="4" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="L1383" s="4" t="s">
         <v>1546</v>
@@ -67648,7 +67675,7 @@
         <v>1337</v>
       </c>
       <c r="K1384" s="4" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="L1384" s="4" t="s">
         <v>1546</v>
@@ -67689,7 +67716,7 @@
         <v>1337</v>
       </c>
       <c r="K1385" s="4" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="L1385" s="4" t="s">
         <v>1546</v>
@@ -67730,7 +67757,7 @@
         <v>1337</v>
       </c>
       <c r="K1386" s="4" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="L1386" s="4" t="s">
         <v>1546</v>
@@ -67771,7 +67798,7 @@
         <v>1337</v>
       </c>
       <c r="K1387" s="4" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="L1387" s="4" t="s">
         <v>1546</v>
@@ -67853,7 +67880,7 @@
         <v>1339</v>
       </c>
       <c r="K1389" s="4" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="L1389" s="4" t="s">
         <v>1546</v>
@@ -67894,7 +67921,7 @@
         <v>1338</v>
       </c>
       <c r="K1390" s="4" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="L1390" s="4" t="s">
         <v>1546</v>
@@ -67935,7 +67962,7 @@
         <v>1339</v>
       </c>
       <c r="K1391" s="4" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="L1391" s="4" t="s">
         <v>1546</v>
@@ -67976,7 +68003,7 @@
         <v>1338</v>
       </c>
       <c r="K1392" s="4" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="L1392" s="4" t="s">
         <v>1546</v>
@@ -68017,7 +68044,7 @@
         <v>1338</v>
       </c>
       <c r="K1393" s="4" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="L1393" s="4" t="s">
         <v>1546</v>
@@ -68058,7 +68085,7 @@
         <v>1338</v>
       </c>
       <c r="K1394" s="4" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="L1394" s="4" t="s">
         <v>1546</v>
@@ -68099,7 +68126,7 @@
         <v>1337</v>
       </c>
       <c r="K1395" s="4" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="L1395" s="4" t="s">
         <v>1547</v>
@@ -68140,7 +68167,7 @@
         <v>1337</v>
       </c>
       <c r="K1396" s="4" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="L1396" s="4" t="s">
         <v>1546</v>
@@ -68181,7 +68208,7 @@
         <v>1337</v>
       </c>
       <c r="K1397" s="4" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="L1397" s="4" t="s">
         <v>1546</v>
@@ -68222,7 +68249,7 @@
         <v>1338</v>
       </c>
       <c r="K1398" s="4" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="L1398" s="4" t="s">
         <v>1546</v>
@@ -68263,7 +68290,7 @@
         <v>1337</v>
       </c>
       <c r="K1399" s="4" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="L1399" s="4" t="s">
         <v>1546</v>
@@ -68304,7 +68331,7 @@
         <v>1337</v>
       </c>
       <c r="K1400" s="4" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="L1400" s="4" t="s">
         <v>1546</v>
@@ -68345,7 +68372,7 @@
         <v>1339</v>
       </c>
       <c r="K1401" s="4" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="L1401" s="4" t="s">
         <v>1546</v>
@@ -68386,7 +68413,7 @@
         <v>1337</v>
       </c>
       <c r="K1402" s="4" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="L1402" s="4" t="s">
         <v>1546</v>
@@ -68427,7 +68454,7 @@
         <v>1337</v>
       </c>
       <c r="K1403" s="4" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="L1403" s="4" t="s">
         <v>1546</v>
@@ -68468,7 +68495,7 @@
         <v>1337</v>
       </c>
       <c r="K1404" s="4" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="L1404" s="4" t="s">
         <v>1546</v>
@@ -68509,7 +68536,7 @@
         <v>1337</v>
       </c>
       <c r="K1405" s="4" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="L1405" s="4" t="s">
         <v>1546</v>
@@ -68550,7 +68577,7 @@
         <v>1337</v>
       </c>
       <c r="K1406" s="4" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="L1406" s="4" t="s">
         <v>1547</v>
@@ -68591,7 +68618,7 @@
         <v>1337</v>
       </c>
       <c r="K1407" s="4" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="L1407" s="4" t="s">
         <v>1547</v>
@@ -68632,7 +68659,7 @@
         <v>1337</v>
       </c>
       <c r="K1408" s="4" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="L1408" s="4" t="s">
         <v>1547</v>
@@ -68673,7 +68700,7 @@
         <v>1359</v>
       </c>
       <c r="K1409" s="4" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="L1409" s="4" t="s">
         <v>1546</v>
@@ -68714,7 +68741,7 @@
         <v>1337</v>
       </c>
       <c r="K1410" s="4" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="L1410" s="4" t="s">
         <v>1546</v>
@@ -68796,7 +68823,7 @@
         <v>1337</v>
       </c>
       <c r="K1412" s="4" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="L1412" s="4" t="s">
         <v>1546</v>
@@ -68837,7 +68864,7 @@
         <v>1337</v>
       </c>
       <c r="K1413" s="4" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="L1413" s="4" t="s">
         <v>1547</v>
@@ -68878,7 +68905,7 @@
         <v>1338</v>
       </c>
       <c r="K1414" s="4" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="L1414" s="4" t="s">
         <v>1546</v>
@@ -68919,7 +68946,7 @@
         <v>1337</v>
       </c>
       <c r="K1415" s="4" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="L1415" s="4" t="s">
         <v>1546</v>
@@ -68960,7 +68987,7 @@
         <v>1337</v>
       </c>
       <c r="K1416" s="4" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="L1416" s="4" t="s">
         <v>1546</v>
@@ -69001,7 +69028,7 @@
         <v>1337</v>
       </c>
       <c r="K1417" s="4" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="L1417" s="4" t="s">
         <v>1546</v>
@@ -69042,7 +69069,7 @@
         <v>1337</v>
       </c>
       <c r="K1418" s="4" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="L1418" s="4" t="s">
         <v>1546</v>
@@ -69083,7 +69110,7 @@
         <v>1337</v>
       </c>
       <c r="K1419" s="4" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="L1419" s="4" t="s">
         <v>1546</v>
@@ -69124,7 +69151,7 @@
         <v>1337</v>
       </c>
       <c r="K1420" s="4" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="L1420" s="4" t="s">
         <v>1546</v>
@@ -69165,7 +69192,7 @@
         <v>1337</v>
       </c>
       <c r="K1421" s="4" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="L1421" s="4" t="s">
         <v>1546</v>
@@ -69206,7 +69233,7 @@
         <v>1337</v>
       </c>
       <c r="K1422" s="4" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="L1422" s="4" t="s">
         <v>1546</v>
@@ -69247,7 +69274,7 @@
         <v>1337</v>
       </c>
       <c r="K1423" s="4" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="L1423" s="4" t="s">
         <v>1546</v>
@@ -69288,7 +69315,7 @@
         <v>1337</v>
       </c>
       <c r="K1424" s="4" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="L1424" s="4" t="s">
         <v>1546</v>
@@ -69329,7 +69356,7 @@
         <v>1337</v>
       </c>
       <c r="K1425" s="4" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="L1425" s="4" t="s">
         <v>1547</v>
@@ -69370,7 +69397,7 @@
         <v>1337</v>
       </c>
       <c r="K1426" s="4" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="L1426" s="4" t="s">
         <v>1546</v>
@@ -69411,7 +69438,7 @@
         <v>1339</v>
       </c>
       <c r="K1427" s="4" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="L1427" s="4" t="s">
         <v>1546</v>
@@ -69452,7 +69479,7 @@
         <v>1337</v>
       </c>
       <c r="K1428" s="4" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="L1428" s="4" t="s">
         <v>1546</v>
@@ -69493,7 +69520,7 @@
         <v>1337</v>
       </c>
       <c r="K1429" s="4" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="L1429" s="4" t="s">
         <v>1546</v>
@@ -69534,7 +69561,7 @@
         <v>1337</v>
       </c>
       <c r="K1430" s="4" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="L1430" s="4" t="s">
         <v>1546</v>
@@ -69575,7 +69602,7 @@
         <v>1338</v>
       </c>
       <c r="K1431" s="4" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="L1431" s="4" t="s">
         <v>1546</v>
@@ -69616,7 +69643,7 @@
         <v>1337</v>
       </c>
       <c r="K1432" s="4" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="L1432" s="4" t="s">
         <v>1546</v>
@@ -69657,7 +69684,7 @@
         <v>1338</v>
       </c>
       <c r="K1433" s="4" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="L1433" s="4" t="s">
         <v>1547</v>
@@ -69698,7 +69725,7 @@
         <v>1337</v>
       </c>
       <c r="K1434" s="4" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="L1434" s="4" t="s">
         <v>1547</v>
@@ -69739,7 +69766,7 @@
         <v>1337</v>
       </c>
       <c r="K1435" s="4" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="L1435" s="4" t="s">
         <v>1546</v>
@@ -69780,7 +69807,7 @@
         <v>1337</v>
       </c>
       <c r="K1436" s="4" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="L1436" s="4" t="s">
         <v>1546</v>
@@ -69821,7 +69848,7 @@
         <v>1359</v>
       </c>
       <c r="K1437" s="4" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="L1437" s="4" t="s">
         <v>1546</v>
@@ -69862,7 +69889,7 @@
         <v>1338</v>
       </c>
       <c r="K1438" s="4" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="L1438" s="4" t="s">
         <v>1547</v>
@@ -69903,7 +69930,7 @@
         <v>1337</v>
       </c>
       <c r="K1439" s="4" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="L1439" s="4" t="s">
         <v>1546</v>
@@ -69944,7 +69971,7 @@
         <v>1338</v>
       </c>
       <c r="K1440" s="4" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="L1440" s="4" t="s">
         <v>1547</v>
@@ -69985,7 +70012,7 @@
         <v>1337</v>
       </c>
       <c r="K1441" s="4" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="L1441" s="4" t="s">
         <v>1546</v>
@@ -70026,7 +70053,7 @@
         <v>1338</v>
       </c>
       <c r="K1442" s="4" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="L1442" s="4" t="s">
         <v>1546</v>
@@ -70067,7 +70094,7 @@
         <v>1337</v>
       </c>
       <c r="K1443" s="4" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="L1443" s="4" t="s">
         <v>1546</v>
@@ -70108,7 +70135,7 @@
         <v>1337</v>
       </c>
       <c r="K1444" s="4" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="L1444" s="4" t="s">
         <v>1546</v>
@@ -70149,7 +70176,7 @@
         <v>1338</v>
       </c>
       <c r="K1445" s="4" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="L1445" s="4" t="s">
         <v>1546</v>
@@ -70190,7 +70217,7 @@
         <v>1337</v>
       </c>
       <c r="K1446" s="4" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="L1446" s="4" t="s">
         <v>1546</v>
@@ -70231,7 +70258,7 @@
         <v>1338</v>
       </c>
       <c r="K1447" s="4" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="L1447" s="4" t="s">
         <v>1546</v>
@@ -70272,7 +70299,7 @@
         <v>1337</v>
       </c>
       <c r="K1448" s="4" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="L1448" s="4" t="s">
         <v>1546</v>
@@ -70313,7 +70340,7 @@
         <v>1337</v>
       </c>
       <c r="K1449" s="4" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="L1449" s="4" t="s">
         <v>1546</v>
@@ -70354,7 +70381,7 @@
         <v>1337</v>
       </c>
       <c r="K1450" s="4" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="L1450" s="4" t="s">
         <v>1546</v>
@@ -70395,7 +70422,7 @@
         <v>1338</v>
       </c>
       <c r="K1451" s="4" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="L1451" s="4" t="s">
         <v>1546</v>
@@ -70436,7 +70463,7 @@
         <v>1337</v>
       </c>
       <c r="K1452" s="4" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="L1452" s="4" t="s">
         <v>1546</v>
@@ -70477,7 +70504,7 @@
         <v>1337</v>
       </c>
       <c r="K1453" s="4" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="L1453" s="4" t="s">
         <v>1547</v>
@@ -70518,7 +70545,7 @@
         <v>1337</v>
       </c>
       <c r="K1454" s="4" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="L1454" s="4" t="s">
         <v>1547</v>
@@ -70559,7 +70586,7 @@
         <v>1338</v>
       </c>
       <c r="K1455" s="4" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="L1455" s="4" t="s">
         <v>1546</v>
@@ -70600,7 +70627,7 @@
         <v>1337</v>
       </c>
       <c r="K1456" s="4" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="L1456" s="4" t="s">
         <v>1546</v>
@@ -70641,7 +70668,7 @@
         <v>1337</v>
       </c>
       <c r="K1457" s="4" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="L1457" s="4" t="s">
         <v>1546</v>
@@ -70682,7 +70709,7 @@
         <v>1337</v>
       </c>
       <c r="K1458" s="4" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="L1458" s="4" t="s">
         <v>1546</v>
@@ -70723,7 +70750,7 @@
         <v>1337</v>
       </c>
       <c r="K1459" s="4" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="L1459" s="4" t="s">
         <v>1546</v>
@@ -70764,7 +70791,7 @@
         <v>1337</v>
       </c>
       <c r="K1460" s="4" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="L1460" s="4" t="s">
         <v>1546</v>
@@ -70805,7 +70832,7 @@
         <v>1337</v>
       </c>
       <c r="K1461" s="4" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="L1461" s="4" t="s">
         <v>1546</v>
@@ -70846,7 +70873,7 @@
         <v>1337</v>
       </c>
       <c r="K1462" s="4" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="L1462" s="4" t="s">
         <v>1546</v>
@@ -70887,7 +70914,7 @@
         <v>1338</v>
       </c>
       <c r="K1463" s="4" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="L1463" s="4" t="s">
         <v>1546</v>
@@ -70928,7 +70955,7 @@
         <v>1337</v>
       </c>
       <c r="K1464" s="4" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="L1464" s="4" t="s">
         <v>1547</v>
@@ -70969,7 +70996,7 @@
         <v>1339</v>
       </c>
       <c r="K1465" s="4" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="L1465" s="4" t="s">
         <v>1546</v>
@@ -71297,7 +71324,7 @@
         <v>1337</v>
       </c>
       <c r="K1473" s="4" t="s">
-        <v>3378</v>
+        <v>3357</v>
       </c>
       <c r="L1473" s="4" t="s">
         <v>1547</v>
@@ -73634,7 +73661,7 @@
         <v>1337</v>
       </c>
       <c r="K1530" s="4" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="L1530" s="4" t="s">
         <v>1546</v>
@@ -73675,7 +73702,7 @@
         <v>1337</v>
       </c>
       <c r="K1531" s="4" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="L1531" s="4" t="s">
         <v>1546</v>
@@ -73716,7 +73743,7 @@
         <v>1339</v>
       </c>
       <c r="K1532" s="4" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="L1532" s="4" t="s">
         <v>1546</v>
@@ -73757,7 +73784,7 @@
         <v>1337</v>
       </c>
       <c r="K1533" s="4" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="L1533" s="4" t="s">
         <v>1546</v>
@@ -73798,7 +73825,7 @@
         <v>1337</v>
       </c>
       <c r="K1534" s="4" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="L1534" s="4" t="s">
         <v>1546</v>
@@ -73962,7 +73989,7 @@
         <v>1359</v>
       </c>
       <c r="K1538" s="4" t="s">
-        <v>3379</v>
+        <v>3358</v>
       </c>
       <c r="L1538" s="4" t="s">
         <v>1546</v>
@@ -74249,7 +74276,7 @@
         <v>1338</v>
       </c>
       <c r="K1545" s="4" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="L1545" s="4" t="s">
         <v>1546</v>
@@ -74331,7 +74358,7 @@
         <v>1337</v>
       </c>
       <c r="K1547" s="4" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="L1547" s="4" t="s">
         <v>1546</v>
@@ -74372,7 +74399,7 @@
         <v>1337</v>
       </c>
       <c r="K1548" s="4" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="L1548" s="4" t="s">
         <v>1546</v>
@@ -74413,7 +74440,7 @@
         <v>1337</v>
       </c>
       <c r="K1549" s="4" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="L1549" s="4" t="s">
         <v>1546</v>
@@ -74454,7 +74481,7 @@
         <v>1338</v>
       </c>
       <c r="K1550" s="4" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="L1550" s="4" t="s">
         <v>1546</v>
@@ -74495,7 +74522,7 @@
         <v>1338</v>
       </c>
       <c r="K1551" s="4" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="L1551" s="4" t="s">
         <v>1547</v>
@@ -74536,7 +74563,7 @@
         <v>1337</v>
       </c>
       <c r="K1552" s="4" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="L1552" s="4" t="s">
         <v>1546</v>
@@ -74577,7 +74604,7 @@
         <v>1338</v>
       </c>
       <c r="K1553" s="4" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="L1553" s="4" t="s">
         <v>1546</v>
@@ -74618,7 +74645,7 @@
         <v>1337</v>
       </c>
       <c r="K1554" s="4" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="L1554" s="4" t="s">
         <v>1547</v>
@@ -74659,7 +74686,7 @@
         <v>1337</v>
       </c>
       <c r="K1555" s="4" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="L1555" s="4" t="s">
         <v>1546</v>
@@ -74700,7 +74727,7 @@
         <v>1338</v>
       </c>
       <c r="K1556" s="4" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="L1556" s="4" t="s">
         <v>1546</v>
@@ -74741,7 +74768,7 @@
         <v>1337</v>
       </c>
       <c r="K1557" s="4" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="L1557" s="4" t="s">
         <v>1546</v>
@@ -74782,7 +74809,7 @@
         <v>1337</v>
       </c>
       <c r="K1558" s="4" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="L1558" s="4" t="s">
         <v>1546</v>
@@ -74823,7 +74850,7 @@
         <v>1338</v>
       </c>
       <c r="K1559" s="4" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="L1559" s="4" t="s">
         <v>1546</v>
@@ -74864,7 +74891,7 @@
         <v>1337</v>
       </c>
       <c r="K1560" s="4" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="L1560" s="4" t="s">
         <v>1547</v>
@@ -74905,7 +74932,7 @@
         <v>1337</v>
       </c>
       <c r="K1561" s="4" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="L1561" s="4" t="s">
         <v>1546</v>
@@ -74946,7 +74973,7 @@
         <v>1337</v>
       </c>
       <c r="K1562" s="4" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="L1562" s="4" t="s">
         <v>1547</v>
@@ -74987,7 +75014,7 @@
         <v>1337</v>
       </c>
       <c r="K1563" s="4" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="L1563" s="4" t="s">
         <v>1546</v>
@@ -75069,7 +75096,7 @@
         <v>1338</v>
       </c>
       <c r="K1565" s="4" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="L1565" s="4" t="s">
         <v>1546</v>
@@ -75151,7 +75178,7 @@
         <v>1337</v>
       </c>
       <c r="K1567" s="4" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="L1567" s="4" t="s">
         <v>1546</v>
@@ -75192,7 +75219,7 @@
         <v>1338</v>
       </c>
       <c r="K1568" s="4" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="L1568" s="4" t="s">
         <v>1546</v>
@@ -75233,7 +75260,7 @@
         <v>1337</v>
       </c>
       <c r="K1569" s="4" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="L1569" s="4" t="s">
         <v>1547</v>
@@ -75274,7 +75301,7 @@
         <v>1337</v>
       </c>
       <c r="K1570" s="4" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="L1570" s="4" t="s">
         <v>1546</v>
@@ -75315,7 +75342,7 @@
         <v>1338</v>
       </c>
       <c r="K1571" s="4" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="L1571" s="4" t="s">
         <v>1546</v>
@@ -75356,7 +75383,7 @@
         <v>1338</v>
       </c>
       <c r="K1572" s="4" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="L1572" s="4" t="s">
         <v>1547</v>
@@ -75397,7 +75424,7 @@
         <v>1337</v>
       </c>
       <c r="K1573" s="4" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="L1573" s="4" t="s">
         <v>1546</v>
@@ -75438,7 +75465,7 @@
         <v>1337</v>
       </c>
       <c r="K1574" s="4" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="L1574" s="4" t="s">
         <v>1546</v>
@@ -75479,7 +75506,7 @@
         <v>1337</v>
       </c>
       <c r="K1575" s="4" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="L1575" s="4" t="s">
         <v>1546</v>
@@ -75520,7 +75547,7 @@
         <v>1339</v>
       </c>
       <c r="K1576" s="4" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="L1576" s="4" t="s">
         <v>1546</v>
@@ -75561,7 +75588,7 @@
         <v>1337</v>
       </c>
       <c r="K1577" s="4" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="L1577" s="4" t="s">
         <v>1546</v>
@@ -75602,7 +75629,7 @@
         <v>1337</v>
       </c>
       <c r="K1578" s="4" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="L1578" s="4" t="s">
         <v>1546</v>
@@ -75643,7 +75670,7 @@
         <v>1337</v>
       </c>
       <c r="K1579" s="4" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="L1579" s="4" t="s">
         <v>1547</v>
@@ -75684,7 +75711,7 @@
         <v>1337</v>
       </c>
       <c r="K1580" s="4" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="L1580" s="4" t="s">
         <v>1546</v>
@@ -75725,7 +75752,7 @@
         <v>1337</v>
       </c>
       <c r="K1581" s="4" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="L1581" s="4" t="s">
         <v>1546</v>
@@ -75766,7 +75793,7 @@
         <v>1337</v>
       </c>
       <c r="K1582" s="4" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="L1582" s="4" t="s">
         <v>1546</v>
@@ -75807,7 +75834,7 @@
         <v>1338</v>
       </c>
       <c r="K1583" s="4" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="L1583" s="4" t="s">
         <v>1546</v>
@@ -75848,7 +75875,7 @@
         <v>1337</v>
       </c>
       <c r="K1584" s="4" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="L1584" s="4" t="s">
         <v>1546</v>
@@ -75889,7 +75916,7 @@
         <v>1359</v>
       </c>
       <c r="K1585" s="4" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="L1585" s="4" t="s">
         <v>1546</v>
@@ -75930,7 +75957,7 @@
         <v>1339</v>
       </c>
       <c r="K1586" s="4" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="L1586" s="4" t="s">
         <v>1546</v>
@@ -75971,7 +75998,7 @@
         <v>1337</v>
       </c>
       <c r="K1587" s="4" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="L1587" s="4" t="s">
         <v>1547</v>
@@ -76012,7 +76039,7 @@
         <v>1338</v>
       </c>
       <c r="K1588" s="4" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="L1588" s="4" t="s">
         <v>1546</v>
@@ -76053,7 +76080,7 @@
         <v>1337</v>
       </c>
       <c r="K1589" s="4" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="L1589" s="4" t="s">
         <v>1547</v>
@@ -76094,7 +76121,7 @@
         <v>1338</v>
       </c>
       <c r="K1590" s="4" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="L1590" s="4" t="s">
         <v>1546</v>
@@ -76135,7 +76162,7 @@
         <v>1337</v>
       </c>
       <c r="K1591" s="4" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="L1591" s="4" t="s">
         <v>1546</v>
@@ -76176,7 +76203,7 @@
         <v>1337</v>
       </c>
       <c r="K1592" s="4" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="L1592" s="4" t="s">
         <v>1546</v>
@@ -76217,7 +76244,7 @@
         <v>1337</v>
       </c>
       <c r="K1593" s="4" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="L1593" s="4" t="s">
         <v>1547</v>
@@ -76258,7 +76285,7 @@
         <v>1338</v>
       </c>
       <c r="K1594" s="4" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="L1594" s="4" t="s">
         <v>1546</v>
@@ -76299,7 +76326,7 @@
         <v>1337</v>
       </c>
       <c r="K1595" s="4" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="L1595" s="4" t="s">
         <v>1546</v>
@@ -76340,7 +76367,7 @@
         <v>1337</v>
       </c>
       <c r="K1596" s="4" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="L1596" s="4" t="s">
         <v>1546</v>
@@ -76381,7 +76408,7 @@
         <v>1337</v>
       </c>
       <c r="K1597" s="4" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="L1597" s="4" t="s">
         <v>1546</v>
@@ -76422,7 +76449,7 @@
         <v>1337</v>
       </c>
       <c r="K1598" s="4" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="L1598" s="4" t="s">
         <v>1547</v>
@@ -76463,7 +76490,7 @@
         <v>1337</v>
       </c>
       <c r="K1599" s="4" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="L1599" s="4" t="s">
         <v>1547</v>
@@ -76504,7 +76531,7 @@
         <v>1337</v>
       </c>
       <c r="K1600" s="4" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="L1600" s="4" t="s">
         <v>1546</v>
@@ -76545,7 +76572,7 @@
         <v>1337</v>
       </c>
       <c r="K1601" s="4" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="L1601" s="4" t="s">
         <v>1547</v>
@@ -76559,10 +76586,10 @@
         <v>623</v>
       </c>
       <c r="B1602" s="4" t="s">
-        <v>1227</v>
+        <v>1315</v>
       </c>
       <c r="C1602" s="4">
-        <v>152204</v>
+        <v>153268</v>
       </c>
       <c r="D1602" s="2">
         <v>46296</v>
@@ -76571,13 +76598,13 @@
         <v>13</v>
       </c>
       <c r="F1602" s="4" t="s">
-        <v>2606</v>
+        <v>2595</v>
       </c>
       <c r="G1602" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1602" s="4" t="s">
-        <v>948</v>
+        <v>16</v>
       </c>
       <c r="I1602" s="4" t="s">
         <v>1308</v>
@@ -76586,13 +76613,13 @@
         <v>1337</v>
       </c>
       <c r="K1602" s="4" t="s">
-        <v>3357</v>
+        <v>3364</v>
       </c>
       <c r="L1602" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="M1602" s="4" t="s">
-        <v>2544</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="1603" spans="1:13" x14ac:dyDescent="0.25">
@@ -76603,7 +76630,7 @@
         <v>1315</v>
       </c>
       <c r="C1603" s="4">
-        <v>153268</v>
+        <v>139312</v>
       </c>
       <c r="D1603" s="2">
         <v>46296</v>
@@ -76612,13 +76639,13 @@
         <v>13</v>
       </c>
       <c r="F1603" s="4" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="G1603" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1603" s="4" t="s">
-        <v>948</v>
+        <v>16</v>
       </c>
       <c r="I1603" s="4" t="s">
         <v>1308</v>
@@ -76627,13 +76654,13 @@
         <v>1337</v>
       </c>
       <c r="K1603" s="4" t="s">
-        <v>3358</v>
+        <v>3365</v>
       </c>
       <c r="L1603" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1603" s="4" t="s">
-        <v>2486</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="1604" spans="1:13" x14ac:dyDescent="0.25">
@@ -76644,16 +76671,16 @@
         <v>1315</v>
       </c>
       <c r="C1604" s="4">
-        <v>139312</v>
+        <v>154874</v>
       </c>
       <c r="D1604" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E1604" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F1604" s="4" t="s">
-        <v>2596</v>
+        <v>3359</v>
       </c>
       <c r="G1604" s="4" t="s">
         <v>15</v>
@@ -76668,13 +76695,13 @@
         <v>1337</v>
       </c>
       <c r="K1604" s="4" t="s">
-        <v>3359</v>
+        <v>3366</v>
       </c>
       <c r="L1604" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1604" s="4" t="s">
-        <v>2410</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="1605" spans="1:13" x14ac:dyDescent="0.25">
@@ -76709,7 +76736,7 @@
         <v>1339</v>
       </c>
       <c r="K1605" s="4" t="s">
-        <v>3360</v>
+        <v>3367</v>
       </c>
       <c r="L1605" s="4" t="s">
         <v>1546</v>
@@ -76726,7 +76753,7 @@
         <v>1315</v>
       </c>
       <c r="C1606" s="4">
-        <v>150739</v>
+        <v>138735</v>
       </c>
       <c r="D1606" s="2">
         <v>46298</v>
@@ -76735,13 +76762,13 @@
         <v>13</v>
       </c>
       <c r="F1606" s="4" t="s">
-        <v>2598</v>
+        <v>3360</v>
       </c>
       <c r="G1606" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H1606" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I1606" s="4" t="s">
         <v>1308</v>
@@ -76750,13 +76777,13 @@
         <v>1337</v>
       </c>
       <c r="K1606" s="4" t="s">
-        <v>3361</v>
+        <v>3368</v>
       </c>
       <c r="L1606" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="M1606" s="4" t="s">
-        <v>2602</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="1607" spans="1:13" x14ac:dyDescent="0.25">
@@ -76767,22 +76794,22 @@
         <v>1315</v>
       </c>
       <c r="C1607" s="4">
-        <v>155418</v>
+        <v>150739</v>
       </c>
       <c r="D1607" s="2">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E1607" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F1607" s="4" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="G1607" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H1607" s="4" t="s">
-        <v>948</v>
+        <v>46</v>
       </c>
       <c r="I1607" s="4" t="s">
         <v>1308</v>
@@ -76791,13 +76818,13 @@
         <v>1337</v>
       </c>
       <c r="K1607" s="4" t="s">
-        <v>3362</v>
+        <v>3369</v>
       </c>
       <c r="L1607" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1607" s="4" t="s">
-        <v>2486</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="1608" spans="1:13" x14ac:dyDescent="0.25">
@@ -76805,40 +76832,40 @@
         <v>629</v>
       </c>
       <c r="B1608" s="4" t="s">
-        <v>1315</v>
+        <v>1227</v>
       </c>
       <c r="C1608" s="4">
-        <v>152748</v>
+        <v>148521</v>
       </c>
       <c r="D1608" s="2">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="E1608" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F1608" s="4" t="s">
-        <v>2600</v>
+        <v>3361</v>
       </c>
       <c r="G1608" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1608" s="4" t="s">
-        <v>16</v>
+        <v>948</v>
       </c>
       <c r="I1608" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1608" s="4" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="K1608" s="4" t="s">
-        <v>3363</v>
+        <v>3370</v>
       </c>
       <c r="L1608" s="4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="M1608" s="4" t="s">
-        <v>2494</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="1609" spans="1:13" x14ac:dyDescent="0.25">
@@ -76846,34 +76873,34 @@
         <v>630</v>
       </c>
       <c r="B1609" s="4" t="s">
-        <v>1227</v>
+        <v>1315</v>
       </c>
       <c r="C1609" s="4">
-        <v>156293</v>
+        <v>155418</v>
       </c>
       <c r="D1609" s="2">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="E1609" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F1609" s="4" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="G1609" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1609" s="4" t="s">
-        <v>18</v>
+        <v>948</v>
       </c>
       <c r="I1609" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1609" s="4" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="K1609" s="4" t="s">
-        <v>3364</v>
+        <v>3371</v>
       </c>
       <c r="L1609" s="4" t="s">
         <v>1546</v>
@@ -76890,7 +76917,7 @@
         <v>1315</v>
       </c>
       <c r="C1610" s="4">
-        <v>147960</v>
+        <v>152748</v>
       </c>
       <c r="D1610" s="2">
         <v>46300</v>
@@ -76899,28 +76926,28 @@
         <v>13</v>
       </c>
       <c r="F1610" s="4" t="s">
-        <v>3380</v>
+        <v>2600</v>
       </c>
       <c r="G1610" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H1610" s="4" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="I1610" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1610" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K1610" s="4" t="s">
-        <v>3365</v>
+        <v>3372</v>
       </c>
       <c r="L1610" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="M1610" s="4" t="s">
-        <v>2484</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="1611" spans="1:13" x14ac:dyDescent="0.25">
@@ -76931,7 +76958,7 @@
         <v>1227</v>
       </c>
       <c r="C1611" s="4">
-        <v>156377</v>
+        <v>156293</v>
       </c>
       <c r="D1611" s="2">
         <v>46300</v>
@@ -76940,22 +76967,22 @@
         <v>13</v>
       </c>
       <c r="F1611" s="4" t="s">
-        <v>2607</v>
+        <v>2601</v>
       </c>
       <c r="G1611" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H1611" s="4" t="s">
-        <v>392</v>
+        <v>18</v>
       </c>
       <c r="I1611" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1611" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K1611" s="4" t="s">
-        <v>3366</v>
+        <v>3373</v>
       </c>
       <c r="L1611" s="4" t="s">
         <v>1546</v>
@@ -76972,7 +76999,7 @@
         <v>1315</v>
       </c>
       <c r="C1612" s="4">
-        <v>156132</v>
+        <v>147960</v>
       </c>
       <c r="D1612" s="2">
         <v>46300</v>
@@ -76981,28 +77008,28 @@
         <v>13</v>
       </c>
       <c r="F1612" s="4" t="s">
-        <v>2608</v>
+        <v>3362</v>
       </c>
       <c r="G1612" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H1612" s="4" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="I1612" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1612" s="4" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="K1612" s="4" t="s">
-        <v>3367</v>
+        <v>3374</v>
       </c>
       <c r="L1612" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="M1612" s="4" t="s">
-        <v>2413</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="1613" spans="1:13" x14ac:dyDescent="0.25">
@@ -77010,25 +77037,25 @@
         <v>634</v>
       </c>
       <c r="B1613" s="4" t="s">
-        <v>1315</v>
+        <v>1227</v>
       </c>
       <c r="C1613" s="4">
-        <v>152514</v>
+        <v>156377</v>
       </c>
       <c r="D1613" s="2">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="E1613" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F1613" s="4" t="s">
-        <v>2609</v>
+        <v>2606</v>
       </c>
       <c r="G1613" s="4" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H1613" s="4" t="s">
-        <v>40</v>
+        <v>392</v>
       </c>
       <c r="I1613" s="4" t="s">
         <v>1308</v>
@@ -77037,13 +77064,13 @@
         <v>1337</v>
       </c>
       <c r="K1613" s="4" t="s">
-        <v>3368</v>
+        <v>3375</v>
       </c>
       <c r="L1613" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1613" s="4" t="s">
-        <v>2604</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="1614" spans="1:13" x14ac:dyDescent="0.25">
@@ -77054,37 +77081,37 @@
         <v>1315</v>
       </c>
       <c r="C1614" s="4">
-        <v>151254</v>
+        <v>156132</v>
       </c>
       <c r="D1614" s="2">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="E1614" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F1614" s="4" t="s">
-        <v>2610</v>
+        <v>2607</v>
       </c>
       <c r="G1614" s="4" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H1614" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="I1614" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1614" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K1614" s="4" t="s">
-        <v>3369</v>
+        <v>3376</v>
       </c>
       <c r="L1614" s="4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="M1614" s="4" t="s">
-        <v>2509</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="1615" spans="1:13" x14ac:dyDescent="0.25">
@@ -77095,22 +77122,22 @@
         <v>1315</v>
       </c>
       <c r="C1615" s="4">
-        <v>143724</v>
+        <v>147098</v>
       </c>
       <c r="D1615" s="2">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="E1615" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F1615" s="4" t="s">
-        <v>2611</v>
+        <v>3363</v>
       </c>
       <c r="G1615" s="4" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H1615" s="4" t="s">
-        <v>948</v>
+        <v>216</v>
       </c>
       <c r="I1615" s="4" t="s">
         <v>1308</v>
@@ -77119,13 +77146,13 @@
         <v>1337</v>
       </c>
       <c r="K1615" s="4" t="s">
-        <v>3370</v>
+        <v>3377</v>
       </c>
       <c r="L1615" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1615" s="4" t="s">
-        <v>2520</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="1616" spans="1:13" x14ac:dyDescent="0.25">
@@ -77133,10 +77160,10 @@
         <v>637</v>
       </c>
       <c r="B1616" s="4" t="s">
-        <v>1227</v>
+        <v>1315</v>
       </c>
       <c r="C1616" s="4">
-        <v>155841</v>
+        <v>152514</v>
       </c>
       <c r="D1616" s="2">
         <v>46301</v>
@@ -77145,13 +77172,13 @@
         <v>13</v>
       </c>
       <c r="F1616" s="4" t="s">
-        <v>2612</v>
+        <v>2608</v>
       </c>
       <c r="G1616" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1616" s="4" t="s">
-        <v>948</v>
+        <v>40</v>
       </c>
       <c r="I1616" s="4" t="s">
         <v>1308</v>
@@ -77160,16 +77187,16 @@
         <v>1337</v>
       </c>
       <c r="K1616" s="4" t="s">
-        <v>3371</v>
+        <v>3378</v>
       </c>
       <c r="L1616" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1616" s="4" t="s">
-        <v>2520</v>
-      </c>
-    </row>
-    <row r="1617" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1617" s="4">
         <v>638</v>
       </c>
@@ -77177,7 +77204,7 @@
         <v>1315</v>
       </c>
       <c r="C1617" s="4">
-        <v>147491</v>
+        <v>151254</v>
       </c>
       <c r="D1617" s="2">
         <v>46301</v>
@@ -77185,29 +77212,29 @@
       <c r="E1617" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F1617" s="5" t="s">
-        <v>2613</v>
+      <c r="F1617" s="4" t="s">
+        <v>2609</v>
       </c>
       <c r="G1617" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1617" s="4" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I1617" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1617" s="4" t="s">
-        <v>1359</v>
+        <v>1337</v>
       </c>
       <c r="K1617" s="4" t="s">
-        <v>3372</v>
+        <v>3379</v>
       </c>
       <c r="L1617" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="M1617" s="4" t="s">
-        <v>2605</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1618" spans="1:13" x14ac:dyDescent="0.25">
@@ -77218,7 +77245,7 @@
         <v>1315</v>
       </c>
       <c r="C1618" s="4">
-        <v>157479</v>
+        <v>143724</v>
       </c>
       <c r="D1618" s="2">
         <v>46301</v>
@@ -77227,13 +77254,13 @@
         <v>13</v>
       </c>
       <c r="F1618" s="4" t="s">
-        <v>2614</v>
+        <v>2610</v>
       </c>
       <c r="G1618" s="4" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H1618" s="4" t="s">
-        <v>133</v>
+        <v>948</v>
       </c>
       <c r="I1618" s="4" t="s">
         <v>1308</v>
@@ -77242,13 +77269,13 @@
         <v>1337</v>
       </c>
       <c r="K1618" s="4" t="s">
-        <v>3373</v>
+        <v>3380</v>
       </c>
       <c r="L1618" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1618" s="4" t="s">
-        <v>2486</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="1619" spans="1:13" x14ac:dyDescent="0.25">
@@ -77259,7 +77286,7 @@
         <v>1227</v>
       </c>
       <c r="C1619" s="4">
-        <v>159040</v>
+        <v>155841</v>
       </c>
       <c r="D1619" s="2">
         <v>46301</v>
@@ -77268,13 +77295,13 @@
         <v>13</v>
       </c>
       <c r="F1619" s="4" t="s">
-        <v>2615</v>
+        <v>2611</v>
       </c>
       <c r="G1619" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H1619" s="4" t="s">
-        <v>18</v>
+        <v>948</v>
       </c>
       <c r="I1619" s="4" t="s">
         <v>1308</v>
@@ -77283,13 +77310,13 @@
         <v>1337</v>
       </c>
       <c r="K1619" s="4" t="s">
-        <v>3374</v>
+        <v>3381</v>
       </c>
       <c r="L1619" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1619" s="4" t="s">
-        <v>2493</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="1620" spans="1:13" x14ac:dyDescent="0.25">
@@ -77300,7 +77327,7 @@
         <v>1315</v>
       </c>
       <c r="C1620" s="4">
-        <v>152033</v>
+        <v>147491</v>
       </c>
       <c r="D1620" s="2">
         <v>46301</v>
@@ -77309,7 +77336,7 @@
         <v>13</v>
       </c>
       <c r="F1620" s="4" t="s">
-        <v>2616</v>
+        <v>2612</v>
       </c>
       <c r="G1620" s="4" t="s">
         <v>15</v>
@@ -77321,16 +77348,16 @@
         <v>1308</v>
       </c>
       <c r="J1620" s="4" t="s">
-        <v>1337</v>
+        <v>1359</v>
       </c>
       <c r="K1620" s="4" t="s">
-        <v>3375</v>
+        <v>3382</v>
       </c>
       <c r="L1620" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1620" s="4" t="s">
-        <v>2412</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="1621" spans="1:13" x14ac:dyDescent="0.25">
@@ -77341,7 +77368,7 @@
         <v>1315</v>
       </c>
       <c r="C1621" s="4">
-        <v>158233</v>
+        <v>157479</v>
       </c>
       <c r="D1621" s="2">
         <v>46301</v>
@@ -77350,28 +77377,28 @@
         <v>13</v>
       </c>
       <c r="F1621" s="4" t="s">
-        <v>2617</v>
+        <v>2613</v>
       </c>
       <c r="G1621" s="4" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H1621" s="4" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="I1621" s="4" t="s">
         <v>1308</v>
       </c>
       <c r="J1621" s="4" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="K1621" s="4" t="s">
-        <v>3376</v>
+        <v>3383</v>
       </c>
       <c r="L1621" s="4" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="M1621" s="4" t="s">
-        <v>2494</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="1622" spans="1:13" x14ac:dyDescent="0.25">
@@ -77379,10 +77406,10 @@
         <v>643</v>
       </c>
       <c r="B1622" s="4" t="s">
-        <v>1315</v>
+        <v>1227</v>
       </c>
       <c r="C1622" s="4">
-        <v>152891</v>
+        <v>159040</v>
       </c>
       <c r="D1622" s="2">
         <v>46301</v>
@@ -77391,13 +77418,13 @@
         <v>13</v>
       </c>
       <c r="F1622" s="4" t="s">
-        <v>2618</v>
+        <v>2614</v>
       </c>
       <c r="G1622" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H1622" s="4" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I1622" s="4" t="s">
         <v>1308</v>
@@ -77406,12 +77433,135 @@
         <v>1337</v>
       </c>
       <c r="K1622" s="4" t="s">
-        <v>3377</v>
+        <v>3384</v>
       </c>
       <c r="L1622" s="4" t="s">
         <v>1547</v>
       </c>
       <c r="M1622" s="4" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1623" s="4">
+        <v>644</v>
+      </c>
+      <c r="B1623" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1623" s="4">
+        <v>152033</v>
+      </c>
+      <c r="D1623" s="2">
+        <v>46301</v>
+      </c>
+      <c r="E1623" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1623" s="4" t="s">
+        <v>2615</v>
+      </c>
+      <c r="G1623" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1623" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1623" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1623" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1623" s="4" t="s">
+        <v>3356</v>
+      </c>
+      <c r="L1623" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1623" s="4" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1624" s="4">
+        <v>645</v>
+      </c>
+      <c r="B1624" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1624" s="4">
+        <v>158233</v>
+      </c>
+      <c r="D1624" s="2">
+        <v>46301</v>
+      </c>
+      <c r="E1624" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1624" s="4" t="s">
+        <v>2616</v>
+      </c>
+      <c r="G1624" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1624" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1624" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1624" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1624" s="4" t="s">
+        <v>3385</v>
+      </c>
+      <c r="L1624" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1624" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1625" s="4">
+        <v>646</v>
+      </c>
+      <c r="B1625" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1625" s="4">
+        <v>152891</v>
+      </c>
+      <c r="D1625" s="2">
+        <v>46301</v>
+      </c>
+      <c r="E1625" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1625" s="4" t="s">
+        <v>2617</v>
+      </c>
+      <c r="G1625" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1625" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1625" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1625" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1625" s="4" t="s">
+        <v>3386</v>
+      </c>
+      <c r="L1625" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1625" s="4" t="s">
         <v>2494</v>
       </c>
     </row>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2716" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26A3224E-F964-4036-90E8-448D27AEF531}"/>
+  <xr:revisionPtr revIDLastSave="2823" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0845E1C-C723-4542-BC4D-36F593934B1A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1570</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16290" uniqueCount="3387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16326" uniqueCount="3396">
   <si>
     <t>ID</t>
   </si>
@@ -10466,6 +10466,34 @@
   </si>
   <si>
     <t>não ajustou fluxo, estava vazando + sem ferramenta</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demora para limpeza do filtro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marquei a visita do  técnico para a manutenção técnica do purificador e ele não veio
+</t>
+  </si>
+  <si>
+    <t>Desde que a Culligan assumiu só tive problemas. Ficaram 3 meses sem cobrar, não avisaram do atraso, depois mudaram o dia do pagamento e fiquei novamente em atraso pois não fui informada e na data X ñao tinha dinheiro na conta, Mandaram Whatsapp para marcar a manutenção, chegou no dia não veio ninguém. Tudo isso qdo reclamo falam que eh erro do sistema. E outra, antes podíamos marcar a manutenção e/ou problema com uma no max estourando 2 semanas. Agora para marcar a manutenção é um mês pra frente. O que está havendo? Sou cliente a mais de 10 anos da Brastemp e na gestão Whillor (ANTERIOR A CULLIGAN) isso não acontecia! Péssima troca. Péssima troca!!!! Precisam rever isso. E vou averiguar agora, se nnao vou.ve cobrança em duplicidade, pq nunca vi uma empresa mudar data de pagamento em debito automático sem avisar, sem notificar. Péssimo , péssimo!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque desde que o purificador brastemp que  tenho a mais de 10 anos passou para a Culligan , nada funciona , as marcações de visita não são respeitadas , a cobrança saiu do débito automático e não mandam o boleto para pagamento. Já solicitei várias vezes e só consigo falar com robô . </t>
+  </si>
+  <si>
+    <t>FRQ SANTOS SP R02</t>
+  </si>
+  <si>
+    <t>Financeiro</t>
+  </si>
+  <si>
+    <t>Problemas no Faturamento</t>
   </si>
 </sst>
 </file>
@@ -10921,7 +10949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1625"/>
+  <dimension ref="A1:M1629"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -17315,10 +17343,10 @@
         <v>190</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I156" s="4" t="s">
         <v>1307</v>
@@ -22153,10 +22181,10 @@
         <v>310</v>
       </c>
       <c r="G274" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I274" s="4" t="s">
         <v>1307</v>
@@ -22276,10 +22304,10 @@
         <v>313</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>25</v>
+        <v>3394</v>
       </c>
       <c r="H277" s="4" t="s">
-        <v>26</v>
+        <v>3395</v>
       </c>
       <c r="I277" s="4" t="s">
         <v>1307</v>
@@ -34822,10 +34850,10 @@
         <v>619</v>
       </c>
       <c r="G583" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H583" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I583" s="4" t="s">
         <v>1307</v>
@@ -35724,10 +35752,10 @@
         <v>641</v>
       </c>
       <c r="G605" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H605" s="4" t="s">
-        <v>392</v>
+        <v>3395</v>
       </c>
       <c r="I605" s="4" t="s">
         <v>1307</v>
@@ -37077,10 +37105,10 @@
         <v>673</v>
       </c>
       <c r="G638" s="4" t="s">
-        <v>25</v>
+        <v>3394</v>
       </c>
       <c r="H638" s="4" t="s">
-        <v>26</v>
+        <v>3395</v>
       </c>
       <c r="I638" s="4" t="s">
         <v>1307</v>
@@ -43473,10 +43501,10 @@
         <v>829</v>
       </c>
       <c r="G794" s="4" t="s">
-        <v>134</v>
+        <v>3394</v>
       </c>
       <c r="H794" s="4" t="s">
-        <v>158</v>
+        <v>3395</v>
       </c>
       <c r="I794" s="4" t="s">
         <v>1307</v>
@@ -44949,10 +44977,10 @@
         <v>864</v>
       </c>
       <c r="G830" s="4" t="s">
-        <v>15</v>
+        <v>3394</v>
       </c>
       <c r="H830" s="4" t="s">
-        <v>40</v>
+        <v>3395</v>
       </c>
       <c r="I830" s="4" t="s">
         <v>1307</v>
@@ -45851,10 +45879,10 @@
         <v>886</v>
       </c>
       <c r="G852" s="4" t="s">
-        <v>28</v>
+        <v>3394</v>
       </c>
       <c r="H852" s="4" t="s">
-        <v>200</v>
+        <v>3395</v>
       </c>
       <c r="I852" s="4" t="s">
         <v>1307</v>
@@ -46056,10 +46084,10 @@
         <v>891</v>
       </c>
       <c r="G857" s="4" t="s">
-        <v>15</v>
+        <v>3394</v>
       </c>
       <c r="H857" s="4" t="s">
-        <v>18</v>
+        <v>3395</v>
       </c>
       <c r="I857" s="4" t="s">
         <v>1307</v>
@@ -48106,10 +48134,10 @@
         <v>941</v>
       </c>
       <c r="G907" s="4" t="s">
-        <v>51</v>
+        <v>3394</v>
       </c>
       <c r="H907" s="4" t="s">
-        <v>2769</v>
+        <v>3395</v>
       </c>
       <c r="I907" s="4" t="s">
         <v>1307</v>
@@ -53928,10 +53956,10 @@
         <v>1082</v>
       </c>
       <c r="G1049" s="4" t="s">
-        <v>15</v>
+        <v>3394</v>
       </c>
       <c r="H1049" s="4" t="s">
-        <v>40</v>
+        <v>3395</v>
       </c>
       <c r="I1049" s="4" t="s">
         <v>1307</v>
@@ -54051,10 +54079,10 @@
         <v>1085</v>
       </c>
       <c r="G1052" s="4" t="s">
-        <v>15</v>
+        <v>3394</v>
       </c>
       <c r="H1052" s="4" t="s">
-        <v>948</v>
+        <v>3395</v>
       </c>
       <c r="I1052" s="4" t="s">
         <v>1307</v>
@@ -56224,10 +56252,10 @@
         <v>1137</v>
       </c>
       <c r="G1105" s="4" t="s">
-        <v>11</v>
+        <v>3394</v>
       </c>
       <c r="H1105" s="4" t="s">
-        <v>21</v>
+        <v>3395</v>
       </c>
       <c r="I1105" s="4" t="s">
         <v>1307</v>
@@ -56429,10 +56457,10 @@
         <v>1142</v>
       </c>
       <c r="G1110" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1110" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I1110" s="4" t="s">
         <v>1307</v>
@@ -58971,10 +58999,10 @@
         <v>1203</v>
       </c>
       <c r="G1172" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1172" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1172" s="4" t="s">
         <v>1307</v>
@@ -62333,10 +62361,10 @@
         <v>1284</v>
       </c>
       <c r="G1254" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1254" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1254" s="4" t="s">
         <v>1308</v>
@@ -63358,10 +63386,10 @@
         <v>1312</v>
       </c>
       <c r="G1279" s="4" t="s">
-        <v>15</v>
+        <v>3394</v>
       </c>
       <c r="H1279" s="4" t="s">
-        <v>18</v>
+        <v>3395</v>
       </c>
       <c r="I1279" s="4" t="s">
         <v>1307</v>
@@ -63891,10 +63919,10 @@
         <v>1326</v>
       </c>
       <c r="G1292" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1292" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1292" s="4" t="s">
         <v>1308</v>
@@ -65162,10 +65190,10 @@
         <v>1365</v>
       </c>
       <c r="G1323" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1323" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1323" s="4" t="s">
         <v>1308</v>
@@ -65613,10 +65641,10 @@
         <v>1376</v>
       </c>
       <c r="G1334" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1334" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1334" s="4" t="s">
         <v>1308</v>
@@ -66351,10 +66379,10 @@
         <v>1394</v>
       </c>
       <c r="G1352" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1352" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1352" s="4" t="s">
         <v>1308</v>
@@ -67007,10 +67035,10 @@
         <v>1410</v>
       </c>
       <c r="G1368" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1368" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I1368" s="4" t="s">
         <v>1308</v>
@@ -67540,10 +67568,10 @@
         <v>1417</v>
       </c>
       <c r="G1381" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1381" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1381" s="4" t="s">
         <v>1422</v>
@@ -68114,10 +68142,10 @@
         <v>1439</v>
       </c>
       <c r="G1395" s="4" t="s">
-        <v>15</v>
+        <v>3394</v>
       </c>
       <c r="H1395" s="4" t="s">
-        <v>18</v>
+        <v>3395</v>
       </c>
       <c r="I1395" s="4" t="s">
         <v>1308</v>
@@ -68278,10 +68306,10 @@
         <v>1443</v>
       </c>
       <c r="G1399" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1399" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I1399" s="4" t="s">
         <v>1308</v>
@@ -68606,10 +68634,10 @@
         <v>1451</v>
       </c>
       <c r="G1407" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1407" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1407" s="4" t="s">
         <v>1308</v>
@@ -68688,10 +68716,10 @@
         <v>1453</v>
       </c>
       <c r="G1409" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1409" s="4" t="s">
-        <v>392</v>
+        <v>3395</v>
       </c>
       <c r="I1409" s="4" t="s">
         <v>1308</v>
@@ -69180,10 +69208,10 @@
         <v>1467</v>
       </c>
       <c r="G1421" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1421" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I1421" s="4" t="s">
         <v>1308</v>
@@ -69344,10 +69372,10 @@
         <v>1460</v>
       </c>
       <c r="G1425" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1425" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I1425" s="4" t="s">
         <v>1308</v>
@@ -70861,10 +70889,10 @@
         <v>1508</v>
       </c>
       <c r="G1462" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1462" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I1462" s="4" t="s">
         <v>1308</v>
@@ -71107,10 +71135,10 @@
         <v>1515</v>
       </c>
       <c r="G1468" s="4" t="s">
-        <v>15</v>
+        <v>3394</v>
       </c>
       <c r="H1468" s="4" t="s">
-        <v>948</v>
+        <v>3395</v>
       </c>
       <c r="I1468" s="4" t="s">
         <v>1308</v>
@@ -73157,10 +73185,10 @@
         <v>1611</v>
       </c>
       <c r="G1518" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1518" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I1518" s="4" t="s">
         <v>1308</v>
@@ -74756,10 +74784,10 @@
         <v>2536</v>
       </c>
       <c r="G1557" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1557" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1557" s="4" t="s">
         <v>1308</v>
@@ -75289,10 +75317,10 @@
         <v>2554</v>
       </c>
       <c r="G1570" s="4" t="s">
-        <v>28</v>
+        <v>3394</v>
       </c>
       <c r="H1570" s="4" t="s">
-        <v>81</v>
+        <v>3395</v>
       </c>
       <c r="I1570" s="4" t="s">
         <v>1308</v>
@@ -75740,10 +75768,10 @@
         <v>2569</v>
       </c>
       <c r="G1581" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1581" s="4" t="s">
-        <v>66</v>
+        <v>3395</v>
       </c>
       <c r="I1581" s="4" t="s">
         <v>1308</v>
@@ -76232,10 +76260,10 @@
         <v>2585</v>
       </c>
       <c r="G1593" s="4" t="s">
-        <v>65</v>
+        <v>3394</v>
       </c>
       <c r="H1593" s="4" t="s">
-        <v>133</v>
+        <v>3395</v>
       </c>
       <c r="I1593" s="4" t="s">
         <v>1308</v>
@@ -76314,10 +76342,10 @@
         <v>2587</v>
       </c>
       <c r="G1595" s="4" t="s">
-        <v>25</v>
+        <v>3394</v>
       </c>
       <c r="H1595" s="4" t="s">
-        <v>26</v>
+        <v>3395</v>
       </c>
       <c r="I1595" s="4" t="s">
         <v>1308</v>
@@ -77298,10 +77326,10 @@
         <v>2611</v>
       </c>
       <c r="G1619" s="4" t="s">
-        <v>15</v>
+        <v>3394</v>
       </c>
       <c r="H1619" s="4" t="s">
-        <v>948</v>
+        <v>3395</v>
       </c>
       <c r="I1619" s="4" t="s">
         <v>1308</v>
@@ -77565,7 +77593,136 @@
         <v>2494</v>
       </c>
     </row>
+    <row r="1626" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1626" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1626" s="4">
+        <v>158917</v>
+      </c>
+      <c r="D1626" s="2" t="s">
+        <v>3387</v>
+      </c>
+      <c r="E1626" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1626" s="4" t="s">
+        <v>3389</v>
+      </c>
+      <c r="G1626" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1626" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1626" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1626" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1626" s="4" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1627" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1627" s="4">
+        <v>159122</v>
+      </c>
+      <c r="D1627" s="2" t="s">
+        <v>3387</v>
+      </c>
+      <c r="E1627" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1627" s="4" t="s">
+        <v>3390</v>
+      </c>
+      <c r="G1627" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1627" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1627" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1627" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1627" s="4" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1628" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1628" s="4">
+        <v>161524</v>
+      </c>
+      <c r="D1628" s="2" t="s">
+        <v>3387</v>
+      </c>
+      <c r="E1628" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1628" s="4" t="s">
+        <v>3391</v>
+      </c>
+      <c r="G1628" s="4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="H1628" s="4" t="s">
+        <v>3395</v>
+      </c>
+      <c r="I1628" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1628" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1628" s="4" t="s">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1629" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1629" s="4">
+        <v>160872</v>
+      </c>
+      <c r="D1629" s="2" t="s">
+        <v>3388</v>
+      </c>
+      <c r="E1629" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1629" s="4" t="s">
+        <v>3392</v>
+      </c>
+      <c r="G1629" s="4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="H1629" s="4" t="s">
+        <v>3395</v>
+      </c>
+      <c r="I1629" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1629" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1629" s="4" t="s">
+        <v>2410</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:M1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2848" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AD39BB3-6A9B-4E0A-8035-F5C485078235}"/>
+  <xr:revisionPtr revIDLastSave="2867" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ADB7116-F99D-4A6D-B1FA-5DE68608FF84}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16366" uniqueCount="3402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16624" uniqueCount="3459">
   <si>
     <t>ID</t>
   </si>
@@ -10519,6 +10519,190 @@
   </si>
   <si>
     <t>campo</t>
+  </si>
+  <si>
+    <t>FRQ BRASILIA DF R04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O filtro instalado já foi instalado com defeito e a troca do filtro só será feita dia 20 tenho 2 idosos em casa </t>
+  </si>
+  <si>
+    <t>Pela segunda vez seguida, a visita e manutenção foi marcada para o horário da tarde e o técnico apareceu pela manhã. Na primeira vez, no ano passado, foi necessário remarcar. Neste ano, por acaso tinha alguém em casa, que pôde acompanhar a visita.</t>
+  </si>
+  <si>
+    <t>Hoje o técnico compareceu em nossa unidade para realizar a preventiva apenas de "1 purificador" os outros 2 ficaram sem reparo, a etiqueta consta vencido em setembro; Ficamos no aguardo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde que passou para a Culligan e tiraram o pagamento do débito automático, tenho tido problemas para pagar a mensalidade. É trabalhoso, desgastante, muito tempo esperando ao telefone, tocando m[usica, antes de transferir para o financeiro, 10:07, atendem e nao conseguem me enviar  boleto do pagamento.´e muito estressante. Quando atendem, desligam o telefone!!
+Hoje,neste momento. é a terceira vez que ligo, Evely, Samuel e outra atendente, última agoa. esqueci o nome, mal conseguia falar, caia a ligação ou eles desligaram o telefone!
+É uma falta de respeito e consideração um atendimento ao cliente,como esse. Obrigada. </t>
+  </si>
+  <si>
+    <t>Pq meu problema não foi resolvido, e o técnico solicitou a troca do aparelho, que foi agendado para o dia 24/10. 
+Até lá vamos ficar sem usar o purificador.
+Porque não está saindo agua gelada,  nem fria, e a natural esta quente.</t>
+  </si>
+  <si>
+    <t>A data disponível para agendamento de visita técnica destinada a conserto de um defeito foi muito distante. Pedi prioridade mas não atenderam, embora seja um bom e antigo cliente. Fiquei uma semana sem utilizar o purificador e tive gasto com a compra de água mineral.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A água não está saindo gelado EA natural está saindo quente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devido ao atendimento da area juridica - contratos.
+Quando da mudança de Brastemp para Culligan nos orientaram a fazer um adendo ao contrato.
+Gerou-se esforços desnecessários, pois aoi final do processo uma das pessoas da Culligan não assinou o documento e informaram que não era mais necessário.
+Essa situação foi muito desagradável.
+Quanto ao produto locado não tenho qualquer comentário.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não cumpriram o horário da visita para manutenção, além do que não trouxeram o equipamento para resolver a baixa pressão. </t>
+  </si>
+  <si>
+    <t>Foi uma técnica fazer a visita periódica no dia 25/09, disse que só fez o teste da água, mas desde que ela saiu, o filtro na sai água na opção gelada e bem na com gás. Só foi possível marcar outra visita para o dia 02/10. O técnico disse que tinha queimado alguma coisa e disse que trocou. Porém continua com os mesmos problemas. Liguei para pedir uma visita com urgência e só consegui agendar para o dia 08/10. Ou seja, vai totalizar 2 semanas sem água gelada (motivo pelo qual fechei com vocês) e nessa visita vai acabar sendo a mesma coisa, vai vir uma pessoa, trocar uma coisinha e cair fora. Eles não esperam a água gelada sair para ir embora e ver que realmente deu certo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eu avaliei o atendimento com um especialista com o máximo,  porém expliquei que reformei a cozinha e que tinha que reinstalar o purificador. Chegou o técnico apenas para manutenção. Provei pela conversa no WhatsApp que não era só manutenção.  Tempo perdido. A OS era só manutenção! Sem obs alguma inclusive que a mangueira deveria ter 1,5m. NÃO FOI FEITA A MANUTENÇÃO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Além de todos os problemas até a data da manutenção, no dia marcado o horário não foi cumprido. Atenção parece que o funcionário não foi culpado pois segundo ele havia grande número de visitas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chegou antes do horário agendado </t>
+  </si>
+  <si>
+    <t>Foi muito estranho!!!! Agendei pelo WhatsApp p dia 13 out pela manhã e vieram sem avisar no dia 8 out!!!!</t>
+  </si>
+  <si>
+    <t>As manutenções regulares não foram realizadas nas datas agendas por 3 vezes seguidas. A visita foi realizada apenas após eu tentar cancelar o serviço.  O técnico veio realizar a visita em um dia diferente do combinado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intalou mas deu vazamento em baixo </t>
+  </si>
+  <si>
+    <t>Atendimento muito impessoal, não ouve o cliente, fiz um agendamento de rotina, chegou aqui um  técnico que tinha um chamado de manutenção, não fez nada, abriu e fechou a torneira e foi embora, não tenho certeza se esse filtro precisa ou não de reparo, o técnico se quer pode explicar tamanha a pressa que ele tinha de sair.</t>
+  </si>
+  <si>
+    <t>O serviço não foi realizado. Agendei entre 13 e 18hs, o técnico apareceu as 12hs, fora do horário marcado. Marquei após as 13hs justamente porque não podia atender antes. Solicitei ao porteiro que informasse ao técnico a impossibilidade, e que o mesmo retornasse ao intervalo anteriormente marcado, o que não aconteceu.  Péssimo serviço!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demoram demais para fazer visita e quando fazem sempre falam que não precisa trocar o filtro. Engraçado.. se eu tivesse que comprar.. teria que trocar de 3 em 3 meses. Como pago mensalidade, querem trocar 1 vez por ano e olhe lá. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pq pela 4a, 5a vez já havia solicitado a "troca do aparelho", conf minha assinatura + de 08 anos e sempre a mesma desculpa, o técnico chega diz que n tem nenhuma observação p troca, q a mesma deve ser solicitada etc...a história se repete, o tempo passa, meu aparelho talvez nem tenha + atualização, peças de substituição s demoradas. Essa mensagem n diz respeito aos atendimentos pessoais, os técnicos enviados n tem culpa, eles simplesmente atendem o que é passado e exatamente o que passam como simples manutenção que deve ser reavaliado. No mesmo dia, 3 reclamações no mesmo condominio, pelo mesmo motivo . </t>
+  </si>
+  <si>
+    <t>Eu gosto do filtro e da qualidade ! A minha nota diz respeito a visita que é agendada, porém o técnico não cumpre o horário, já é a segunda vez que isso ocorre! Na visita anterior ele não veio tive que reagendar. Hj, qdo reclamei, recebi uma ligação e logo em seguida o interfone tocou dizendo que ele havia chegado, muito estranho isso, ele trocou o filtro em menos de 5 minutos! A gente desmarca compromissos e fica esperando. Melhor vcs agendarem um horário e não um período, facilitaria muito.</t>
+  </si>
+  <si>
+    <t>Péssima qualidade na comunicação entre funcionários e clientes. Qto ao purificador é ótimo mas o funcionamento da empresa NÃO É BOM! São enrolados. O funcionário veio aqui trocar o filtro e a água não está como das outras vezes.... tá com gosto ruim. Vou esperar mais uns 2 dias p ver se melhora o gosto.</t>
+  </si>
+  <si>
+    <t>Olá!
+O atendimento foi bom, porém fiquei bastante insatisfeito com a substituição do equipamento. O aparelho disponibilizado, além de ser recondicionado, é de um modelo inferior ao que eu tinha anteriormente, o que considero uma perda na qualidade do serviço contratado.
+Dessa forma, peço que avaliem a situação e considerem a possibilidade de retornar com o modelo do equipamento anterior, pois, nas condições atuais, não estou satisfeito com o serviço da Brastemp Culligan.
+Caso não seja possível solucionar essa questão, infelizmente terei que cancelar minha assinatura.
+Aguardo um retorno e uma solução para o caso. Obrigado.</t>
+  </si>
+  <si>
+    <t>demora para limpeza do filtro</t>
+  </si>
+  <si>
+    <t>marquei a visita e ele não veio</t>
+  </si>
+  <si>
+    <t>mudaram data do débito + visita não veio + agenda distante</t>
+  </si>
+  <si>
+    <t>saiu do débito automático, sem boleto + visitas não respeitadas</t>
+  </si>
+  <si>
+    <t>filtro não é mais trocado semestralmente</t>
+  </si>
+  <si>
+    <t>serviço não ficou perfeito (genérico)</t>
+  </si>
+  <si>
+    <t>ninguém apareceu no segundo endereço</t>
+  </si>
+  <si>
+    <t>troca só dia 20 + instalado com defeito</t>
+  </si>
+  <si>
+    <t>marcado à tarde, apareceu pela manhã</t>
+  </si>
+  <si>
+    <t>preventiva de apenas 1 de 3 purificadores</t>
+  </si>
+  <si>
+    <t>tiraram débito automático + atendimento telefônico ruim</t>
+  </si>
+  <si>
+    <t>troca agendada só 24/10 + não gela</t>
+  </si>
+  <si>
+    <t>data para visita técnica muito distante</t>
+  </si>
+  <si>
+    <t>"Bom" (comentário positivo, nota detratora)</t>
+  </si>
+  <si>
+    <t>água não sai gelada, natural quente</t>
+  </si>
+  <si>
+    <t>orientaram adendo, depois não era necessário</t>
+  </si>
+  <si>
+    <t>não trouxeram equipamento + horário não cumprido</t>
+  </si>
+  <si>
+    <t>continua com os mesmos problemas + agenda 08/10 + só testou</t>
+  </si>
+  <si>
+    <t>OS só manutenção, pedido era reinstalação</t>
+  </si>
+  <si>
+    <t>no dia marcado o horário não foi cumprido</t>
+  </si>
+  <si>
+    <t>chegou antes do horário agendado</t>
+  </si>
+  <si>
+    <t>agendado dia 13, vieram sem avisar dia 8</t>
+  </si>
+  <si>
+    <t>não realizadas nas datas 3 vezes + dia diferente</t>
+  </si>
+  <si>
+    <t>instalou mas deu vazamento embaixo</t>
+  </si>
+  <si>
+    <t>abriu e fechou a torneira e foi embora</t>
+  </si>
+  <si>
+    <t>técnico apareceu às 12h, fora do horário</t>
+  </si>
+  <si>
+    <t>não trocam o filtro + demora na visita</t>
+  </si>
+  <si>
+    <t>pela 4ª, 5ª vez solicitei a troca</t>
+  </si>
+  <si>
+    <t>técnico não cumpre horário + não veio antes + 5 min</t>
+  </si>
+  <si>
+    <t>gosto ruim após troca do filtro + comunicação ruim</t>
+  </si>
+  <si>
+    <t>recondicionado e modelo inferior ao anterior</t>
+  </si>
+  <si>
+    <t>parou de gelar após a visita + ruído</t>
+  </si>
+  <si>
+    <t>mangueira insuficiente + promessa na venda</t>
   </si>
 </sst>
 </file>
@@ -10974,7 +11158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1634"/>
+  <dimension ref="A1:M1658"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -77649,6 +77833,12 @@
       <c r="J1626" s="4" t="s">
         <v>1338</v>
       </c>
+      <c r="K1626" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="L1626" s="4" t="s">
+        <v>1547</v>
+      </c>
       <c r="M1626" s="4" t="s">
         <v>2487</v>
       </c>
@@ -77684,6 +77874,12 @@
       <c r="J1627" s="4" t="s">
         <v>1337</v>
       </c>
+      <c r="K1627" s="4" t="s">
+        <v>3427</v>
+      </c>
+      <c r="L1627" s="4" t="s">
+        <v>1546</v>
+      </c>
       <c r="M1627" s="4" t="s">
         <v>2495</v>
       </c>
@@ -77719,6 +77915,12 @@
       <c r="J1628" s="4" t="s">
         <v>1337</v>
       </c>
+      <c r="K1628" s="4" t="s">
+        <v>3428</v>
+      </c>
+      <c r="L1628" s="4" t="s">
+        <v>1547</v>
+      </c>
       <c r="M1628" s="4" t="s">
         <v>3393</v>
       </c>
@@ -77754,6 +77956,12 @@
       <c r="J1629" s="4" t="s">
         <v>1337</v>
       </c>
+      <c r="K1629" s="4" t="s">
+        <v>3429</v>
+      </c>
+      <c r="L1629" s="4" t="s">
+        <v>1547</v>
+      </c>
       <c r="M1629" s="4" t="s">
         <v>2410</v>
       </c>
@@ -77789,6 +77997,12 @@
       <c r="J1630" s="4" t="s">
         <v>1337</v>
       </c>
+      <c r="K1630" s="4" t="s">
+        <v>3430</v>
+      </c>
+      <c r="L1630" s="4" t="s">
+        <v>1546</v>
+      </c>
       <c r="M1630" s="4" t="s">
         <v>2485</v>
       </c>
@@ -77824,6 +78038,12 @@
       <c r="J1631" s="4" t="s">
         <v>1337</v>
       </c>
+      <c r="K1631" s="4" t="s">
+        <v>3431</v>
+      </c>
+      <c r="L1631" s="4" t="s">
+        <v>1547</v>
+      </c>
       <c r="M1631" s="4" t="s">
         <v>2492</v>
       </c>
@@ -77859,6 +78079,12 @@
       <c r="J1632" s="4" t="s">
         <v>1337</v>
       </c>
+      <c r="K1632" s="4" t="s">
+        <v>3432</v>
+      </c>
+      <c r="L1632" s="4" t="s">
+        <v>1546</v>
+      </c>
       <c r="M1632" s="4" t="s">
         <v>2494</v>
       </c>
@@ -77894,6 +78120,12 @@
       <c r="J1633" s="4" t="s">
         <v>1337</v>
       </c>
+      <c r="K1633" s="4" t="s">
+        <v>3457</v>
+      </c>
+      <c r="L1633" s="4" t="s">
+        <v>1547</v>
+      </c>
       <c r="M1633" s="4" t="s">
         <v>2512</v>
       </c>
@@ -77929,12 +78161,1001 @@
       <c r="J1634" s="4" t="s">
         <v>1337</v>
       </c>
+      <c r="K1634" s="4" t="s">
+        <v>3458</v>
+      </c>
+      <c r="L1634" s="4" t="s">
+        <v>1547</v>
+      </c>
       <c r="M1634" s="4" t="s">
         <v>2495</v>
       </c>
     </row>
+    <row r="1635" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1635" s="4">
+        <v>656</v>
+      </c>
+      <c r="B1635" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1635" s="4">
+        <v>162940</v>
+      </c>
+      <c r="D1635" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1635" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1635" s="4" t="s">
+        <v>3403</v>
+      </c>
+      <c r="G1635" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1635" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1635" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1635" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1635" s="4" t="s">
+        <v>3433</v>
+      </c>
+      <c r="L1635" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1635" s="4" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1636" s="4">
+        <v>657</v>
+      </c>
+      <c r="B1636" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1636" s="4">
+        <v>160726</v>
+      </c>
+      <c r="D1636" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1636" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1636" s="4" t="s">
+        <v>3404</v>
+      </c>
+      <c r="G1636" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1636" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1636" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1636" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1636" s="4" t="s">
+        <v>3434</v>
+      </c>
+      <c r="L1636" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1636" s="4" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1637" s="4">
+        <v>658</v>
+      </c>
+      <c r="B1637" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1637" s="4">
+        <v>162386</v>
+      </c>
+      <c r="D1637" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1637" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1637" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="G1637" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1637" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1637" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1637" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K1637" s="4" t="s">
+        <v>3435</v>
+      </c>
+      <c r="L1637" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1637" s="4" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1638" s="4">
+        <v>659</v>
+      </c>
+      <c r="B1638" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1638" s="4">
+        <v>150173</v>
+      </c>
+      <c r="D1638" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1638" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1638" s="4" t="s">
+        <v>3406</v>
+      </c>
+      <c r="G1638" s="4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="H1638" s="4" t="s">
+        <v>3395</v>
+      </c>
+      <c r="I1638" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1638" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1638" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="L1638" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1638" s="4" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1639" s="4">
+        <v>660</v>
+      </c>
+      <c r="B1639" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1639" s="4">
+        <v>160209</v>
+      </c>
+      <c r="D1639" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1639" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1639" s="4" t="s">
+        <v>3407</v>
+      </c>
+      <c r="G1639" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1639" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1639" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1639" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1639" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="L1639" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1639" s="4" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1640" s="4">
+        <v>661</v>
+      </c>
+      <c r="B1640" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1640" s="4">
+        <v>158919</v>
+      </c>
+      <c r="D1640" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1640" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1640" s="4" t="s">
+        <v>3408</v>
+      </c>
+      <c r="G1640" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1640" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1640" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1640" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1640" s="4" t="s">
+        <v>3438</v>
+      </c>
+      <c r="L1640" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1640" s="4" t="s">
+        <v>3402</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1641" s="4">
+        <v>662</v>
+      </c>
+      <c r="B1641" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1641" s="4">
+        <v>159170</v>
+      </c>
+      <c r="D1641" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1641" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1641" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="G1641" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1641" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1641" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1641" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1641" s="4" t="s">
+        <v>3439</v>
+      </c>
+      <c r="L1641" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1641" s="4" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1642" s="4">
+        <v>663</v>
+      </c>
+      <c r="B1642" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1642" s="4">
+        <v>161157</v>
+      </c>
+      <c r="D1642" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1642" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1642" s="4" t="s">
+        <v>3409</v>
+      </c>
+      <c r="G1642" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1642" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1642" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1642" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1642" s="4" t="s">
+        <v>3440</v>
+      </c>
+      <c r="L1642" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1642" s="4" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1643" s="4">
+        <v>664</v>
+      </c>
+      <c r="B1643" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1643" s="4">
+        <v>62155</v>
+      </c>
+      <c r="D1643" s="2">
+        <v>46304</v>
+      </c>
+      <c r="E1643" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1643" s="4" t="s">
+        <v>3410</v>
+      </c>
+      <c r="G1643" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1643" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1643" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1643" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1643" s="4" t="s">
+        <v>3441</v>
+      </c>
+      <c r="L1643" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1643" s="4" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1644" s="4">
+        <v>665</v>
+      </c>
+      <c r="B1644" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1644" s="4">
+        <v>151848</v>
+      </c>
+      <c r="D1644" s="2">
+        <v>46305</v>
+      </c>
+      <c r="E1644" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1644" s="4" t="s">
+        <v>3411</v>
+      </c>
+      <c r="G1644" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1644" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1644" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1644" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1644" s="4" t="s">
+        <v>3442</v>
+      </c>
+      <c r="L1644" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1644" s="4" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1645" s="4">
+        <v>666</v>
+      </c>
+      <c r="B1645" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1645" s="4">
+        <v>154245</v>
+      </c>
+      <c r="D1645" s="2">
+        <v>46305</v>
+      </c>
+      <c r="E1645" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1645" s="4" t="s">
+        <v>3412</v>
+      </c>
+      <c r="G1645" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1645" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1645" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1645" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1645" s="4" t="s">
+        <v>3443</v>
+      </c>
+      <c r="L1645" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1645" s="4" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1646" s="4">
+        <v>667</v>
+      </c>
+      <c r="B1646" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1646" s="4">
+        <v>158163</v>
+      </c>
+      <c r="D1646" s="2">
+        <v>46305</v>
+      </c>
+      <c r="E1646" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1646" s="4" t="s">
+        <v>3413</v>
+      </c>
+      <c r="G1646" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1646" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1646" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1646" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1646" s="4" t="s">
+        <v>3444</v>
+      </c>
+      <c r="L1646" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1646" s="4" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1647" s="4">
+        <v>668</v>
+      </c>
+      <c r="B1647" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1647" s="4">
+        <v>65384</v>
+      </c>
+      <c r="D1647" s="2">
+        <v>46305</v>
+      </c>
+      <c r="E1647" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1647" s="4" t="s">
+        <v>3414</v>
+      </c>
+      <c r="G1647" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1647" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1647" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1647" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K1647" s="4" t="s">
+        <v>3445</v>
+      </c>
+      <c r="L1647" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1647" s="4" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1648" s="4">
+        <v>669</v>
+      </c>
+      <c r="B1648" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1648" s="4">
+        <v>161441</v>
+      </c>
+      <c r="D1648" s="2">
+        <v>46306</v>
+      </c>
+      <c r="E1648" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1648" s="4" t="s">
+        <v>3415</v>
+      </c>
+      <c r="G1648" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1648" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1648" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1648" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1648" s="4" t="s">
+        <v>3446</v>
+      </c>
+      <c r="L1648" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1648" s="4" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1649" s="4">
+        <v>670</v>
+      </c>
+      <c r="B1649" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1649" s="4">
+        <v>162410</v>
+      </c>
+      <c r="D1649" s="2">
+        <v>46307</v>
+      </c>
+      <c r="E1649" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1649" s="4" t="s">
+        <v>3416</v>
+      </c>
+      <c r="G1649" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1649" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1649" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1649" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1649" s="4" t="s">
+        <v>3447</v>
+      </c>
+      <c r="L1649" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1649" s="4" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1650" s="4">
+        <v>671</v>
+      </c>
+      <c r="B1650" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1650" s="4">
+        <v>164338</v>
+      </c>
+      <c r="D1650" s="2">
+        <v>46307</v>
+      </c>
+      <c r="E1650" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1650" s="4" t="s">
+        <v>3417</v>
+      </c>
+      <c r="G1650" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1650" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1650" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1650" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1650" s="4" t="s">
+        <v>3448</v>
+      </c>
+      <c r="L1650" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1650" s="4" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1651" s="4">
+        <v>672</v>
+      </c>
+      <c r="B1651" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1651" s="4">
+        <v>150983</v>
+      </c>
+      <c r="D1651" s="2">
+        <v>46307</v>
+      </c>
+      <c r="E1651" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1651" s="4" t="s">
+        <v>3418</v>
+      </c>
+      <c r="G1651" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1651" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1651" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1651" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1651" s="4" t="s">
+        <v>3449</v>
+      </c>
+      <c r="L1651" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1651" s="4" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1652" s="4">
+        <v>673</v>
+      </c>
+      <c r="B1652" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1652" s="4">
+        <v>158923</v>
+      </c>
+      <c r="D1652" s="2">
+        <v>46308</v>
+      </c>
+      <c r="E1652" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1652" s="4" t="s">
+        <v>3419</v>
+      </c>
+      <c r="G1652" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1652" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1652" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1652" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1652" s="4" t="s">
+        <v>3450</v>
+      </c>
+      <c r="L1652" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1652" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1653" s="4">
+        <v>674</v>
+      </c>
+      <c r="B1653" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1653" s="4">
+        <v>161620</v>
+      </c>
+      <c r="D1653" s="2">
+        <v>46308</v>
+      </c>
+      <c r="E1653" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1653" s="4" t="s">
+        <v>3420</v>
+      </c>
+      <c r="G1653" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1653" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1653" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1653" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1653" s="4" t="s">
+        <v>3451</v>
+      </c>
+      <c r="L1653" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1653" s="4" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1654" s="4">
+        <v>675</v>
+      </c>
+      <c r="B1654" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1654" s="4">
+        <v>152917</v>
+      </c>
+      <c r="D1654" s="2">
+        <v>46308</v>
+      </c>
+      <c r="E1654" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1654" s="4" t="s">
+        <v>3421</v>
+      </c>
+      <c r="G1654" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1654" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1654" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1654" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1654" s="4" t="s">
+        <v>3452</v>
+      </c>
+      <c r="L1654" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1654" s="4" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1655" s="4">
+        <v>676</v>
+      </c>
+      <c r="B1655" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1655" s="4">
+        <v>166349</v>
+      </c>
+      <c r="D1655" s="2">
+        <v>46308</v>
+      </c>
+      <c r="E1655" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1655" s="4" t="s">
+        <v>3422</v>
+      </c>
+      <c r="G1655" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1655" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1655" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1655" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1655" s="4" t="s">
+        <v>3453</v>
+      </c>
+      <c r="L1655" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1655" s="4" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1656" s="4">
+        <v>677</v>
+      </c>
+      <c r="B1656" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1656" s="4">
+        <v>159125</v>
+      </c>
+      <c r="D1656" s="2">
+        <v>46308</v>
+      </c>
+      <c r="E1656" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1656" s="4" t="s">
+        <v>3423</v>
+      </c>
+      <c r="G1656" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1656" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1656" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1656" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1656" s="4" t="s">
+        <v>3454</v>
+      </c>
+      <c r="L1656" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1656" s="4" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1657" s="4">
+        <v>678</v>
+      </c>
+      <c r="B1657" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1657" s="4">
+        <v>158303</v>
+      </c>
+      <c r="D1657" s="2">
+        <v>46308</v>
+      </c>
+      <c r="E1657" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1657" s="4" t="s">
+        <v>3424</v>
+      </c>
+      <c r="G1657" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1657" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1657" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1657" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1657" s="4" t="s">
+        <v>3455</v>
+      </c>
+      <c r="L1657" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1657" s="4" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1658" s="4">
+        <v>679</v>
+      </c>
+      <c r="B1658" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1658" s="4">
+        <v>164987</v>
+      </c>
+      <c r="D1658" s="2">
+        <v>46308</v>
+      </c>
+      <c r="E1658" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1658" s="5" t="s">
+        <v>3425</v>
+      </c>
+      <c r="G1658" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1658" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1658" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1658" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1658" s="4" t="s">
+        <v>3456</v>
+      </c>
+      <c r="L1658" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1658" s="4" t="s">
+        <v>2517</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2867" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ADB7116-F99D-4A6D-B1FA-5DE68608FF84}"/>
+  <xr:revisionPtr revIDLastSave="2902" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B672193D-AC02-42EE-B637-71757D2F66C7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16624" uniqueCount="3459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16704" uniqueCount="3474">
   <si>
     <t>ID</t>
   </si>
@@ -10518,9 +10518,6 @@
 Frustrante isso ! </t>
   </si>
   <si>
-    <t>campo</t>
-  </si>
-  <si>
     <t>FRQ BRASILIA DF R04</t>
   </si>
   <si>
@@ -10703,6 +10700,58 @@
   </si>
   <si>
     <t>mangueira insuficiente + promessa na venda</t>
+  </si>
+  <si>
+    <t>Meu problema nao foi resolvido. Existe uma mistura de assuntos tecnicos com assuntos financeiros. Enfim estou bem desanimada e provavelmente eu desista do serviço.</t>
+  </si>
+  <si>
+    <t>O processo de agendamento de manutenção tem se mostrado bastante moroso. A Culligan não possui um controle proativo das manutenções, fazendo com que seja necessário um acompanhamento constante da nossa parte para que os agendamentos sejam realizados.
+Hoje foi efetuada a manutenção para troca dos filtros dos bebedouros. No entanto, apesar de possuirmos três equipamentos, foi aberta apenas uma Ordem de Serviço (O.S.), quando o correto seria a abertura de uma O.S. para cada bebedouro atendido.
+Ressalto que não houve qualquer problema em relação ao técnico responsável pelo atendimento. O serviço foi executado de forma adequada, e o profissional demonstrou ser extremamente educado, cordial e prestativo durante toda a manutenção.</t>
+  </si>
+  <si>
+    <t>Apesar das manutenções em dia, um dia saiu uma larva viva junto com a agua. TIve uma dificuldade absurda de marcar direito uma manutenção. No dia que o tecnico veio ele não sabia o que fazer (eu não estava em casa, mas a central DEVERIA TER PASSADO AS INFORMAÇÕES). Que experiência patética.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nao sei ainda se está consertado! Vou aguardar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Técnico não  reparou o filtro e, além disso, terminou de quebra-lo! Foi embora e me deixou com o filtro quebrado e sem água. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muita demora no atendimento e profissional vai despreparado para fazer possíveis reparos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não apareceu ninguém para fazer a manutenção, e nossa loja é aberta das 10;00 as 22;00h, todos os dias da semana!!! um verdadeiro descaso por parte de vcs.
+grato! </t>
+  </si>
+  <si>
+    <t>A empresa apresentou problemas no sistema de cobrança e ao invés de comunicar claramente e resolver, foi necessário ligar diversas vezes para resolver.
+Além disso, o agendamento de manutenções e/ou trocas de endereço é sempre ruim.</t>
+  </si>
+  <si>
+    <t>problema não foi resolvido + mistura técnico/financeiro</t>
+  </si>
+  <si>
+    <t>agendamento de manutenção moroso + 1 OS para 3 equipamentos</t>
+  </si>
+  <si>
+    <t>saiu uma larva viva + dificuldade de agendar/técnico sem informação</t>
+  </si>
+  <si>
+    <t>não sei se está consertado</t>
+  </si>
+  <si>
+    <t>terminou de quebrá-lo, fiquei sem água (R5)</t>
+  </si>
+  <si>
+    <t>profissional vai despreparado + muita demora no atendimento</t>
+  </si>
+  <si>
+    <t>não apareceu ninguém para a manutenção</t>
+  </si>
+  <si>
+    <t>problemas no sistema de cobrança + agendamento ruim</t>
   </si>
 </sst>
 </file>
@@ -11158,7 +11207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1658"/>
+  <dimension ref="A1:M1666"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -77834,7 +77883,7 @@
         <v>1338</v>
       </c>
       <c r="K1626" s="4" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="L1626" s="4" t="s">
         <v>1547</v>
@@ -77875,7 +77924,7 @@
         <v>1337</v>
       </c>
       <c r="K1627" s="4" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="L1627" s="4" t="s">
         <v>1546</v>
@@ -77916,7 +77965,7 @@
         <v>1337</v>
       </c>
       <c r="K1628" s="4" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="L1628" s="4" t="s">
         <v>1547</v>
@@ -77957,7 +78006,7 @@
         <v>1337</v>
       </c>
       <c r="K1629" s="4" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="L1629" s="4" t="s">
         <v>1547</v>
@@ -77986,7 +78035,7 @@
         <v>3396</v>
       </c>
       <c r="G1630" s="4" t="s">
-        <v>3401</v>
+        <v>15</v>
       </c>
       <c r="H1630" s="4" t="s">
         <v>40</v>
@@ -77998,7 +78047,7 @@
         <v>1337</v>
       </c>
       <c r="K1630" s="4" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="L1630" s="4" t="s">
         <v>1546</v>
@@ -78027,7 +78076,7 @@
         <v>3397</v>
       </c>
       <c r="G1631" s="4" t="s">
-        <v>3401</v>
+        <v>15</v>
       </c>
       <c r="H1631" s="4" t="s">
         <v>18</v>
@@ -78039,7 +78088,7 @@
         <v>1337</v>
       </c>
       <c r="K1631" s="4" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="L1631" s="4" t="s">
         <v>1547</v>
@@ -78068,7 +78117,7 @@
         <v>3398</v>
       </c>
       <c r="G1632" s="4" t="s">
-        <v>3401</v>
+        <v>15</v>
       </c>
       <c r="H1632" s="4" t="s">
         <v>948</v>
@@ -78080,7 +78129,7 @@
         <v>1337</v>
       </c>
       <c r="K1632" s="4" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="L1632" s="4" t="s">
         <v>1546</v>
@@ -78109,7 +78158,7 @@
         <v>3399</v>
       </c>
       <c r="G1633" s="4" t="s">
-        <v>3401</v>
+        <v>15</v>
       </c>
       <c r="H1633" s="4" t="s">
         <v>18</v>
@@ -78121,7 +78170,7 @@
         <v>1337</v>
       </c>
       <c r="K1633" s="4" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="L1633" s="4" t="s">
         <v>1547</v>
@@ -78150,7 +78199,7 @@
         <v>3400</v>
       </c>
       <c r="G1634" s="4" t="s">
-        <v>3401</v>
+        <v>15</v>
       </c>
       <c r="H1634" s="4" t="s">
         <v>48</v>
@@ -78162,7 +78211,7 @@
         <v>1337</v>
       </c>
       <c r="K1634" s="4" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="L1634" s="4" t="s">
         <v>1547</v>
@@ -78188,7 +78237,7 @@
         <v>13</v>
       </c>
       <c r="F1635" s="4" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G1635" s="4" t="s">
         <v>25</v>
@@ -78203,7 +78252,7 @@
         <v>1337</v>
       </c>
       <c r="K1635" s="4" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="L1635" s="4" t="s">
         <v>1546</v>
@@ -78229,7 +78278,7 @@
         <v>13</v>
       </c>
       <c r="F1636" s="4" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="G1636" s="4" t="s">
         <v>15</v>
@@ -78244,7 +78293,7 @@
         <v>1337</v>
       </c>
       <c r="K1636" s="4" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="L1636" s="4" t="s">
         <v>1546</v>
@@ -78270,7 +78319,7 @@
         <v>13</v>
       </c>
       <c r="F1637" s="4" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="G1637" s="4" t="s">
         <v>15</v>
@@ -78285,7 +78334,7 @@
         <v>1359</v>
       </c>
       <c r="K1637" s="4" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="L1637" s="4" t="s">
         <v>1546</v>
@@ -78311,7 +78360,7 @@
         <v>13</v>
       </c>
       <c r="F1638" s="4" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="G1638" s="4" t="s">
         <v>3394</v>
@@ -78326,7 +78375,7 @@
         <v>1337</v>
       </c>
       <c r="K1638" s="4" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="L1638" s="4" t="s">
         <v>1546</v>
@@ -78352,7 +78401,7 @@
         <v>13</v>
       </c>
       <c r="F1639" s="4" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="G1639" s="4" t="s">
         <v>25</v>
@@ -78367,7 +78416,7 @@
         <v>1337</v>
       </c>
       <c r="K1639" s="4" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="L1639" s="4" t="s">
         <v>1546</v>
@@ -78393,7 +78442,7 @@
         <v>13</v>
       </c>
       <c r="F1640" s="4" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="G1640" s="4" t="s">
         <v>25</v>
@@ -78408,13 +78457,13 @@
         <v>1337</v>
       </c>
       <c r="K1640" s="4" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="L1640" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1640" s="4" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="1641" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -78449,7 +78498,7 @@
         <v>1337</v>
       </c>
       <c r="K1641" s="4" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="L1641" s="4" t="s">
         <v>1547</v>
@@ -78475,7 +78524,7 @@
         <v>13</v>
       </c>
       <c r="F1642" s="4" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="G1642" s="4" t="s">
         <v>28</v>
@@ -78490,7 +78539,7 @@
         <v>1338</v>
       </c>
       <c r="K1642" s="4" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="L1642" s="4" t="s">
         <v>1546</v>
@@ -78516,7 +78565,7 @@
         <v>13</v>
       </c>
       <c r="F1643" s="4" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="G1643" s="4" t="s">
         <v>65</v>
@@ -78531,7 +78580,7 @@
         <v>1337</v>
       </c>
       <c r="K1643" s="4" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="L1643" s="4" t="s">
         <v>1546</v>
@@ -78557,7 +78606,7 @@
         <v>13</v>
       </c>
       <c r="F1644" s="4" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="G1644" s="4" t="s">
         <v>15</v>
@@ -78572,7 +78621,7 @@
         <v>1337</v>
       </c>
       <c r="K1644" s="4" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="L1644" s="4" t="s">
         <v>1547</v>
@@ -78598,7 +78647,7 @@
         <v>13</v>
       </c>
       <c r="F1645" s="4" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="G1645" s="4" t="s">
         <v>15</v>
@@ -78613,7 +78662,7 @@
         <v>1337</v>
       </c>
       <c r="K1645" s="4" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="L1645" s="4" t="s">
         <v>1547</v>
@@ -78639,7 +78688,7 @@
         <v>13</v>
       </c>
       <c r="F1646" s="4" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="G1646" s="4" t="s">
         <v>65</v>
@@ -78654,7 +78703,7 @@
         <v>1337</v>
       </c>
       <c r="K1646" s="4" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="L1646" s="4" t="s">
         <v>1547</v>
@@ -78680,7 +78729,7 @@
         <v>13</v>
       </c>
       <c r="F1647" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="G1647" s="4" t="s">
         <v>15</v>
@@ -78695,7 +78744,7 @@
         <v>1359</v>
       </c>
       <c r="K1647" s="4" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="L1647" s="4" t="s">
         <v>1546</v>
@@ -78721,7 +78770,7 @@
         <v>13</v>
       </c>
       <c r="F1648" s="4" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="G1648" s="4" t="s">
         <v>15</v>
@@ -78736,7 +78785,7 @@
         <v>1337</v>
       </c>
       <c r="K1648" s="4" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="L1648" s="4" t="s">
         <v>1546</v>
@@ -78762,7 +78811,7 @@
         <v>13</v>
       </c>
       <c r="F1649" s="4" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="G1649" s="4" t="s">
         <v>15</v>
@@ -78777,7 +78826,7 @@
         <v>1337</v>
       </c>
       <c r="K1649" s="4" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="L1649" s="4" t="s">
         <v>1546</v>
@@ -78803,7 +78852,7 @@
         <v>13</v>
       </c>
       <c r="F1650" s="4" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="G1650" s="4" t="s">
         <v>15</v>
@@ -78818,7 +78867,7 @@
         <v>1337</v>
       </c>
       <c r="K1650" s="4" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="L1650" s="4" t="s">
         <v>1546</v>
@@ -78844,7 +78893,7 @@
         <v>13</v>
       </c>
       <c r="F1651" s="4" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="G1651" s="4" t="s">
         <v>28</v>
@@ -78859,7 +78908,7 @@
         <v>1337</v>
       </c>
       <c r="K1651" s="4" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="L1651" s="4" t="s">
         <v>1546</v>
@@ -78885,7 +78934,7 @@
         <v>13</v>
       </c>
       <c r="F1652" s="4" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="G1652" s="4" t="s">
         <v>15</v>
@@ -78900,7 +78949,7 @@
         <v>1338</v>
       </c>
       <c r="K1652" s="4" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="L1652" s="4" t="s">
         <v>1546</v>
@@ -78926,7 +78975,7 @@
         <v>13</v>
       </c>
       <c r="F1653" s="4" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="G1653" s="4" t="s">
         <v>15</v>
@@ -78941,7 +78990,7 @@
         <v>1337</v>
       </c>
       <c r="K1653" s="4" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="L1653" s="4" t="s">
         <v>1546</v>
@@ -78967,7 +79016,7 @@
         <v>13</v>
       </c>
       <c r="F1654" s="4" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="G1654" s="4" t="s">
         <v>15</v>
@@ -78982,7 +79031,7 @@
         <v>1337</v>
       </c>
       <c r="K1654" s="4" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="L1654" s="4" t="s">
         <v>1546</v>
@@ -79008,7 +79057,7 @@
         <v>13</v>
       </c>
       <c r="F1655" s="4" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="G1655" s="4" t="s">
         <v>15</v>
@@ -79023,7 +79072,7 @@
         <v>1337</v>
       </c>
       <c r="K1655" s="4" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="L1655" s="4" t="s">
         <v>1546</v>
@@ -79049,7 +79098,7 @@
         <v>13</v>
       </c>
       <c r="F1656" s="4" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="G1656" s="4" t="s">
         <v>15</v>
@@ -79064,7 +79113,7 @@
         <v>1337</v>
       </c>
       <c r="K1656" s="4" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="L1656" s="4" t="s">
         <v>1547</v>
@@ -79090,7 +79139,7 @@
         <v>13</v>
       </c>
       <c r="F1657" s="4" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="G1657" s="4" t="s">
         <v>28</v>
@@ -79105,7 +79154,7 @@
         <v>1337</v>
       </c>
       <c r="K1657" s="4" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="L1657" s="4" t="s">
         <v>1547</v>
@@ -79131,7 +79180,7 @@
         <v>13</v>
       </c>
       <c r="F1658" s="5" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="G1658" s="4" t="s">
         <v>28</v>
@@ -79146,13 +79195,341 @@
         <v>1337</v>
       </c>
       <c r="K1658" s="4" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="L1658" s="4" t="s">
         <v>1546</v>
       </c>
       <c r="M1658" s="4" t="s">
         <v>2517</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1659" s="4">
+        <v>680</v>
+      </c>
+      <c r="B1659" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1659" s="4">
+        <v>155845</v>
+      </c>
+      <c r="D1659" s="2">
+        <v>46309</v>
+      </c>
+      <c r="E1659" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1659" s="4" t="s">
+        <v>3458</v>
+      </c>
+      <c r="G1659" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1659" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1659" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1659" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1659" s="4" t="s">
+        <v>3466</v>
+      </c>
+      <c r="L1659" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1659" s="4" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1660" s="4">
+        <v>681</v>
+      </c>
+      <c r="B1660" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1660" s="4">
+        <v>143350</v>
+      </c>
+      <c r="D1660" s="2">
+        <v>46309</v>
+      </c>
+      <c r="E1660" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1660" s="5" t="s">
+        <v>3459</v>
+      </c>
+      <c r="G1660" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1660" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1660" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1660" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1660" s="4" t="s">
+        <v>3467</v>
+      </c>
+      <c r="L1660" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1660" s="4" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1661" s="4">
+        <v>682</v>
+      </c>
+      <c r="B1661" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1661" s="4">
+        <v>166438</v>
+      </c>
+      <c r="D1661" s="2">
+        <v>46309</v>
+      </c>
+      <c r="E1661" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1661" s="4" t="s">
+        <v>3460</v>
+      </c>
+      <c r="G1661" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1661" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1661" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1661" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1661" s="4" t="s">
+        <v>3468</v>
+      </c>
+      <c r="L1661" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1661" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1662" s="4">
+        <v>683</v>
+      </c>
+      <c r="B1662" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1662" s="4">
+        <v>166797</v>
+      </c>
+      <c r="D1662" s="2">
+        <v>46309</v>
+      </c>
+      <c r="E1662" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1662" s="4" t="s">
+        <v>3461</v>
+      </c>
+      <c r="G1662" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1662" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1662" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1662" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1662" s="4" t="s">
+        <v>3469</v>
+      </c>
+      <c r="L1662" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1662" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1663" s="4">
+        <v>684</v>
+      </c>
+      <c r="B1663" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1663" s="4">
+        <v>166156</v>
+      </c>
+      <c r="D1663" s="2">
+        <v>46309</v>
+      </c>
+      <c r="E1663" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1663" s="4" t="s">
+        <v>3462</v>
+      </c>
+      <c r="G1663" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1663" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1663" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1663" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1663" s="4" t="s">
+        <v>3470</v>
+      </c>
+      <c r="L1663" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1663" s="4" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1664" s="4">
+        <v>685</v>
+      </c>
+      <c r="B1664" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1664" s="4">
+        <v>166940</v>
+      </c>
+      <c r="D1664" s="2">
+        <v>46309</v>
+      </c>
+      <c r="E1664" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1664" s="4" t="s">
+        <v>3463</v>
+      </c>
+      <c r="G1664" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1664" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1664" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1664" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1664" s="4" t="s">
+        <v>3471</v>
+      </c>
+      <c r="L1664" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1664" s="4" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1665" s="4">
+        <v>686</v>
+      </c>
+      <c r="B1665" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1665" s="4">
+        <v>155765</v>
+      </c>
+      <c r="D1665" s="2">
+        <v>46309</v>
+      </c>
+      <c r="E1665" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1665" s="4" t="s">
+        <v>3464</v>
+      </c>
+      <c r="G1665" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1665" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1665" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1665" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1665" s="4" t="s">
+        <v>3472</v>
+      </c>
+      <c r="L1665" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1665" s="4" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1666" s="4">
+        <v>687</v>
+      </c>
+      <c r="B1666" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1666" s="4">
+        <v>157572</v>
+      </c>
+      <c r="D1666" s="2">
+        <v>46310</v>
+      </c>
+      <c r="E1666" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1666" s="4" t="s">
+        <v>3465</v>
+      </c>
+      <c r="G1666" s="4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="H1666" s="4" t="s">
+        <v>3395</v>
+      </c>
+      <c r="I1666" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1666" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1666" s="4" t="s">
+        <v>3473</v>
+      </c>
+      <c r="L1666" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1666" s="4" t="s">
+        <v>2446</v>
       </c>
     </row>
   </sheetData>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2902" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B672193D-AC02-42EE-B637-71757D2F66C7}"/>
+  <xr:revisionPtr revIDLastSave="2940" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BED1B3-627B-41E7-8003-DCC1C8FA535B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16704" uniqueCount="3474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16764" uniqueCount="3487">
   <si>
     <t>ID</t>
   </si>
@@ -10752,6 +10752,48 @@
   </si>
   <si>
     <t>problemas no sistema de cobrança + agendamento ruim</t>
+  </si>
+  <si>
+    <t>Lixo de serviço!!! Não monitoram o tempo das manutenções periódicas e não respondem ao canal oficial de WhatsApp da própria empresa!!! Jamais recomendarei a alguém.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So um técnico realmente limpou tudo, a fan as aletas de entrada de ar. Os atuais so passam um pano por fora e um cotonete.  Isso eu ja faço por higiene. </t>
+  </si>
+  <si>
+    <t>Porque o cliente marca o horário de atendimento pela manhã de 8:00 às 13:00 e no entanto o técnico só chegou às 14:30 h.
+Ou seja atrapalha a vida do cliente.
+E a culpa é da empresa que faz um itinerário errado do técnico pois marca mais clientes do que deve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pq fiquei 1 ano sem a visita técnica,ligo para pedir uma visita e marquei por 3 vezes e as 3 vezes marcadas a visita,não foram nenhuma, alegam sempre alguma coisa, os contatos com a empresa e péssimo um robô que nunca quase deixa vc ter um contato para maior esclarecimento e sempre terminando a conversa,e o pior com dois representantes o de são Paulo e do Rio de janeiro,que não se entendem e o robô marcando a visita técnica e cancelando uma verdadeira bagunça no qual ninguém se entende. </t>
+  </si>
+  <si>
+    <t>Fiz o upgrade para um novo plano. Porém me trouxerem o mesmo purificador do plano antigo.</t>
+  </si>
+  <si>
+    <t>Não tive visita do técnico pois ficou agendado para parte da tarde e o mesmo chegou às 11:05 hs e eu estava na rua pois o agendamento começava às 13 hs.
+Uma vergonha !</t>
+  </si>
+  <si>
+    <t>AT SJRPRETO SP R04</t>
+  </si>
+  <si>
+    <t>não monitoram manutenções periódicas + WhatsApp não responde</t>
+  </si>
+  <si>
+    <t>só passam um pano por fora</t>
+  </si>
+  <si>
+    <t>marcado 8h-13h, técnico chegou 14:30</t>
+  </si>
+  <si>
+    <t>3 visitas marcadas, nenhuma ocorreu + contato via robô péssimo</t>
+  </si>
+  <si>
+    <t>upgrade, mas trouxeram mesmo purificador antigo</t>
+  </si>
+  <si>
+    <t>agendado à tarde, chegou às 11:05</t>
   </si>
 </sst>
 </file>
@@ -11207,7 +11249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1666"/>
+  <dimension ref="A1:M1672"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -79532,6 +79574,252 @@
         <v>2446</v>
       </c>
     </row>
+    <row r="1667" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1667" s="4">
+        <v>688</v>
+      </c>
+      <c r="B1667" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1667" s="4">
+        <v>155583</v>
+      </c>
+      <c r="D1667" s="2">
+        <v>46310</v>
+      </c>
+      <c r="E1667" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1667" s="4" t="s">
+        <v>3474</v>
+      </c>
+      <c r="G1667" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1667" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1667" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1667" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1667" s="4" t="s">
+        <v>3481</v>
+      </c>
+      <c r="L1667" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1667" s="4" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1668" s="4">
+        <v>689</v>
+      </c>
+      <c r="B1668" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1668" s="4">
+        <v>163783</v>
+      </c>
+      <c r="D1668" s="2">
+        <v>46310</v>
+      </c>
+      <c r="E1668" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1668" s="4" t="s">
+        <v>3475</v>
+      </c>
+      <c r="G1668" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1668" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1668" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1668" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1668" s="4" t="s">
+        <v>3482</v>
+      </c>
+      <c r="L1668" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1668" s="4" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1669" s="4">
+        <v>690</v>
+      </c>
+      <c r="B1669" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1669" s="4">
+        <v>151864</v>
+      </c>
+      <c r="D1669" s="2">
+        <v>46310</v>
+      </c>
+      <c r="E1669" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1669" s="4" t="s">
+        <v>3476</v>
+      </c>
+      <c r="G1669" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1669" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1669" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1669" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1669" s="4" t="s">
+        <v>3483</v>
+      </c>
+      <c r="L1669" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1669" s="4" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1670" s="4">
+        <v>691</v>
+      </c>
+      <c r="B1670" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1670" s="4">
+        <v>169636</v>
+      </c>
+      <c r="D1670" s="2">
+        <v>46310</v>
+      </c>
+      <c r="E1670" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1670" s="4" t="s">
+        <v>3477</v>
+      </c>
+      <c r="G1670" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1670" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1670" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1670" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1670" s="4" t="s">
+        <v>3484</v>
+      </c>
+      <c r="L1670" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1670" s="4" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1671" s="4">
+        <v>692</v>
+      </c>
+      <c r="B1671" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1671" s="4">
+        <v>167755</v>
+      </c>
+      <c r="D1671" s="2">
+        <v>46310</v>
+      </c>
+      <c r="E1671" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1671" s="4" t="s">
+        <v>3478</v>
+      </c>
+      <c r="G1671" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1671" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1671" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1671" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1671" s="4" t="s">
+        <v>3485</v>
+      </c>
+      <c r="L1671" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1671" s="4" t="s">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1672" s="4">
+        <v>693</v>
+      </c>
+      <c r="B1672" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1672" s="4">
+        <v>157462</v>
+      </c>
+      <c r="D1672" s="2">
+        <v>46310</v>
+      </c>
+      <c r="E1672" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1672" s="4" t="s">
+        <v>3479</v>
+      </c>
+      <c r="G1672" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1672" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1672" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1672" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1672" s="4" t="s">
+        <v>3486</v>
+      </c>
+      <c r="L1672" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1672" s="4" t="s">
+        <v>2488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2940" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BED1B3-627B-41E7-8003-DCC1C8FA535B}"/>
+  <xr:revisionPtr revIDLastSave="2955" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02DA56A3-3853-43B1-AE85-B4F681C41140}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16764" uniqueCount="3487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16788" uniqueCount="3490">
   <si>
     <t>ID</t>
   </si>
@@ -10794,6 +10794,15 @@
   </si>
   <si>
     <t>agendado à tarde, chegou às 11:05</t>
+  </si>
+  <si>
+    <t>Nao compareceram para trocar o filtro que veio errado</t>
+  </si>
+  <si>
+    <t>Atendimento péssimo, gostaria que vocês escutassem a gravação das minhas ligações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque existem no mercado filtros de qualidade por um preço muito bom </t>
   </si>
 </sst>
 </file>
@@ -11249,7 +11258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1672"/>
+  <dimension ref="A1:M1675"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -79820,6 +79829,111 @@
         <v>2488</v>
       </c>
     </row>
+    <row r="1673" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1673" s="4">
+        <v>694</v>
+      </c>
+      <c r="B1673" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1673" s="4">
+        <v>162322</v>
+      </c>
+      <c r="D1673" s="2">
+        <v>46311</v>
+      </c>
+      <c r="E1673" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1673" s="4" t="s">
+        <v>3487</v>
+      </c>
+      <c r="G1673" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1673" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1673" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1673" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1673" s="4" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1674" s="4">
+        <v>695</v>
+      </c>
+      <c r="B1674" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1674" s="4">
+        <v>158327</v>
+      </c>
+      <c r="D1674" s="2">
+        <v>46311</v>
+      </c>
+      <c r="E1674" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1674" s="4" t="s">
+        <v>3488</v>
+      </c>
+      <c r="G1674" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1674" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1674" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1674" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M1674" s="4" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1675" s="4">
+        <v>696</v>
+      </c>
+      <c r="B1675" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1675" s="4">
+        <v>150676</v>
+      </c>
+      <c r="D1675" s="2">
+        <v>46312</v>
+      </c>
+      <c r="E1675" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1675" s="4" t="s">
+        <v>3489</v>
+      </c>
+      <c r="G1675" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1675" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1675" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1675" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M1675" s="4" t="s">
+        <v>2410</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2955" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02DA56A3-3853-43B1-AE85-B4F681C41140}"/>
+  <xr:revisionPtr revIDLastSave="2985" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97CF54E0-1014-43C5-A229-BF0758F4691B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16788" uniqueCount="3490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16842" uniqueCount="3500">
   <si>
     <t>ID</t>
   </si>
@@ -10803,6 +10803,39 @@
   </si>
   <si>
     <t xml:space="preserve">Porque existem no mercado filtros de qualidade por um preço muito bom </t>
+  </si>
+  <si>
+    <t>Continuam com péssimo atendimento e relacionamento. Estou aguardando há 4 anos solução… Ainda está tudo muito confuso… não sei até onde vou continuar com vocês… a insatisfação é grande…</t>
+  </si>
+  <si>
+    <t>A CLASSIFICAÇÃO FOI BAIXA DEVIDO QUE PRECISAVAMOS RESOLVER O PROBLEMA, E NO FINAL TEREMOS QUE FICAR SEM AGUA POR 24 HORAS, TRABALHAMOS COM O PUBLICO. E ALEM DE TUDO ESTÁ UM DIA SUPER QUENTE.</t>
+  </si>
+  <si>
+    <t>já agendei visita técnica para reparos pela terceira vez e , nenhum técnico apareceu até agora
+cnpj 58669565000146 - lofer restaurante - avenida coronel silva teles, 514 - cambui - campinas - FILTRO INSTALADO NO BAR DO SALÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Técnico chegou antes das 13h e eu não estava em casa. Retornou as 13h mal-humorado dizendo que a frequência de troca do filtro é de 12 meses e não 6. Não quis ver como a vazão da água havia diminuído e como o elemento estava sujo. Acabou trocando depois que reclamei. Não fez higienização nem nada mais. Não deixou o canhoto do serviço executado comigo. </t>
+  </si>
+  <si>
+    <t>Faltaram para manutenção  preventiva  marcada  para hoje</t>
+  </si>
+  <si>
+    <t>Porque houve demora para o atendimento. Chamado aberto no dia 14/10 e a atendente agendou para somente 22/10 (8 dias depois), mesmo explicando que havia somente um bebedouro no andar para os clientes e de que a clínica abre inclusive nos sábados e domingos.
+Após ligações (que demoram para atender) e emails enviados, suplicando atendimento, é que fomos atendidos no dia 20/10 (6 dias depois).
+Solicitamos desconto dos dias de equipamento parado conforme previsto na cláusula 4.3 do contrato.</t>
+  </si>
+  <si>
+    <t>Eduarda Cândida Jacinta dos Reis</t>
+  </si>
+  <si>
+    <t>Integração BOOMI</t>
+  </si>
+  <si>
+    <t>AlCIONE APARECIDA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Roberta Duarte De Souza</t>
   </si>
 </sst>
 </file>
@@ -11258,7 +11291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1675"/>
+  <dimension ref="A1:M1681"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -79934,6 +79967,234 @@
         <v>2410</v>
       </c>
     </row>
+    <row r="1676" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1676" s="4">
+        <v>697</v>
+      </c>
+      <c r="B1676" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1676" s="4">
+        <v>165349</v>
+      </c>
+      <c r="D1676" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E1676" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1676" s="4" t="s">
+        <v>3490</v>
+      </c>
+      <c r="G1676" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1676" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1676" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1676" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1676" s="4" t="s">
+        <v>3496</v>
+      </c>
+      <c r="M1676" s="4" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1677" s="4">
+        <v>698</v>
+      </c>
+      <c r="B1677" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1677" s="4">
+        <v>167550</v>
+      </c>
+      <c r="D1677" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E1677" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1677" s="4" t="s">
+        <v>3491</v>
+      </c>
+      <c r="G1677" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1677" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1677" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1677" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1677" s="4" t="s">
+        <v>3497</v>
+      </c>
+      <c r="M1677" s="4" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1678" s="4">
+        <v>700</v>
+      </c>
+      <c r="B1678" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1678" s="4">
+        <v>167806</v>
+      </c>
+      <c r="D1678" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E1678" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1678" s="5" t="s">
+        <v>3492</v>
+      </c>
+      <c r="G1678" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1678" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1678" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1678" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1678" s="4" t="s">
+        <v>3497</v>
+      </c>
+      <c r="M1678" s="4" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1679" s="4">
+        <v>701</v>
+      </c>
+      <c r="B1679" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1679" s="4">
+        <v>164009</v>
+      </c>
+      <c r="D1679" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E1679" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1679" s="4" t="s">
+        <v>3493</v>
+      </c>
+      <c r="G1679" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1679" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1679" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1679" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1679" s="4" t="s">
+        <v>3497</v>
+      </c>
+      <c r="M1679" s="4" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1680" s="4">
+        <v>702</v>
+      </c>
+      <c r="B1680" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1680" s="4">
+        <v>159120</v>
+      </c>
+      <c r="D1680" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E1680" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1680" s="4" t="s">
+        <v>3494</v>
+      </c>
+      <c r="G1680" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1680" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1680" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1680" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1680" s="4" t="s">
+        <v>3498</v>
+      </c>
+      <c r="M1680" s="4" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1681" s="4">
+        <v>703</v>
+      </c>
+      <c r="B1681" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1681" s="4">
+        <v>168842</v>
+      </c>
+      <c r="D1681" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E1681" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1681" s="4" t="s">
+        <v>3495</v>
+      </c>
+      <c r="G1681" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1681" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1681" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1681" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K1681" s="4" t="s">
+        <v>3499</v>
+      </c>
+      <c r="M1681" s="4" t="s">
+        <v>2534</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/NPS Classificado.xlsx
+++ b/NPS Classificado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/eduardacjr_callink_com_br/Documents/Área de Trabalho/Dashboards/nps-franquias/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://callinkcombr-my.sharepoint.com/personal/pedroofs_callink_com_br/Documents/Área de Trabalho/Dashboards/12 - NPS/nps-franquias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3026" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B48BC65-184F-4DFD-9821-732EAB2B5454}"/>
+  <xr:revisionPtr revIDLastSave="3039" documentId="8_{855DE731-06B6-4F67-B5F3-79AE1FB3CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{827C5AB5-5BBE-41AB-9394-4FA7382F0DC5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-2580" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16854" uniqueCount="3508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17206" uniqueCount="3581">
   <si>
     <t>ID</t>
   </si>
@@ -10860,6 +10860,232 @@
   </si>
   <si>
     <t>sem comunicado de agendamento (Large) + unificar preventiva dos 3</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>24/10/2026</t>
+  </si>
+  <si>
+    <t>26/10/2026</t>
+  </si>
+  <si>
+    <t>27/10/2026</t>
+  </si>
+  <si>
+    <t>PORQUE? O TECNICO VEIO NAO ARRUMOU MEU PURIFICADOR, DEPOIS DE ESPERAR MAIS DE UMA SEMANA, E ESSE MÉTODO DE ATENTIMENTO E MUITO RUIM, MUITO DEMORADO PARA VC SE COMUNICAR, E NAO AJUDOU EM NADA, SAO DESPREPARADOS, PARA ATENTIMENTO</t>
+  </si>
+  <si>
+    <t>Demora pea manutenção,  e eu solicitei a troca do equipamento,  nao fui atendida</t>
+  </si>
+  <si>
+    <t>Porque eu fiquei desde de 01/04/2026 solicitando a troca do aparelho.
+Tive que comprar galão de água porque o meu aparelho não funcionava, tive que desligar várias vezes porque ele armava e desarmava várias vezes, água não gelava e as vezes o botão não funcionava aí a água ficava direto.
+Nunca tive esse péssimo atendimento de vocês, mas sempre tem a primeira vez e espero que seja a última.
+Mesmo assim muito obrigado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demorou mais de 45 dias para trocar o aparelho que não gelava , trocaram todas as peças 2 vezes , 5 visitas e mais 4 que marquei e não vieram , ou seja marcadas 9 visitas , todos os técnicos diziam que tinha que trocar o aparelho , tive muita paciência , ufa …. Trocaram na 10 visita … o cliente não interessa , fizeram tudo para eu desistir , venci .. </t>
+  </si>
+  <si>
+    <t>O técnico marcou e nao foi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou a duas semanas sem o purificador estar funcionando </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pela segunda vez e agendado um horário e o mesmo não é cumprido.
+Foi marcado para o período </t>
+  </si>
+  <si>
+    <t>Problema não foi resolvido. Filtro continua vazando...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O problema nos botões não foi resolvido. O técnico trocou e ficou ainda pior...desisto. Irei solicitar o cancelamento do serviço. </t>
+  </si>
+  <si>
+    <t>Não trocou a vela sob a alegação de que a vela está boa apartir do teste da água. Então, vamos ter que consumir uma água ruim pra vela ser trocada?</t>
+  </si>
+  <si>
+    <t>Eu expliquei na abertura do chamado que precisamos trocar a conexão do filtro com a água. Depois de 4 agendamentos sem sucesso, o técnico apareceu hoje e disse que só troca vela. Foi embora sem resolver nada. É um absurdo o descaso dos prestadores no Rio de Janeiro. Se acontecer um vazamento por causa disso, a Brastemp vai arcar com os custos de manutenção no imóvel?? Decepcionada. Vou abrir uma reclamação na ouvidoria agora.</t>
+  </si>
+  <si>
+    <t>Colocaram um purificador ruim com a câmara  estragada há muito usada , bebi água suja esse tempo q foi instalado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Técnico não compareceu, ninguém me procurou para remarcar a manutenção. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não voltaram para resolver o problema </t>
+  </si>
+  <si>
+    <t>Nunca vem no horário combinado!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não resolve nenhum problema </t>
+  </si>
+  <si>
+    <t>Recebi a lavadoura amassada e foi um parto tentando realizar a troca tanta burocracia e tb o pedido de recuperação judicial que desisti de fazer a troca</t>
+  </si>
+  <si>
+    <t>Inúmeros problemas com essa empresa, já estive para cancelar 2x e fui convencida a manter. Depois de 3 semanas,  falta de técnico, técnico com OS errada, solicitei reinstalação e manutenção, e hoje, o técnico, que sabe o que faz, estava preparado apenas para reinstalar. Terei que esperar mais tempo para usar o filtro.
+Faz 3 meses que o filtro ficou parado por uma reforma na cozinha. As pesquisas e as opções de menu no WhatsApp,  por ex, são péssimas, não há a opção reinstalar, o equipamento ficou sem uso muito tempo,  etc. Estou nando essa nota porque a empresa não tem boa comunicação com os funcionários. No geral, eles são bons, mas o atendimento é segmentado e só no meu caso, erraram muito duas vezes e a terceira foi por falta, sem comunicar o cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfação </t>
+  </si>
+  <si>
+    <t>O tecnico reparou apenas uma parte do solicitado, o fluxo de agua, porem o vazamento ele falou que o tecnico anterior tinha deixado sujeira e por isso estava congelando, mas nao limpou nem resolveu o problema, o filtro continua vazando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não trocaram o filtro da máquina, mesmo informando que a água está com um gosto ruim, não entendi para que se marca uma visita de manutenção e não trocam no mínimo o filtro? </t>
+  </si>
+  <si>
+    <t>NÃO RECOMENDO A NINGUÉM , mais uma vez o agendamento não foi cumprido , VCS NÃO APARECEM , e mentiram dizendo que tinham ido e não tinha ninguém em casa quando eu estava em casa aguardando . Sem contar que o meu filtro já está há quase 8 MESES SEM MANUTENÇÃO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por motivo de só ter agenda para 3 dias após meu contato e ficar sem agua esse tempo todo,
+é um absurdo. </t>
+  </si>
+  <si>
+    <t>Visita marcada, porém o funcionário não apareceu.</t>
+  </si>
+  <si>
+    <t>Nao compensa manter o aluguel do aparelho, o melhor e comprar, existem varios produtos de excelente qualidade. Eu mesma ja estava p cancelar... provavelmente depois do meu acordo de desconto... cancele.</t>
+  </si>
+  <si>
+    <t>Serviço para atendimento no momento està ruim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Técnico atrasou muito 20 minutos Não sei se fez manutenção correta porque foi embora em menos de 10 minutos Não trocou filtro! </t>
+  </si>
+  <si>
+    <t>O filtro é perfeito, mas não consigo resolver problemas. Estou sendo cobrado em duplicidade e não consigo receber o valor que já foi cobrado (reembolso) e também não consigo deixar de ser cobrado em duplicadade, todo mês sou cobrado, todo mês eu ligo e nada acontece.</t>
+  </si>
+  <si>
+    <t>Porque o atendimento NÃO FOI REALIZADO!!!!! O técnico NÃO compareceu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porque o aparelho deu pane elétrica faz mais de 15 dias, eu liguei pedi prioridade visto que era um problema que inviabilizava o uso, não era uma simples troca de filtro, e não levaram em consideração meu pedido. Sou cliente desde 2008, ou seja há 18 anos e esperava um atendimento diferenciado para este tipo de ocorrência. Estava esperando até que não viessem hoje porque aí iria cancelar minha assinatura.
+Trabalho com prestação de serviços e quando um cliente me procura para solucionar um problema, procuro dar prioridade, ainda mais se for um cliente antigo e fiel.  </t>
+  </si>
+  <si>
+    <t>Não resolveu o problema</t>
+  </si>
+  <si>
+    <t>tecnico se recusou a trocar o filtro</t>
+  </si>
+  <si>
+    <t>Troca</t>
+  </si>
+  <si>
+    <t>SEGURANÇA DO PRODUTO</t>
+  </si>
+  <si>
+    <t>Troca de aparelho não efetivada</t>
+  </si>
+  <si>
+    <t>Caso sem resolução</t>
+  </si>
+  <si>
+    <t>veio e não arrumou + demora/atendimento ruim</t>
+  </si>
+  <si>
+    <t>demora manutenção + troca solicitada não atendida</t>
+  </si>
+  <si>
+    <t>desde 01/04 solicitando a troca</t>
+  </si>
+  <si>
+    <t>técnicos diziam trocar + 4 visitas faltaram</t>
+  </si>
+  <si>
+    <t>técnico marcou e não foi</t>
+  </si>
+  <si>
+    <t>duas semanas sem purificador funcionando</t>
+  </si>
+  <si>
+    <t>horário agendado não é cumprido</t>
+  </si>
+  <si>
+    <t>não resolvido, filtro continua vazando</t>
+  </si>
+  <si>
+    <t>botões não resolvido, ficou pior + cancelamento</t>
+  </si>
+  <si>
+    <t>não trocou a vela após teste</t>
+  </si>
+  <si>
+    <t>pedi troca da conexão, técnico só troca vela + 4 agendamentos</t>
+  </si>
+  <si>
+    <t>purificador ruim, câmara estragada, usado</t>
+  </si>
+  <si>
+    <t>não compareceu + ninguém remarcou</t>
+  </si>
+  <si>
+    <t>não voltaram para resolver</t>
+  </si>
+  <si>
+    <t>nunca vem no horário combinado</t>
+  </si>
+  <si>
+    <t>não resolve nenhum problema</t>
+  </si>
+  <si>
+    <t>lavadora amassada + burocracia na troca</t>
+  </si>
+  <si>
+    <t>técnico com OS errada + WhatsApp ruim</t>
+  </si>
+  <si>
+    <t>satisfação</t>
+  </si>
+  <si>
+    <t>filtro continua vazando + não limpou</t>
+  </si>
+  <si>
+    <t>não trocaram o filtro, gosto ruim</t>
+  </si>
+  <si>
+    <t>não aparecem + 8 meses sem manutenção</t>
+  </si>
+  <si>
+    <t>só agenda para 3 dias depois</t>
+  </si>
+  <si>
+    <t>visita marcada, funcionário não apareceu</t>
+  </si>
+  <si>
+    <t>não compensa manter o aluguel</t>
+  </si>
+  <si>
+    <t>serviço de atendimento está ruim</t>
+  </si>
+  <si>
+    <t>menos de 10 min, não trocou filtro + atraso</t>
+  </si>
+  <si>
+    <t>cobrado em duplicidade, sem reembolso</t>
+  </si>
+  <si>
+    <t>pane há 15 dias, prioridade ignorada</t>
+  </si>
+  <si>
+    <t>não resolveu o problema</t>
+  </si>
+  <si>
+    <t>técnico se recusou a trocar o filtro</t>
   </si>
 </sst>
 </file>
@@ -10948,7 +11174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10973,6 +11199,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11315,7 +11547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1681"/>
+  <dimension ref="A1:M1713"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" customWidth="1"/>
@@ -80255,6 +80487,1318 @@
         <v>2530</v>
       </c>
     </row>
+    <row r="1682" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1682" s="4">
+        <v>704</v>
+      </c>
+      <c r="B1682" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1682" s="4">
+        <v>166505</v>
+      </c>
+      <c r="D1682" s="2" t="s">
+        <v>3508</v>
+      </c>
+      <c r="E1682" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1682" s="9" t="s">
+        <v>3514</v>
+      </c>
+      <c r="G1682" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1682" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1682" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1682" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1682" s="4" t="s">
+        <v>3550</v>
+      </c>
+      <c r="L1682" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1682" s="9" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1683" s="4">
+        <v>705</v>
+      </c>
+      <c r="B1683" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1683" s="4">
+        <v>168073</v>
+      </c>
+      <c r="D1683" s="2" t="s">
+        <v>3508</v>
+      </c>
+      <c r="E1683" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1683" s="9" t="s">
+        <v>3515</v>
+      </c>
+      <c r="G1683" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1683" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1683" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1683" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1683" s="4" t="s">
+        <v>3551</v>
+      </c>
+      <c r="L1683" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1683" s="9" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1684" s="4">
+        <v>706</v>
+      </c>
+      <c r="B1684" s="9" t="s">
+        <v>3546</v>
+      </c>
+      <c r="C1684" s="4">
+        <v>153366</v>
+      </c>
+      <c r="D1684" s="2" t="s">
+        <v>3508</v>
+      </c>
+      <c r="E1684" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1684" s="10" t="s">
+        <v>3516</v>
+      </c>
+      <c r="G1684" s="4" t="s">
+        <v>3490</v>
+      </c>
+      <c r="H1684" s="4" t="s">
+        <v>3548</v>
+      </c>
+      <c r="I1684" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1684" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1684" s="4" t="s">
+        <v>3552</v>
+      </c>
+      <c r="L1684" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1684" s="9" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1685" s="4">
+        <v>707</v>
+      </c>
+      <c r="B1685" s="9" t="s">
+        <v>3546</v>
+      </c>
+      <c r="C1685" s="4">
+        <v>163914</v>
+      </c>
+      <c r="D1685" s="2" t="s">
+        <v>3509</v>
+      </c>
+      <c r="E1685" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1685" s="9" t="s">
+        <v>3517</v>
+      </c>
+      <c r="G1685" s="4" t="s">
+        <v>3490</v>
+      </c>
+      <c r="H1685" s="4" t="s">
+        <v>3548</v>
+      </c>
+      <c r="I1685" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1685" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1685" s="4" t="s">
+        <v>3553</v>
+      </c>
+      <c r="L1685" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1685" s="9" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1686" s="4">
+        <v>708</v>
+      </c>
+      <c r="B1686" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1686" s="4">
+        <v>156651</v>
+      </c>
+      <c r="D1686" s="2" t="s">
+        <v>3509</v>
+      </c>
+      <c r="E1686" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1686" s="9" t="s">
+        <v>3518</v>
+      </c>
+      <c r="G1686" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1686" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1686" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1686" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1686" s="4" t="s">
+        <v>3554</v>
+      </c>
+      <c r="L1686" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1686" s="9" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1687" s="4">
+        <v>709</v>
+      </c>
+      <c r="B1687" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1687" s="4">
+        <v>168394</v>
+      </c>
+      <c r="D1687" s="2" t="s">
+        <v>3509</v>
+      </c>
+      <c r="E1687" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1687" s="9" t="s">
+        <v>3519</v>
+      </c>
+      <c r="G1687" s="4" t="s">
+        <v>3490</v>
+      </c>
+      <c r="H1687" s="4" t="s">
+        <v>3549</v>
+      </c>
+      <c r="I1687" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1687" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1687" s="4" t="s">
+        <v>3555</v>
+      </c>
+      <c r="L1687" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1687" s="9" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1688" s="4">
+        <v>710</v>
+      </c>
+      <c r="B1688" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1688" s="4">
+        <v>155097</v>
+      </c>
+      <c r="D1688" s="2" t="s">
+        <v>3509</v>
+      </c>
+      <c r="E1688" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1688" s="9" t="s">
+        <v>3520</v>
+      </c>
+      <c r="G1688" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1688" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1688" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1688" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1688" s="4" t="s">
+        <v>3556</v>
+      </c>
+      <c r="L1688" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1688" s="9" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1689" s="4">
+        <v>711</v>
+      </c>
+      <c r="B1689" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1689" s="4">
+        <v>163223</v>
+      </c>
+      <c r="D1689" s="2" t="s">
+        <v>3509</v>
+      </c>
+      <c r="E1689" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1689" s="9" t="s">
+        <v>3521</v>
+      </c>
+      <c r="G1689" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1689" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1689" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1689" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1689" s="4" t="s">
+        <v>3557</v>
+      </c>
+      <c r="L1689" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1689" s="9" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1690" s="4">
+        <v>712</v>
+      </c>
+      <c r="B1690" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1690" s="4">
+        <v>170010</v>
+      </c>
+      <c r="D1690" s="2" t="s">
+        <v>3509</v>
+      </c>
+      <c r="E1690" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1690" s="9" t="s">
+        <v>3522</v>
+      </c>
+      <c r="G1690" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1690" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1690" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1690" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1690" s="4" t="s">
+        <v>3558</v>
+      </c>
+      <c r="L1690" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1690" s="9" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1691" s="4">
+        <v>713</v>
+      </c>
+      <c r="B1691" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1691" s="4">
+        <v>153427</v>
+      </c>
+      <c r="D1691" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E1691" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1691" s="9" t="s">
+        <v>3523</v>
+      </c>
+      <c r="G1691" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1691" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1691" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1691" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1691" s="4" t="s">
+        <v>3559</v>
+      </c>
+      <c r="L1691" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1691" s="9" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1692" s="4">
+        <v>714</v>
+      </c>
+      <c r="B1692" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1692" s="4">
+        <v>173112</v>
+      </c>
+      <c r="D1692" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E1692" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1692" s="9" t="s">
+        <v>3524</v>
+      </c>
+      <c r="G1692" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1692" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1692" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1692" s="9" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1692" s="4" t="s">
+        <v>3560</v>
+      </c>
+      <c r="L1692" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1692" s="9" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1693" s="4">
+        <v>715</v>
+      </c>
+      <c r="B1693" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1693" s="4">
+        <v>172045</v>
+      </c>
+      <c r="D1693" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E1693" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1693" s="9" t="s">
+        <v>3525</v>
+      </c>
+      <c r="G1693" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1693" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1693" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1693" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1693" s="4" t="s">
+        <v>3561</v>
+      </c>
+      <c r="L1693" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1693" s="9" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1694" s="4">
+        <v>716</v>
+      </c>
+      <c r="B1694" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1694" s="4">
+        <v>157679</v>
+      </c>
+      <c r="D1694" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E1694" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1694" s="9" t="s">
+        <v>3526</v>
+      </c>
+      <c r="G1694" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1694" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1694" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1694" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1694" s="4" t="s">
+        <v>3562</v>
+      </c>
+      <c r="L1694" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1694" s="9" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1695" s="4">
+        <v>717</v>
+      </c>
+      <c r="B1695" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1695" s="4">
+        <v>165293</v>
+      </c>
+      <c r="D1695" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E1695" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1695" s="9" t="s">
+        <v>3527</v>
+      </c>
+      <c r="G1695" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1695" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1695" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1695" s="9" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1695" s="4" t="s">
+        <v>3563</v>
+      </c>
+      <c r="L1695" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1695" s="9" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1696" s="4">
+        <v>718</v>
+      </c>
+      <c r="B1696" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1696" s="4">
+        <v>162009</v>
+      </c>
+      <c r="D1696" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E1696" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1696" s="9" t="s">
+        <v>3528</v>
+      </c>
+      <c r="G1696" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1696" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1696" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1696" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1696" s="4" t="s">
+        <v>3564</v>
+      </c>
+      <c r="L1696" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1696" s="9" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1697" s="4">
+        <v>719</v>
+      </c>
+      <c r="B1697" s="9" t="s">
+        <v>3547</v>
+      </c>
+      <c r="C1697" s="4">
+        <v>172154</v>
+      </c>
+      <c r="D1697" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E1697" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1697" s="9" t="s">
+        <v>3529</v>
+      </c>
+      <c r="G1697" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1697" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1697" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1697" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1697" s="4" t="s">
+        <v>3565</v>
+      </c>
+      <c r="L1697" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1697" s="9" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1698" s="4">
+        <v>720</v>
+      </c>
+      <c r="B1698" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1698" s="4">
+        <v>170452</v>
+      </c>
+      <c r="D1698" s="2" t="s">
+        <v>3510</v>
+      </c>
+      <c r="E1698" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1698" s="9" t="s">
+        <v>3530</v>
+      </c>
+      <c r="G1698" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1698" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1698" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1698" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1698" s="4" t="s">
+        <v>3566</v>
+      </c>
+      <c r="L1698" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1698" s="9" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1699" s="4">
+        <v>721</v>
+      </c>
+      <c r="B1699" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1699" s="4">
+        <v>173339</v>
+      </c>
+      <c r="D1699" s="2" t="s">
+        <v>3511</v>
+      </c>
+      <c r="E1699" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1699" s="9" t="s">
+        <v>3531</v>
+      </c>
+      <c r="G1699" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1699" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1699" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1699" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1699" s="4" t="s">
+        <v>3567</v>
+      </c>
+      <c r="L1699" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1699" s="9" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1700" s="4">
+        <v>722</v>
+      </c>
+      <c r="B1700" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1700" s="4">
+        <v>173868</v>
+      </c>
+      <c r="D1700" s="2" t="s">
+        <v>3511</v>
+      </c>
+      <c r="E1700" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1700" s="9" t="s">
+        <v>3532</v>
+      </c>
+      <c r="G1700" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1700" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1700" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1700" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1700" s="4" t="s">
+        <v>3568</v>
+      </c>
+      <c r="L1700" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1700" s="9" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1701" s="4">
+        <v>723</v>
+      </c>
+      <c r="B1701" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1701" s="4">
+        <v>175398</v>
+      </c>
+      <c r="D1701" s="2" t="s">
+        <v>3511</v>
+      </c>
+      <c r="E1701" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1701" s="9" t="s">
+        <v>3533</v>
+      </c>
+      <c r="G1701" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1701" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1701" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1701" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1701" s="4" t="s">
+        <v>3569</v>
+      </c>
+      <c r="L1701" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1701" s="9" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1702" s="4">
+        <v>724</v>
+      </c>
+      <c r="B1702" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1702" s="4">
+        <v>165541</v>
+      </c>
+      <c r="D1702" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1702" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1702" s="9" t="s">
+        <v>3534</v>
+      </c>
+      <c r="G1702" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1702" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1702" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1702" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1702" s="4" t="s">
+        <v>3570</v>
+      </c>
+      <c r="L1702" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1702" s="9" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1703" s="4">
+        <v>725</v>
+      </c>
+      <c r="B1703" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1703" s="4">
+        <v>175852</v>
+      </c>
+      <c r="D1703" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1703" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1703" s="9" t="s">
+        <v>3535</v>
+      </c>
+      <c r="G1703" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1703" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1703" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1703" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1703" s="4" t="s">
+        <v>3571</v>
+      </c>
+      <c r="L1703" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1703" s="9" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1704" s="4">
+        <v>726</v>
+      </c>
+      <c r="B1704" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1704" s="4">
+        <v>175672</v>
+      </c>
+      <c r="D1704" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1704" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1704" s="9" t="s">
+        <v>3536</v>
+      </c>
+      <c r="G1704" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1704" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1704" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1704" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1704" s="4" t="s">
+        <v>3572</v>
+      </c>
+      <c r="L1704" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1704" s="9" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1705" s="4">
+        <v>727</v>
+      </c>
+      <c r="B1705" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1705" s="4">
+        <v>154868</v>
+      </c>
+      <c r="D1705" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1705" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1705" s="9" t="s">
+        <v>3537</v>
+      </c>
+      <c r="G1705" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1705" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1705" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1705" s="9" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1705" s="4" t="s">
+        <v>3573</v>
+      </c>
+      <c r="L1705" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1705" s="9" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1706" s="4">
+        <v>728</v>
+      </c>
+      <c r="B1706" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1706" s="4">
+        <v>175611</v>
+      </c>
+      <c r="D1706" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1706" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1706" s="9" t="s">
+        <v>3538</v>
+      </c>
+      <c r="G1706" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1706" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1706" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1706" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1706" s="4" t="s">
+        <v>3574</v>
+      </c>
+      <c r="L1706" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1706" s="9" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1707" s="4">
+        <v>729</v>
+      </c>
+      <c r="B1707" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1707" s="4">
+        <v>167224</v>
+      </c>
+      <c r="D1707" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1707" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1707" s="9" t="s">
+        <v>3539</v>
+      </c>
+      <c r="G1707" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1707" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1707" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1707" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1707" s="4" t="s">
+        <v>3575</v>
+      </c>
+      <c r="L1707" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1707" s="9" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1708" s="4">
+        <v>730</v>
+      </c>
+      <c r="B1708" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1708" s="4">
+        <v>156628</v>
+      </c>
+      <c r="D1708" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1708" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1708" s="9" t="s">
+        <v>3540</v>
+      </c>
+      <c r="G1708" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1708" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1708" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1708" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1708" s="4" t="s">
+        <v>3576</v>
+      </c>
+      <c r="L1708" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1708" s="9" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1709" s="4">
+        <v>731</v>
+      </c>
+      <c r="B1709" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1709" s="4">
+        <v>175419</v>
+      </c>
+      <c r="D1709" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1709" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1709" s="9" t="s">
+        <v>3541</v>
+      </c>
+      <c r="G1709" s="4" t="s">
+        <v>3386</v>
+      </c>
+      <c r="H1709" s="4" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I1709" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1709" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1709" s="4" t="s">
+        <v>3577</v>
+      </c>
+      <c r="L1709" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1709" s="9" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1710" s="4">
+        <v>732</v>
+      </c>
+      <c r="B1710" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1710" s="4">
+        <v>157288</v>
+      </c>
+      <c r="D1710" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1710" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1710" s="9" t="s">
+        <v>3542</v>
+      </c>
+      <c r="G1710" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1710" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="I1710" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1710" s="9" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1710" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="L1710" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1710" s="9" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1711" s="4">
+        <v>733</v>
+      </c>
+      <c r="B1711" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1711" s="4">
+        <v>167665</v>
+      </c>
+      <c r="D1711" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1711" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1711" s="9" t="s">
+        <v>3543</v>
+      </c>
+      <c r="G1711" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1711" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1711" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1711" s="9" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K1711" s="4" t="s">
+        <v>3578</v>
+      </c>
+      <c r="L1711" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1711" s="9" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1712" s="4">
+        <v>734</v>
+      </c>
+      <c r="B1712" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1712" s="4">
+        <v>163769</v>
+      </c>
+      <c r="D1712" s="2" t="s">
+        <v>3512</v>
+      </c>
+      <c r="E1712" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1712" s="9" t="s">
+        <v>3544</v>
+      </c>
+      <c r="G1712" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1712" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1712" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1712" s="9" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1712" s="4" t="s">
+        <v>3579</v>
+      </c>
+      <c r="L1712" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M1712" s="9" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1713" s="4">
+        <v>735</v>
+      </c>
+      <c r="B1713" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1713" s="4">
+        <v>151528</v>
+      </c>
+      <c r="D1713" s="2" t="s">
+        <v>3513</v>
+      </c>
+      <c r="E1713" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1713" s="9" t="s">
+        <v>3545</v>
+      </c>
+      <c r="G1713" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1713" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1713" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J1713" s="9" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K1713" s="4" t="s">
+        <v>3580</v>
+      </c>
+      <c r="L1713" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="M1713" s="9" t="s">
+        <v>2521</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
